--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DE5F83-3E60-4744-AE0F-2CC540EE117D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7208C55-1EB8-45D9-A093-90F802638BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="57">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -45,142 +45,160 @@
     <t xml:space="preserve">Modelo/Descrição </t>
   </si>
   <si>
+    <t xml:space="preserve">Anexo </t>
+  </si>
+  <si>
     <t>Processar</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 10.10.2025</t>
-  </si>
-  <si>
-    <t>134852722</t>
-  </si>
-  <si>
-    <t>134617606</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 27.10.2025</t>
-  </si>
-  <si>
-    <t>130257664</t>
-  </si>
-  <si>
-    <t>134697708</t>
-  </si>
-  <si>
-    <t>135092546</t>
-  </si>
-  <si>
-    <t>130310014</t>
-  </si>
-  <si>
-    <t>130014712</t>
-  </si>
-  <si>
-    <t>135061934</t>
-  </si>
-  <si>
-    <t>130066497</t>
-  </si>
-  <si>
-    <t>135003898</t>
-  </si>
-  <si>
-    <t>135014998</t>
-  </si>
-  <si>
-    <t>135003011</t>
-  </si>
-  <si>
-    <t>129867323</t>
-  </si>
-  <si>
-    <t>134976368</t>
-  </si>
-  <si>
-    <t>134595190</t>
-  </si>
-  <si>
-    <t>134981862</t>
-  </si>
-  <si>
-    <t>130277925</t>
-  </si>
-  <si>
-    <t>135100359</t>
-  </si>
-  <si>
-    <t>135107393</t>
-  </si>
-  <si>
-    <t>134858558</t>
-  </si>
-  <si>
-    <t>130068124</t>
-  </si>
-  <si>
-    <t>135029025</t>
-  </si>
-  <si>
-    <t>130086716</t>
-  </si>
-  <si>
-    <t>135088949</t>
-  </si>
-  <si>
-    <t>135000174</t>
-  </si>
-  <si>
-    <t>135079918</t>
-  </si>
-  <si>
-    <t>134611517</t>
-  </si>
-  <si>
-    <t>130194102</t>
-  </si>
-  <si>
-    <t>134988980</t>
-  </si>
-  <si>
-    <t>134852215</t>
-  </si>
-  <si>
-    <t>135040123</t>
-  </si>
-  <si>
-    <t>134810688</t>
-  </si>
-  <si>
-    <t>135027030</t>
-  </si>
-  <si>
-    <t>135100764</t>
-  </si>
-  <si>
-    <t>135111265</t>
-  </si>
-  <si>
-    <t>134864276</t>
-  </si>
-  <si>
-    <t>134865148</t>
-  </si>
-  <si>
-    <t>135002482</t>
-  </si>
-  <si>
-    <t>135057013</t>
-  </si>
-  <si>
-    <t>133669273</t>
+    <t>135003730</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 28.10.2025</t>
+  </si>
+  <si>
+    <t>135092299</t>
+  </si>
+  <si>
+    <t>135096367</t>
+  </si>
+  <si>
+    <t>134893487</t>
+  </si>
+  <si>
+    <t>135106629</t>
+  </si>
+  <si>
+    <t>134897197</t>
+  </si>
+  <si>
+    <t>135024331</t>
+  </si>
+  <si>
+    <t>135009335</t>
+  </si>
+  <si>
+    <t>134402522</t>
+  </si>
+  <si>
+    <t>135011662</t>
+  </si>
+  <si>
+    <t>135103101</t>
   </si>
   <si>
     <t>135095994</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 27.10.2025</t>
+    <t>133058479</t>
+  </si>
+  <si>
+    <t>134285775</t>
+  </si>
+  <si>
+    <t>130315191</t>
+  </si>
+  <si>
+    <t>130095985</t>
+  </si>
+  <si>
+    <t>135146962</t>
+  </si>
+  <si>
+    <t>130264118</t>
+  </si>
+  <si>
+    <t>135100006</t>
+  </si>
+  <si>
+    <t>134640424</t>
+  </si>
+  <si>
+    <t>135114338</t>
+  </si>
+  <si>
+    <t>135060555</t>
+  </si>
+  <si>
+    <t>134898597</t>
+  </si>
+  <si>
+    <t>130203575</t>
+  </si>
+  <si>
+    <t>135106816</t>
+  </si>
+  <si>
+    <t>134916396</t>
+  </si>
+  <si>
+    <t>130241563</t>
+  </si>
+  <si>
+    <t>134640382</t>
+  </si>
+  <si>
+    <t>134856490</t>
+  </si>
+  <si>
+    <t>135101782</t>
+  </si>
+  <si>
+    <t>135106611</t>
+  </si>
+  <si>
+    <t>130306862</t>
+  </si>
+  <si>
+    <t>134282987</t>
+  </si>
+  <si>
+    <t>134920573</t>
+  </si>
+  <si>
+    <t>130351974</t>
+  </si>
+  <si>
+    <t>135028444</t>
+  </si>
+  <si>
+    <t>134874102</t>
+  </si>
+  <si>
+    <t>134858646</t>
+  </si>
+  <si>
+    <t>135118005</t>
+  </si>
+  <si>
+    <t>132923191</t>
+  </si>
+  <si>
+    <t>135129372</t>
+  </si>
+  <si>
+    <t>129917574</t>
+  </si>
+  <si>
+    <t>135106834</t>
+  </si>
+  <si>
+    <t>135109798</t>
+  </si>
+  <si>
+    <t>135097460</t>
+  </si>
+  <si>
+    <t>134863976</t>
+  </si>
+  <si>
+    <t>134229560</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 28.10.2025</t>
   </si>
 </sst>
 </file>
@@ -576,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -597,7 +615,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -608,699 +626,835 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>5</v>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1317,31 +1471,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7208C55-1EB8-45D9-A093-90F802638BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E50C9F-089E-42F9-BB62-9B5F902EE100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,151 +54,118 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135003730</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 28.10.2025</t>
-  </si>
-  <si>
-    <t>135092299</t>
-  </si>
-  <si>
-    <t>135096367</t>
-  </si>
-  <si>
-    <t>134893487</t>
-  </si>
-  <si>
-    <t>135106629</t>
-  </si>
-  <si>
-    <t>134897197</t>
-  </si>
-  <si>
-    <t>135024331</t>
-  </si>
-  <si>
-    <t>135009335</t>
-  </si>
-  <si>
-    <t>134402522</t>
-  </si>
-  <si>
-    <t>135011662</t>
-  </si>
-  <si>
-    <t>135103101</t>
-  </si>
-  <si>
-    <t>135095994</t>
-  </si>
-  <si>
-    <t>133058479</t>
-  </si>
-  <si>
-    <t>134285775</t>
-  </si>
-  <si>
-    <t>130315191</t>
-  </si>
-  <si>
-    <t>130095985</t>
-  </si>
-  <si>
-    <t>135146962</t>
-  </si>
-  <si>
-    <t>130264118</t>
-  </si>
-  <si>
-    <t>135100006</t>
-  </si>
-  <si>
-    <t>134640424</t>
-  </si>
-  <si>
-    <t>135114338</t>
-  </si>
-  <si>
-    <t>135060555</t>
-  </si>
-  <si>
-    <t>134898597</t>
-  </si>
-  <si>
-    <t>130203575</t>
-  </si>
-  <si>
-    <t>135106816</t>
-  </si>
-  <si>
-    <t>134916396</t>
-  </si>
-  <si>
-    <t>130241563</t>
-  </si>
-  <si>
-    <t>134640382</t>
-  </si>
-  <si>
-    <t>134856490</t>
-  </si>
-  <si>
-    <t>135101782</t>
-  </si>
-  <si>
-    <t>135106611</t>
-  </si>
-  <si>
-    <t>130306862</t>
-  </si>
-  <si>
-    <t>134282987</t>
-  </si>
-  <si>
-    <t>134920573</t>
-  </si>
-  <si>
-    <t>130351974</t>
-  </si>
-  <si>
-    <t>135028444</t>
-  </si>
-  <si>
-    <t>134874102</t>
-  </si>
-  <si>
-    <t>134858646</t>
-  </si>
-  <si>
-    <t>135118005</t>
-  </si>
-  <si>
-    <t>132923191</t>
-  </si>
-  <si>
-    <t>135129372</t>
-  </si>
-  <si>
-    <t>129917574</t>
-  </si>
-  <si>
-    <t>135106834</t>
-  </si>
-  <si>
-    <t>135109798</t>
-  </si>
-  <si>
-    <t>135097460</t>
-  </si>
-  <si>
-    <t>134863976</t>
-  </si>
-  <si>
-    <t>134229560</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 28.10.2025</t>
+    <t>135022813</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 29.10.2025</t>
+  </si>
+  <si>
+    <t>135106703</t>
+  </si>
+  <si>
+    <t>134972033</t>
+  </si>
+  <si>
+    <t>130081308</t>
+  </si>
+  <si>
+    <t>135109721</t>
+  </si>
+  <si>
+    <t>134941764</t>
+  </si>
+  <si>
+    <t>135110746</t>
+  </si>
+  <si>
+    <t>135003304</t>
+  </si>
+  <si>
+    <t>130288302</t>
+  </si>
+  <si>
+    <t>130289024</t>
+  </si>
+  <si>
+    <t>130099984</t>
+  </si>
+  <si>
+    <t>135003228</t>
+  </si>
+  <si>
+    <t>134897146</t>
+  </si>
+  <si>
+    <t>135103592</t>
+  </si>
+  <si>
+    <t>135126562</t>
+  </si>
+  <si>
+    <t>129925448</t>
+  </si>
+  <si>
+    <t>135101897</t>
+  </si>
+  <si>
+    <t>135003202</t>
+  </si>
+  <si>
+    <t>135130198</t>
+  </si>
+  <si>
+    <t>134962886</t>
+  </si>
+  <si>
+    <t>134931982</t>
+  </si>
+  <si>
+    <t>135003368</t>
+  </si>
+  <si>
+    <t>135118669</t>
+  </si>
+  <si>
+    <t>135096962</t>
+  </si>
+  <si>
+    <t>135112032</t>
+  </si>
+  <si>
+    <t>135104477</t>
+  </si>
+  <si>
+    <t>134748070</t>
+  </si>
+  <si>
+    <t>135106811</t>
+  </si>
+  <si>
+    <t>133075744</t>
+  </si>
+  <si>
+    <t>129971237</t>
+  </si>
+  <si>
+    <t>133613295</t>
+  </si>
+  <si>
+    <t>135016248</t>
+  </si>
+  <si>
+    <t>134992535</t>
+  </si>
+  <si>
+    <t>129925764</t>
+  </si>
+  <si>
+    <t>135035358</t>
+  </si>
+  <si>
+    <t>134938173</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 29.10.2025</t>
   </si>
 </sst>
 </file>
@@ -594,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -635,7 +602,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -653,7 +620,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -671,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -689,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -707,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -725,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -743,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -761,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -779,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -797,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -815,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -833,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -851,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -869,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -887,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -905,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -923,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -941,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -959,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -977,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -995,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1031,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1049,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1067,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1085,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1103,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1121,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1139,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1157,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1175,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1193,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1211,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1229,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1247,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1264,196 +1231,9 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1471,31 +1251,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E50C9F-089E-42F9-BB62-9B5F902EE100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814F4CD8-DAA4-46A2-88F8-26BDF4484410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="124">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,118 +54,352 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135022813</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 29.10.2025</t>
-  </si>
-  <si>
-    <t>135106703</t>
-  </si>
-  <si>
-    <t>134972033</t>
-  </si>
-  <si>
-    <t>130081308</t>
-  </si>
-  <si>
-    <t>135109721</t>
-  </si>
-  <si>
-    <t>134941764</t>
-  </si>
-  <si>
-    <t>135110746</t>
-  </si>
-  <si>
-    <t>135003304</t>
-  </si>
-  <si>
-    <t>130288302</t>
-  </si>
-  <si>
-    <t>130289024</t>
-  </si>
-  <si>
-    <t>130099984</t>
-  </si>
-  <si>
-    <t>135003228</t>
-  </si>
-  <si>
-    <t>134897146</t>
-  </si>
-  <si>
-    <t>135103592</t>
-  </si>
-  <si>
-    <t>135126562</t>
-  </si>
-  <si>
-    <t>129925448</t>
-  </si>
-  <si>
-    <t>135101897</t>
-  </si>
-  <si>
-    <t>135003202</t>
-  </si>
-  <si>
-    <t>135130198</t>
-  </si>
-  <si>
-    <t>134962886</t>
-  </si>
-  <si>
-    <t>134931982</t>
-  </si>
-  <si>
-    <t>135003368</t>
-  </si>
-  <si>
-    <t>135118669</t>
-  </si>
-  <si>
-    <t>135096962</t>
-  </si>
-  <si>
-    <t>135112032</t>
-  </si>
-  <si>
-    <t>135104477</t>
-  </si>
-  <si>
-    <t>134748070</t>
-  </si>
-  <si>
-    <t>135106811</t>
-  </si>
-  <si>
-    <t>133075744</t>
-  </si>
-  <si>
-    <t>129971237</t>
-  </si>
-  <si>
-    <t>133613295</t>
-  </si>
-  <si>
-    <t>135016248</t>
-  </si>
-  <si>
-    <t>134992535</t>
-  </si>
-  <si>
-    <t>129925764</t>
-  </si>
-  <si>
-    <t>135035358</t>
-  </si>
-  <si>
-    <t>134938173</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 29.10.2025</t>
+    <t>135126555</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 30.10.2025</t>
+  </si>
+  <si>
+    <t>134606910</t>
+  </si>
+  <si>
+    <t>135101886</t>
+  </si>
+  <si>
+    <t>135100689</t>
+  </si>
+  <si>
+    <t>135126978</t>
+  </si>
+  <si>
+    <t>135137862</t>
+  </si>
+  <si>
+    <t>135005199</t>
+  </si>
+  <si>
+    <t>135003708</t>
+  </si>
+  <si>
+    <t>132333252</t>
+  </si>
+  <si>
+    <t>134520143</t>
+  </si>
+  <si>
+    <t>135003505</t>
+  </si>
+  <si>
+    <t>135068030</t>
+  </si>
+  <si>
+    <t>134921282</t>
+  </si>
+  <si>
+    <t>135126771</t>
+  </si>
+  <si>
+    <t>135003586</t>
+  </si>
+  <si>
+    <t>134916362</t>
+  </si>
+  <si>
+    <t>134985751</t>
+  </si>
+  <si>
+    <t>135126539</t>
+  </si>
+  <si>
+    <t>130320476</t>
+  </si>
+  <si>
+    <t>130180004</t>
+  </si>
+  <si>
+    <t>135011488</t>
+  </si>
+  <si>
+    <t>134858520</t>
+  </si>
+  <si>
+    <t>135096619</t>
+  </si>
+  <si>
+    <t>130065811</t>
+  </si>
+  <si>
+    <t>135106790</t>
+  </si>
+  <si>
+    <t>134828532</t>
+  </si>
+  <si>
+    <t>130248747</t>
+  </si>
+  <si>
+    <t>134086428</t>
+  </si>
+  <si>
+    <t>135089966</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 30.10.2025</t>
+  </si>
+  <si>
+    <t>130078841</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 31.10.2025</t>
+  </si>
+  <si>
+    <t>134721671</t>
+  </si>
+  <si>
+    <t>135100251</t>
+  </si>
+  <si>
+    <t>135106785</t>
+  </si>
+  <si>
+    <t>135106854</t>
+  </si>
+  <si>
+    <t>130361712</t>
+  </si>
+  <si>
+    <t>134859335</t>
+  </si>
+  <si>
+    <t>135097822</t>
+  </si>
+  <si>
+    <t>135105244</t>
+  </si>
+  <si>
+    <t>135049705</t>
+  </si>
+  <si>
+    <t>130258711</t>
+  </si>
+  <si>
+    <t>134988676</t>
+  </si>
+  <si>
+    <t>135116969</t>
+  </si>
+  <si>
+    <t>135148017</t>
+  </si>
+  <si>
+    <t>135064936</t>
+  </si>
+  <si>
+    <t>130301348</t>
+  </si>
+  <si>
+    <t>130099959</t>
+  </si>
+  <si>
+    <t>134679695</t>
+  </si>
+  <si>
+    <t>135106726</t>
+  </si>
+  <si>
+    <t>135155268</t>
+  </si>
+  <si>
+    <t>129968132</t>
+  </si>
+  <si>
+    <t>135101854</t>
+  </si>
+  <si>
+    <t>130987069</t>
+  </si>
+  <si>
+    <t>130321570</t>
+  </si>
+  <si>
+    <t>135107374</t>
+  </si>
+  <si>
+    <t>134971817</t>
+  </si>
+  <si>
+    <t>135021720</t>
+  </si>
+  <si>
+    <t>135137762</t>
+  </si>
+  <si>
+    <t>135208989</t>
+  </si>
+  <si>
+    <t>135170987</t>
+  </si>
+  <si>
+    <t>135061634</t>
+  </si>
+  <si>
+    <t>135116743</t>
+  </si>
+  <si>
+    <t>135057553</t>
+  </si>
+  <si>
+    <t>135003641</t>
+  </si>
+  <si>
+    <t>133631823</t>
+  </si>
+  <si>
+    <t>135023307</t>
+  </si>
+  <si>
+    <t>135111233</t>
+  </si>
+  <si>
+    <t>135171249</t>
+  </si>
+  <si>
+    <t>135156075</t>
+  </si>
+  <si>
+    <t>134897729</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 31.10.2025</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 03.11.2025</t>
+  </si>
+  <si>
+    <t>135044242</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 03.11.2025</t>
+  </si>
+  <si>
+    <t>135169011</t>
+  </si>
+  <si>
+    <t>135103804</t>
+  </si>
+  <si>
+    <t>135096701</t>
+  </si>
+  <si>
+    <t>135104195</t>
+  </si>
+  <si>
+    <t>129999606</t>
+  </si>
+  <si>
+    <t>135166506</t>
+  </si>
+  <si>
+    <t>130210173</t>
+  </si>
+  <si>
+    <t>130350191</t>
+  </si>
+  <si>
+    <t>135224431</t>
+  </si>
+  <si>
+    <t>133882717</t>
+  </si>
+  <si>
+    <t>135056953</t>
+  </si>
+  <si>
+    <t>135195143</t>
+  </si>
+  <si>
+    <t>135151101</t>
+  </si>
+  <si>
+    <t>135003547</t>
+  </si>
+  <si>
+    <t>129947153</t>
+  </si>
+  <si>
+    <t>130104869</t>
+  </si>
+  <si>
+    <t>135003455</t>
+  </si>
+  <si>
+    <t>135051444</t>
+  </si>
+  <si>
+    <t>130098394</t>
+  </si>
+  <si>
+    <t>135180844</t>
+  </si>
+  <si>
+    <t>135111759</t>
+  </si>
+  <si>
+    <t>135102994</t>
+  </si>
+  <si>
+    <t>135095020</t>
+  </si>
+  <si>
+    <t>135207078</t>
+  </si>
+  <si>
+    <t>135003561</t>
+  </si>
+  <si>
+    <t>135171462</t>
+  </si>
+  <si>
+    <t>133317087</t>
+  </si>
+  <si>
+    <t>135172638</t>
+  </si>
+  <si>
+    <t>130039103</t>
+  </si>
+  <si>
+    <t>134902761</t>
+  </si>
+  <si>
+    <t>130107347</t>
+  </si>
+  <si>
+    <t>130360940</t>
+  </si>
+  <si>
+    <t>135104456</t>
+  </si>
+  <si>
+    <t>134944215</t>
+  </si>
+  <si>
+    <t>135187075</t>
+  </si>
+  <si>
+    <t>130770923</t>
+  </si>
+  <si>
+    <t>130664102</t>
+  </si>
+  <si>
+    <t>135179285</t>
+  </si>
+  <si>
+    <t>130015028</t>
+  </si>
+  <si>
+    <t>135177383</t>
   </si>
 </sst>
 </file>
@@ -561,7 +795,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -602,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -620,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -638,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -674,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -692,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -710,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -728,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -746,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -764,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -782,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -800,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -836,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -854,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -872,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -890,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -908,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -926,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -944,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -962,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -980,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -998,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1304,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1322,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1349,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1133,16 +1367,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1151,16 +1385,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1169,16 +1403,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1187,16 +1421,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1205,16 +1439,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1222,18 +1456,1344 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1251,31 +2811,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE59196F-DE94-42B6-970D-CB7FFED0EE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2407060-B5E7-4961-825B-C48997F7769A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,175 +54,139 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135004018</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 04.11.2025</t>
-  </si>
-  <si>
-    <t>135099857</t>
-  </si>
-  <si>
-    <t>135152135</t>
-  </si>
-  <si>
-    <t>135206362</t>
-  </si>
-  <si>
-    <t>135092486</t>
-  </si>
-  <si>
-    <t>130412317</t>
-  </si>
-  <si>
-    <t>135162952</t>
-  </si>
-  <si>
-    <t>135094478</t>
-  </si>
-  <si>
-    <t>135150549</t>
-  </si>
-  <si>
-    <t>135173459</t>
-  </si>
-  <si>
-    <t>135111167</t>
-  </si>
-  <si>
-    <t>135003257</t>
-  </si>
-  <si>
-    <t>135011729</t>
-  </si>
-  <si>
-    <t>134937504</t>
-  </si>
-  <si>
-    <t>135150239</t>
-  </si>
-  <si>
-    <t>135173508</t>
-  </si>
-  <si>
-    <t>135150672</t>
-  </si>
-  <si>
-    <t>135205799</t>
-  </si>
-  <si>
-    <t>135099564</t>
-  </si>
-  <si>
-    <t>130088458</t>
-  </si>
-  <si>
-    <t>130019913</t>
-  </si>
-  <si>
-    <t>135108100</t>
-  </si>
-  <si>
-    <t>135211114</t>
-  </si>
-  <si>
-    <t>135003251</t>
-  </si>
-  <si>
-    <t>135131515</t>
-  </si>
-  <si>
-    <t>135083116</t>
-  </si>
-  <si>
-    <t>135003632</t>
-  </si>
-  <si>
-    <t>135009527</t>
-  </si>
-  <si>
-    <t>130474299</t>
-  </si>
-  <si>
-    <t>135175815</t>
-  </si>
-  <si>
-    <t>135221235</t>
-  </si>
-  <si>
-    <t>135094828</t>
-  </si>
-  <si>
-    <t>135175225</t>
-  </si>
-  <si>
-    <t>129861585</t>
-  </si>
-  <si>
-    <t>135148512</t>
-  </si>
-  <si>
-    <t>130125238</t>
-  </si>
-  <si>
-    <t>135107385</t>
-  </si>
-  <si>
-    <t>135107585</t>
-  </si>
-  <si>
-    <t>135058412</t>
-  </si>
-  <si>
-    <t>135169909</t>
-  </si>
-  <si>
-    <t>130300623</t>
-  </si>
-  <si>
-    <t>135094098</t>
-  </si>
-  <si>
-    <t>130333716</t>
-  </si>
-  <si>
-    <t>135222859</t>
-  </si>
-  <si>
-    <t>134991311</t>
-  </si>
-  <si>
-    <t>135029538</t>
-  </si>
-  <si>
-    <t>135178635</t>
-  </si>
-  <si>
-    <t>134859010</t>
-  </si>
-  <si>
-    <t>135173956</t>
-  </si>
-  <si>
-    <t>130152466</t>
-  </si>
-  <si>
-    <t>134897293</t>
-  </si>
-  <si>
-    <t>135128447</t>
-  </si>
-  <si>
-    <t>133982457</t>
-  </si>
-  <si>
-    <t>130185462</t>
-  </si>
-  <si>
-    <t>132489540</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 04.11.2025</t>
+    <t>135106677</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.11.2025</t>
+  </si>
+  <si>
+    <t>135100203</t>
+  </si>
+  <si>
+    <t>130389688</t>
+  </si>
+  <si>
+    <t>130003555</t>
+  </si>
+  <si>
+    <t>135211128</t>
+  </si>
+  <si>
+    <t>135168582</t>
+  </si>
+  <si>
+    <t>135060171</t>
+  </si>
+  <si>
+    <t>134997397</t>
+  </si>
+  <si>
+    <t>135215076</t>
+  </si>
+  <si>
+    <t>135221699</t>
+  </si>
+  <si>
+    <t>130245919</t>
+  </si>
+  <si>
+    <t>135251151</t>
+  </si>
+  <si>
+    <t>135102897</t>
+  </si>
+  <si>
+    <t>135211338</t>
+  </si>
+  <si>
+    <t>135003524</t>
+  </si>
+  <si>
+    <t>129972278</t>
+  </si>
+  <si>
+    <t>130390055</t>
+  </si>
+  <si>
+    <t>135061502</t>
+  </si>
+  <si>
+    <t>135059757</t>
+  </si>
+  <si>
+    <t>130367197</t>
+  </si>
+  <si>
+    <t>135218311</t>
+  </si>
+  <si>
+    <t>130221095</t>
+  </si>
+  <si>
+    <t>135146736</t>
+  </si>
+  <si>
+    <t>135106829</t>
+  </si>
+  <si>
+    <t>130449507</t>
+  </si>
+  <si>
+    <t>130123995</t>
+  </si>
+  <si>
+    <t>135174995</t>
+  </si>
+  <si>
+    <t>130239301</t>
+  </si>
+  <si>
+    <t>135150017</t>
+  </si>
+  <si>
+    <t>135101459</t>
+  </si>
+  <si>
+    <t>131059736</t>
+  </si>
+  <si>
+    <t>135148030</t>
+  </si>
+  <si>
+    <t>129826618</t>
+  </si>
+  <si>
+    <t>130310585</t>
+  </si>
+  <si>
+    <t>130109728</t>
+  </si>
+  <si>
+    <t>135003119</t>
+  </si>
+  <si>
+    <t>135021723</t>
+  </si>
+  <si>
+    <t>135206522</t>
+  </si>
+  <si>
+    <t>135006254</t>
+  </si>
+  <si>
+    <t>135104432</t>
+  </si>
+  <si>
+    <t>134079569</t>
+  </si>
+  <si>
+    <t>135005138</t>
+  </si>
+  <si>
+    <t>135126509</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 05.11.2025</t>
   </si>
 </sst>
 </file>
@@ -618,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -659,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -677,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -695,7 +659,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -713,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -731,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -749,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -767,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -785,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -803,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -821,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -839,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -857,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -875,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -893,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -911,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -929,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -947,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -965,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -983,7 +947,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1001,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1019,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1199,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1217,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1235,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1253,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1271,7 +1235,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1288,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1305,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1322,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1339,7 +1303,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1356,7 +1320,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1373,7 +1337,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1390,7 +1354,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1407,213 +1371,9 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1631,31 +1391,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2407060-B5E7-4961-825B-C48997F7769A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A05E260-B577-482C-8B72-0B5F5629EE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="73">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,139 +54,199 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135106677</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 05.11.2025</t>
-  </si>
-  <si>
-    <t>135100203</t>
-  </si>
-  <si>
-    <t>130389688</t>
-  </si>
-  <si>
-    <t>130003555</t>
-  </si>
-  <si>
-    <t>135211128</t>
-  </si>
-  <si>
-    <t>135168582</t>
-  </si>
-  <si>
-    <t>135060171</t>
-  </si>
-  <si>
-    <t>134997397</t>
-  </si>
-  <si>
-    <t>135215076</t>
-  </si>
-  <si>
-    <t>135221699</t>
-  </si>
-  <si>
-    <t>130245919</t>
-  </si>
-  <si>
-    <t>135251151</t>
-  </si>
-  <si>
-    <t>135102897</t>
-  </si>
-  <si>
-    <t>135211338</t>
-  </si>
-  <si>
-    <t>135003524</t>
-  </si>
-  <si>
-    <t>129972278</t>
-  </si>
-  <si>
-    <t>130390055</t>
-  </si>
-  <si>
-    <t>135061502</t>
-  </si>
-  <si>
-    <t>135059757</t>
-  </si>
-  <si>
-    <t>130367197</t>
-  </si>
-  <si>
-    <t>135218311</t>
-  </si>
-  <si>
-    <t>130221095</t>
-  </si>
-  <si>
-    <t>135146736</t>
-  </si>
-  <si>
-    <t>135106829</t>
-  </si>
-  <si>
-    <t>130449507</t>
-  </si>
-  <si>
-    <t>130123995</t>
-  </si>
-  <si>
-    <t>135174995</t>
-  </si>
-  <si>
-    <t>130239301</t>
-  </si>
-  <si>
-    <t>135150017</t>
-  </si>
-  <si>
-    <t>135101459</t>
-  </si>
-  <si>
-    <t>131059736</t>
-  </si>
-  <si>
-    <t>135148030</t>
-  </si>
-  <si>
-    <t>129826618</t>
-  </si>
-  <si>
-    <t>130310585</t>
-  </si>
-  <si>
-    <t>130109728</t>
-  </si>
-  <si>
-    <t>135003119</t>
-  </si>
-  <si>
-    <t>135021723</t>
-  </si>
-  <si>
-    <t>135206522</t>
-  </si>
-  <si>
-    <t>135006254</t>
-  </si>
-  <si>
-    <t>135104432</t>
-  </si>
-  <si>
-    <t>134079569</t>
-  </si>
-  <si>
-    <t>135005138</t>
-  </si>
-  <si>
     <t>135126509</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 05.11.2025</t>
+    <t>135206422</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 06.11.2025</t>
+  </si>
+  <si>
+    <t>135224450</t>
+  </si>
+  <si>
+    <t>135206509</t>
+  </si>
+  <si>
+    <t>135110556</t>
+  </si>
+  <si>
+    <t>130183860</t>
+  </si>
+  <si>
+    <t>130351949</t>
+  </si>
+  <si>
+    <t>135278803</t>
+  </si>
+  <si>
+    <t>135007116</t>
+  </si>
+  <si>
+    <t>135198264</t>
+  </si>
+  <si>
+    <t>135207436</t>
+  </si>
+  <si>
+    <t>135100560</t>
+  </si>
+  <si>
+    <t>135191534</t>
+  </si>
+  <si>
+    <t>135172778</t>
+  </si>
+  <si>
+    <t>135100709</t>
+  </si>
+  <si>
+    <t>134921983</t>
+  </si>
+  <si>
+    <t>135113084</t>
+  </si>
+  <si>
+    <t>134696293</t>
+  </si>
+  <si>
+    <t>135280071</t>
+  </si>
+  <si>
+    <t>135168660</t>
+  </si>
+  <si>
+    <t>130230489</t>
+  </si>
+  <si>
+    <t>135003607</t>
+  </si>
+  <si>
+    <t>130187440</t>
+  </si>
+  <si>
+    <t>135106930</t>
+  </si>
+  <si>
+    <t>130226433</t>
+  </si>
+  <si>
+    <t>135164609</t>
+  </si>
+  <si>
+    <t>135219941</t>
+  </si>
+  <si>
+    <t>130279427</t>
+  </si>
+  <si>
+    <t>130368183</t>
+  </si>
+  <si>
+    <t>135134233</t>
+  </si>
+  <si>
+    <t>135131988</t>
+  </si>
+  <si>
+    <t>135239617</t>
+  </si>
+  <si>
+    <t>130314880</t>
+  </si>
+  <si>
+    <t>135061246</t>
+  </si>
+  <si>
+    <t>135206403</t>
+  </si>
+  <si>
+    <t>135207104</t>
+  </si>
+  <si>
+    <t>130059903</t>
+  </si>
+  <si>
+    <t>135252883</t>
+  </si>
+  <si>
+    <t>130386928</t>
+  </si>
+  <si>
+    <t>135227889</t>
+  </si>
+  <si>
+    <t>135109385</t>
+  </si>
+  <si>
+    <t>130140873</t>
+  </si>
+  <si>
+    <t>130189168</t>
+  </si>
+  <si>
+    <t>135245695</t>
+  </si>
+  <si>
+    <t>135185493</t>
+  </si>
+  <si>
+    <t>135154633</t>
+  </si>
+  <si>
+    <t>130256226</t>
+  </si>
+  <si>
+    <t>130195297</t>
+  </si>
+  <si>
+    <t>135003877</t>
+  </si>
+  <si>
+    <t>135095194</t>
+  </si>
+  <si>
+    <t>135106866</t>
+  </si>
+  <si>
+    <t>130435730</t>
+  </si>
+  <si>
+    <t>135260735</t>
+  </si>
+  <si>
+    <t>135262875</t>
+  </si>
+  <si>
+    <t>135175444</t>
+  </si>
+  <si>
+    <t>135002578</t>
+  </si>
+  <si>
+    <t>135250083</t>
+  </si>
+  <si>
+    <t>135243275</t>
+  </si>
+  <si>
+    <t>135211786</t>
+  </si>
+  <si>
+    <t>132463969</t>
+  </si>
+  <si>
+    <t>135276240</t>
+  </si>
+  <si>
+    <t>135104022</t>
+  </si>
+  <si>
+    <t>135206542</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
   </si>
 </sst>
 </file>
@@ -582,7 +642,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,16 +674,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -632,16 +692,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -650,16 +710,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -668,16 +728,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -686,16 +746,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -704,16 +764,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -722,16 +782,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -740,16 +800,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -758,16 +818,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -776,16 +836,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -794,16 +854,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -812,16 +872,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -830,16 +890,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -848,16 +908,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -866,16 +926,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -884,16 +944,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -902,16 +962,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -920,16 +980,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -938,16 +998,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -962,10 +1022,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -980,10 +1040,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -998,10 +1058,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,10 +1076,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1034,10 +1094,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1052,10 +1112,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1070,10 +1130,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1088,10 +1148,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1106,10 +1166,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1124,10 +1184,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1142,10 +1202,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1160,10 +1220,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1178,10 +1238,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1196,10 +1256,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1214,10 +1274,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1232,10 +1292,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1249,10 +1309,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1266,10 +1326,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1277,16 +1337,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1294,16 +1354,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1311,16 +1371,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1328,16 +1388,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1345,16 +1405,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1362,18 +1422,375 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1391,31 +1808,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A05E260-B577-482C-8B72-0B5F5629EE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15EBD7E-AF1A-4542-B27B-1531AD35A59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,199 +54,97 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135126509</t>
-  </si>
-  <si>
-    <t>135206422</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 06.11.2025</t>
-  </si>
-  <si>
-    <t>135224450</t>
-  </si>
-  <si>
-    <t>135206509</t>
-  </si>
-  <si>
-    <t>135110556</t>
-  </si>
-  <si>
-    <t>130183860</t>
-  </si>
-  <si>
-    <t>130351949</t>
-  </si>
-  <si>
-    <t>135278803</t>
-  </si>
-  <si>
-    <t>135007116</t>
-  </si>
-  <si>
-    <t>135198264</t>
-  </si>
-  <si>
-    <t>135207436</t>
-  </si>
-  <si>
-    <t>135100560</t>
-  </si>
-  <si>
-    <t>135191534</t>
-  </si>
-  <si>
-    <t>135172778</t>
-  </si>
-  <si>
-    <t>135100709</t>
-  </si>
-  <si>
-    <t>134921983</t>
-  </si>
-  <si>
     <t>135113084</t>
   </si>
   <si>
-    <t>134696293</t>
-  </si>
-  <si>
-    <t>135280071</t>
-  </si>
-  <si>
-    <t>135168660</t>
-  </si>
-  <si>
-    <t>130230489</t>
-  </si>
-  <si>
-    <t>135003607</t>
-  </si>
-  <si>
-    <t>130187440</t>
-  </si>
-  <si>
-    <t>135106930</t>
-  </si>
-  <si>
-    <t>130226433</t>
-  </si>
-  <si>
-    <t>135164609</t>
-  </si>
-  <si>
-    <t>135219941</t>
-  </si>
-  <si>
-    <t>130279427</t>
-  </si>
-  <si>
-    <t>130368183</t>
-  </si>
-  <si>
-    <t>135134233</t>
-  </si>
-  <si>
-    <t>135131988</t>
-  </si>
-  <si>
-    <t>135239617</t>
-  </si>
-  <si>
-    <t>130314880</t>
-  </si>
-  <si>
-    <t>135061246</t>
-  </si>
-  <si>
-    <t>135206403</t>
-  </si>
-  <si>
-    <t>135207104</t>
-  </si>
-  <si>
-    <t>130059903</t>
-  </si>
-  <si>
-    <t>135252883</t>
-  </si>
-  <si>
-    <t>130386928</t>
-  </si>
-  <si>
-    <t>135227889</t>
-  </si>
-  <si>
-    <t>135109385</t>
-  </si>
-  <si>
-    <t>130140873</t>
-  </si>
-  <si>
-    <t>130189168</t>
-  </si>
-  <si>
-    <t>135245695</t>
-  </si>
-  <si>
-    <t>135185493</t>
-  </si>
-  <si>
-    <t>135154633</t>
-  </si>
-  <si>
-    <t>130256226</t>
-  </si>
-  <si>
-    <t>130195297</t>
-  </si>
-  <si>
-    <t>135003877</t>
-  </si>
-  <si>
-    <t>135095194</t>
-  </si>
-  <si>
-    <t>135106866</t>
-  </si>
-  <si>
-    <t>130435730</t>
-  </si>
-  <si>
-    <t>135260735</t>
-  </si>
-  <si>
-    <t>135262875</t>
-  </si>
-  <si>
-    <t>135175444</t>
-  </si>
-  <si>
-    <t>135002578</t>
-  </si>
-  <si>
-    <t>135250083</t>
-  </si>
-  <si>
-    <t>135243275</t>
-  </si>
-  <si>
-    <t>135211786</t>
-  </si>
-  <si>
-    <t>132463969</t>
-  </si>
-  <si>
-    <t>135276240</t>
-  </si>
-  <si>
-    <t>135104022</t>
-  </si>
-  <si>
-    <t>135206542</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
+    <t>135005304</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 07.11.2025</t>
+  </si>
+  <si>
+    <t>135134039</t>
+  </si>
+  <si>
+    <t>135104395</t>
+  </si>
+  <si>
+    <t>135106780</t>
+  </si>
+  <si>
+    <t>132709629</t>
+  </si>
+  <si>
+    <t>135214919</t>
+  </si>
+  <si>
+    <t>135263909</t>
+  </si>
+  <si>
+    <t>135100852</t>
+  </si>
+  <si>
+    <t>135255016</t>
+  </si>
+  <si>
+    <t>135174307</t>
+  </si>
+  <si>
+    <t>135174690</t>
+  </si>
+  <si>
+    <t>135061806</t>
+  </si>
+  <si>
+    <t>135010908</t>
+  </si>
+  <si>
+    <t>130038587</t>
+  </si>
+  <si>
+    <t>135003297</t>
+  </si>
+  <si>
+    <t>135232801</t>
+  </si>
+  <si>
+    <t>135172614</t>
+  </si>
+  <si>
+    <t>135149275</t>
+  </si>
+  <si>
+    <t>130210180</t>
+  </si>
+  <si>
+    <t>135253679</t>
+  </si>
+  <si>
+    <t>135288060</t>
+  </si>
+  <si>
+    <t>135147776</t>
+  </si>
+  <si>
+    <t>135172829</t>
+  </si>
+  <si>
+    <t>134004285</t>
+  </si>
+  <si>
+    <t>135176570</t>
+  </si>
+  <si>
+    <t>133885245</t>
+  </si>
+  <si>
+    <t>135034572</t>
+  </si>
+  <si>
+    <t>135275756</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 07.11.2025</t>
   </si>
 </sst>
 </file>
@@ -642,7 +540,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -683,7 +581,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -701,7 +599,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -719,7 +617,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -737,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -755,7 +653,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -773,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -791,7 +689,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -809,7 +707,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -827,7 +725,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -845,7 +743,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -863,7 +761,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -881,7 +779,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -899,7 +797,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -917,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -935,7 +833,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -953,7 +851,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -971,7 +869,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -989,7 +887,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -998,7 +896,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -1007,7 +905,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1016,7 +914,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -1025,7 +923,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1034,7 +932,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -1043,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1052,7 +950,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -1061,7 +959,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1070,7 +968,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1079,7 +977,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1088,7 +986,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1097,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1004,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1115,7 +1013,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1067,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1187,612 +1085,12 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1808,31 +1106,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15EBD7E-AF1A-4542-B27B-1531AD35A59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6578B0A-94B8-462D-84CA-DA5FC1C83335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,97 +54,127 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135113084</t>
-  </si>
-  <si>
-    <t>135005304</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 07.11.2025</t>
-  </si>
-  <si>
-    <t>135134039</t>
-  </si>
-  <si>
-    <t>135104395</t>
-  </si>
-  <si>
-    <t>135106780</t>
-  </si>
-  <si>
-    <t>132709629</t>
-  </si>
-  <si>
-    <t>135214919</t>
-  </si>
-  <si>
-    <t>135263909</t>
-  </si>
-  <si>
-    <t>135100852</t>
-  </si>
-  <si>
-    <t>135255016</t>
-  </si>
-  <si>
-    <t>135174307</t>
-  </si>
-  <si>
-    <t>135174690</t>
-  </si>
-  <si>
-    <t>135061806</t>
-  </si>
-  <si>
-    <t>135010908</t>
-  </si>
-  <si>
-    <t>130038587</t>
-  </si>
-  <si>
-    <t>135003297</t>
-  </si>
-  <si>
-    <t>135232801</t>
-  </si>
-  <si>
-    <t>135172614</t>
-  </si>
-  <si>
-    <t>135149275</t>
-  </si>
-  <si>
-    <t>130210180</t>
-  </si>
-  <si>
-    <t>135253679</t>
-  </si>
-  <si>
-    <t>135288060</t>
-  </si>
-  <si>
-    <t>135147776</t>
-  </si>
-  <si>
-    <t>135172829</t>
-  </si>
-  <si>
-    <t>134004285</t>
-  </si>
-  <si>
-    <t>135176570</t>
-  </si>
-  <si>
-    <t>133885245</t>
-  </si>
-  <si>
-    <t>135034572</t>
-  </si>
-  <si>
-    <t>135275756</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 07.11.2025</t>
+    <t>135173286</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 10.11.2025</t>
+  </si>
+  <si>
+    <t>135202300</t>
+  </si>
+  <si>
+    <t>134902573</t>
+  </si>
+  <si>
+    <t>134551950</t>
+  </si>
+  <si>
+    <t>135106619</t>
+  </si>
+  <si>
+    <t>135003780</t>
+  </si>
+  <si>
+    <t>135107382</t>
+  </si>
+  <si>
+    <t>135250713</t>
+  </si>
+  <si>
+    <t>135095657</t>
+  </si>
+  <si>
+    <t>135104411</t>
+  </si>
+  <si>
+    <t>130454760</t>
+  </si>
+  <si>
+    <t>130496488</t>
+  </si>
+  <si>
+    <t>135188014</t>
+  </si>
+  <si>
+    <t>130437390</t>
+  </si>
+  <si>
+    <t>135097592</t>
+  </si>
+  <si>
+    <t>130341176</t>
+  </si>
+  <si>
+    <t>135174990</t>
+  </si>
+  <si>
+    <t>135146657</t>
+  </si>
+  <si>
+    <t>135103891</t>
+  </si>
+  <si>
+    <t>135003761</t>
+  </si>
+  <si>
+    <t>135198652</t>
+  </si>
+  <si>
+    <t>135276660</t>
+  </si>
+  <si>
+    <t>135202267</t>
+  </si>
+  <si>
+    <t>130416221</t>
+  </si>
+  <si>
+    <t>130429370</t>
+  </si>
+  <si>
+    <t>135278219</t>
+  </si>
+  <si>
+    <t>134916455</t>
+  </si>
+  <si>
+    <t>135223855</t>
+  </si>
+  <si>
+    <t>135106918</t>
+  </si>
+  <si>
+    <t>135214185</t>
+  </si>
+  <si>
+    <t>135206532</t>
+  </si>
+  <si>
+    <t>135101464</t>
+  </si>
+  <si>
+    <t>135276973</t>
+  </si>
+  <si>
+    <t>135169071</t>
+  </si>
+  <si>
+    <t>130475177</t>
+  </si>
+  <si>
+    <t>135146603</t>
+  </si>
+  <si>
+    <t>135206394</t>
+  </si>
+  <si>
+    <t>131471237</t>
+  </si>
+  <si>
+    <t>135296616</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 10.11.2025</t>
   </si>
 </sst>
 </file>
@@ -540,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,16 +602,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,16 +620,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,16 +638,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,16 +656,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,16 +674,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,16 +692,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,16 +710,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,16 +728,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,16 +746,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -734,16 +764,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,16 +782,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -770,16 +800,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,16 +818,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -806,16 +836,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -824,16 +854,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -842,16 +872,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -860,16 +890,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,16 +908,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,16 +926,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -914,16 +944,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -932,16 +962,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -950,16 +980,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -968,16 +998,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -986,16 +1016,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1034,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1028,10 +1058,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1046,10 +1076,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1064,10 +1094,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1082,15 +1112,185 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30"/>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1106,31 +1306,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6578B0A-94B8-462D-84CA-DA5FC1C83335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C8575F-CD23-4DB7-993F-9AF22ADD2B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,100 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135173286</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 10.11.2025</t>
-  </si>
-  <si>
-    <t>135202300</t>
-  </si>
-  <si>
-    <t>134902573</t>
-  </si>
-  <si>
-    <t>134551950</t>
-  </si>
-  <si>
-    <t>135106619</t>
-  </si>
-  <si>
-    <t>135003780</t>
-  </si>
-  <si>
-    <t>135107382</t>
-  </si>
-  <si>
-    <t>135250713</t>
-  </si>
-  <si>
-    <t>135095657</t>
-  </si>
-  <si>
-    <t>135104411</t>
-  </si>
-  <si>
-    <t>130454760</t>
-  </si>
-  <si>
-    <t>130496488</t>
-  </si>
-  <si>
-    <t>135188014</t>
-  </si>
-  <si>
-    <t>130437390</t>
-  </si>
-  <si>
-    <t>135097592</t>
-  </si>
-  <si>
-    <t>130341176</t>
-  </si>
-  <si>
-    <t>135174990</t>
-  </si>
-  <si>
-    <t>135146657</t>
-  </si>
-  <si>
-    <t>135103891</t>
-  </si>
-  <si>
-    <t>135003761</t>
-  </si>
-  <si>
-    <t>135198652</t>
-  </si>
-  <si>
-    <t>135276660</t>
-  </si>
-  <si>
-    <t>135202267</t>
-  </si>
-  <si>
-    <t>130416221</t>
-  </si>
-  <si>
-    <t>130429370</t>
-  </si>
-  <si>
-    <t>135278219</t>
-  </si>
-  <si>
-    <t>134916455</t>
-  </si>
-  <si>
-    <t>135223855</t>
-  </si>
-  <si>
-    <t>135106918</t>
-  </si>
-  <si>
-    <t>135214185</t>
-  </si>
-  <si>
-    <t>135206532</t>
-  </si>
-  <si>
-    <t>135101464</t>
-  </si>
-  <si>
-    <t>135276973</t>
-  </si>
-  <si>
-    <t>135169071</t>
-  </si>
-  <si>
-    <t>130475177</t>
-  </si>
-  <si>
-    <t>135146603</t>
-  </si>
-  <si>
-    <t>135206394</t>
-  </si>
-  <si>
-    <t>131471237</t>
-  </si>
-  <si>
-    <t>135296616</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 10.11.2025</t>
+    <t>130093249</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 11.11.2025</t>
+  </si>
+  <si>
+    <t>130162348</t>
+  </si>
+  <si>
+    <t>135296932</t>
+  </si>
+  <si>
+    <t>130506204</t>
+  </si>
+  <si>
+    <t>130266599</t>
+  </si>
+  <si>
+    <t>135278746</t>
+  </si>
+  <si>
+    <t>129972349</t>
+  </si>
+  <si>
+    <t>130230978</t>
+  </si>
+  <si>
+    <t>130218717</t>
+  </si>
+  <si>
+    <t>135091932</t>
+  </si>
+  <si>
+    <t>135057951</t>
+  </si>
+  <si>
+    <t>135004122</t>
+  </si>
+  <si>
+    <t>135308948</t>
+  </si>
+  <si>
+    <t>135148850</t>
+  </si>
+  <si>
+    <t>135276765</t>
+  </si>
+  <si>
+    <t>134931966</t>
+  </si>
+  <si>
+    <t>135201182</t>
+  </si>
+  <si>
+    <t>130187316</t>
+  </si>
+  <si>
+    <t>134853444</t>
+  </si>
+  <si>
+    <t>135284850</t>
+  </si>
+  <si>
+    <t>130308297</t>
+  </si>
+  <si>
+    <t>130151010</t>
+  </si>
+  <si>
+    <t>135209958</t>
+  </si>
+  <si>
+    <t>135092708</t>
+  </si>
+  <si>
+    <t>135177127</t>
+  </si>
+  <si>
+    <t>134789238</t>
+  </si>
+  <si>
+    <t>134838353</t>
+  </si>
+  <si>
+    <t>134911926</t>
+  </si>
+  <si>
+    <t>135088398</t>
+  </si>
+  <si>
+    <t>135060657</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 11.11.2025</t>
   </si>
 </sst>
 </file>
@@ -570,7 +543,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -611,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -629,7 +602,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -647,7 +620,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -683,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -701,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -719,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -737,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -755,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -773,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -791,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -809,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -827,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -845,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -863,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -881,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -899,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -917,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -935,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -953,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -971,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -989,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1007,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1025,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1025,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1061,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1043,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1079,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1061,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1097,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1079,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1115,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1097,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1133,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1141,7 +1114,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1150,145 +1123,9 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1306,31 +1143,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C8575F-CD23-4DB7-993F-9AF22ADD2B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4A7889-56B9-4540-B511-FC032F03318E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="65">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,100 +54,175 @@
     <t>1070</t>
   </si>
   <si>
-    <t>130093249</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 11.11.2025</t>
-  </si>
-  <si>
-    <t>130162348</t>
-  </si>
-  <si>
-    <t>135296932</t>
-  </si>
-  <si>
-    <t>130506204</t>
-  </si>
-  <si>
-    <t>130266599</t>
-  </si>
-  <si>
-    <t>135278746</t>
-  </si>
-  <si>
-    <t>129972349</t>
-  </si>
-  <si>
-    <t>130230978</t>
-  </si>
-  <si>
-    <t>130218717</t>
-  </si>
-  <si>
-    <t>135091932</t>
-  </si>
-  <si>
-    <t>135057951</t>
-  </si>
-  <si>
-    <t>135004122</t>
-  </si>
-  <si>
-    <t>135308948</t>
-  </si>
-  <si>
-    <t>135148850</t>
-  </si>
-  <si>
-    <t>135276765</t>
-  </si>
-  <si>
-    <t>134931966</t>
-  </si>
-  <si>
-    <t>135201182</t>
-  </si>
-  <si>
-    <t>130187316</t>
-  </si>
-  <si>
-    <t>134853444</t>
-  </si>
-  <si>
-    <t>135284850</t>
-  </si>
-  <si>
-    <t>130308297</t>
-  </si>
-  <si>
-    <t>130151010</t>
-  </si>
-  <si>
-    <t>135209958</t>
-  </si>
-  <si>
-    <t>135092708</t>
-  </si>
-  <si>
-    <t>135177127</t>
-  </si>
-  <si>
-    <t>134789238</t>
-  </si>
-  <si>
-    <t>134838353</t>
-  </si>
-  <si>
-    <t>134911926</t>
-  </si>
-  <si>
-    <t>135088398</t>
-  </si>
-  <si>
-    <t>135060657</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 11.11.2025</t>
+    <t>135106927</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 12.11.2025</t>
+  </si>
+  <si>
+    <t>135275609</t>
+  </si>
+  <si>
+    <t>135106800</t>
+  </si>
+  <si>
+    <t>130039103</t>
+  </si>
+  <si>
+    <t>134674271</t>
+  </si>
+  <si>
+    <t>130299662</t>
+  </si>
+  <si>
+    <t>130440125</t>
+  </si>
+  <si>
+    <t>130496267</t>
+  </si>
+  <si>
+    <t>135106693</t>
+  </si>
+  <si>
+    <t>130519502</t>
+  </si>
+  <si>
+    <t>135254648</t>
+  </si>
+  <si>
+    <t>130257460</t>
+  </si>
+  <si>
+    <t>130301072</t>
+  </si>
+  <si>
+    <t>130483354</t>
+  </si>
+  <si>
+    <t>135249107</t>
+  </si>
+  <si>
+    <t>130137022</t>
+  </si>
+  <si>
+    <t>135172999</t>
+  </si>
+  <si>
+    <t>135106798</t>
+  </si>
+  <si>
+    <t>135316201</t>
+  </si>
+  <si>
+    <t>135283793</t>
+  </si>
+  <si>
+    <t>135106733</t>
+  </si>
+  <si>
+    <t>135315202</t>
+  </si>
+  <si>
+    <t>135003634</t>
+  </si>
+  <si>
+    <t>135150122</t>
+  </si>
+  <si>
+    <t>133894971</t>
+  </si>
+  <si>
+    <t>135314929</t>
+  </si>
+  <si>
+    <t>135106664</t>
+  </si>
+  <si>
+    <t>135276045</t>
+  </si>
+  <si>
+    <t>135106764</t>
+  </si>
+  <si>
+    <t>135241970</t>
+  </si>
+  <si>
+    <t>130528906</t>
+  </si>
+  <si>
+    <t>135106657</t>
+  </si>
+  <si>
+    <t>135247258</t>
+  </si>
+  <si>
+    <t>135323276</t>
+  </si>
+  <si>
+    <t>135126656</t>
+  </si>
+  <si>
+    <t>134682853</t>
+  </si>
+  <si>
+    <t>135315252</t>
+  </si>
+  <si>
+    <t>135342217</t>
+  </si>
+  <si>
+    <t>135106914</t>
+  </si>
+  <si>
+    <t>130249166</t>
+  </si>
+  <si>
+    <t>135126443</t>
+  </si>
+  <si>
+    <t>130186870</t>
+  </si>
+  <si>
+    <t>130516039</t>
+  </si>
+  <si>
+    <t>135096379</t>
+  </si>
+  <si>
+    <t>130297031</t>
+  </si>
+  <si>
+    <t>130452353</t>
+  </si>
+  <si>
+    <t>130239065</t>
+  </si>
+  <si>
+    <t>135324817</t>
+  </si>
+  <si>
+    <t>135179390</t>
+  </si>
+  <si>
+    <t>135216762</t>
+  </si>
+  <si>
+    <t>134606047</t>
+  </si>
+  <si>
+    <t>135003969</t>
+  </si>
+  <si>
+    <t>135273993</t>
+  </si>
+  <si>
+    <t>135227730</t>
+  </si>
+  <si>
+    <t>132436317</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 12.11.2025</t>
   </si>
 </sst>
 </file>
@@ -543,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,7 +659,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -602,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -620,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -638,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -656,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -674,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -692,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -710,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -728,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -746,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -764,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -782,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -800,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -818,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -836,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -854,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -872,7 +947,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -890,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -926,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -944,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -980,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -998,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1025,7 +1100,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1034,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1118,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1052,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1136,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1070,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1079,7 +1154,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1088,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1172,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1106,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1114,7 +1189,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1123,9 +1198,417 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1143,31 +1626,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4A7889-56B9-4540-B511-FC032F03318E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC9D894-A5FB-4DA8-B504-60C329363AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25815" yWindow="1800" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="61">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,175 +54,163 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135106927</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 12.11.2025</t>
-  </si>
-  <si>
-    <t>135275609</t>
-  </si>
-  <si>
-    <t>135106800</t>
-  </si>
-  <si>
-    <t>130039103</t>
-  </si>
-  <si>
-    <t>134674271</t>
-  </si>
-  <si>
-    <t>130299662</t>
-  </si>
-  <si>
-    <t>130440125</t>
-  </si>
-  <si>
-    <t>130496267</t>
-  </si>
-  <si>
-    <t>135106693</t>
-  </si>
-  <si>
-    <t>130519502</t>
-  </si>
-  <si>
-    <t>135254648</t>
-  </si>
-  <si>
-    <t>130257460</t>
-  </si>
-  <si>
-    <t>130301072</t>
-  </si>
-  <si>
-    <t>130483354</t>
-  </si>
-  <si>
-    <t>135249107</t>
-  </si>
-  <si>
-    <t>130137022</t>
-  </si>
-  <si>
-    <t>135172999</t>
-  </si>
-  <si>
-    <t>135106798</t>
-  </si>
-  <si>
-    <t>135316201</t>
-  </si>
-  <si>
-    <t>135283793</t>
-  </si>
-  <si>
-    <t>135106733</t>
-  </si>
-  <si>
-    <t>135315202</t>
-  </si>
-  <si>
-    <t>135003634</t>
-  </si>
-  <si>
-    <t>135150122</t>
-  </si>
-  <si>
-    <t>133894971</t>
-  </si>
-  <si>
-    <t>135314929</t>
-  </si>
-  <si>
-    <t>135106664</t>
-  </si>
-  <si>
-    <t>135276045</t>
-  </si>
-  <si>
-    <t>135106764</t>
-  </si>
-  <si>
-    <t>135241970</t>
-  </si>
-  <si>
-    <t>130528906</t>
-  </si>
-  <si>
-    <t>135106657</t>
-  </si>
-  <si>
-    <t>135247258</t>
-  </si>
-  <si>
-    <t>135323276</t>
-  </si>
-  <si>
-    <t>135126656</t>
-  </si>
-  <si>
-    <t>134682853</t>
-  </si>
-  <si>
-    <t>135315252</t>
-  </si>
-  <si>
-    <t>135342217</t>
-  </si>
-  <si>
-    <t>135106914</t>
-  </si>
-  <si>
-    <t>130249166</t>
-  </si>
-  <si>
-    <t>135126443</t>
-  </si>
-  <si>
-    <t>130186870</t>
-  </si>
-  <si>
-    <t>130516039</t>
-  </si>
-  <si>
-    <t>135096379</t>
-  </si>
-  <si>
-    <t>130297031</t>
-  </si>
-  <si>
-    <t>130452353</t>
-  </si>
-  <si>
-    <t>130239065</t>
-  </si>
-  <si>
-    <t>135324817</t>
-  </si>
-  <si>
-    <t>135179390</t>
-  </si>
-  <si>
-    <t>135216762</t>
-  </si>
-  <si>
-    <t>134606047</t>
-  </si>
-  <si>
-    <t>135003969</t>
-  </si>
-  <si>
-    <t>135273993</t>
-  </si>
-  <si>
-    <t>135227730</t>
-  </si>
-  <si>
-    <t>132436317</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 12.11.2025</t>
+    <t>130126005</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 14.11.2025</t>
+  </si>
+  <si>
+    <t>135118152</t>
+  </si>
+  <si>
+    <t>130523406</t>
+  </si>
+  <si>
+    <t>130093249</t>
+  </si>
+  <si>
+    <t>135207913</t>
+  </si>
+  <si>
+    <t>135212837</t>
+  </si>
+  <si>
+    <t>135276306</t>
+  </si>
+  <si>
+    <t>135321337</t>
+  </si>
+  <si>
+    <t>134721677</t>
+  </si>
+  <si>
+    <t>135112142</t>
+  </si>
+  <si>
+    <t>135276828</t>
+  </si>
+  <si>
+    <t>130182329</t>
+  </si>
+  <si>
+    <t>135315181</t>
+  </si>
+  <si>
+    <t>135216388</t>
+  </si>
+  <si>
+    <t>130117333</t>
+  </si>
+  <si>
+    <t>130727395</t>
+  </si>
+  <si>
+    <t>130272939</t>
+  </si>
+  <si>
+    <t>130157487</t>
+  </si>
+  <si>
+    <t>135315064</t>
+  </si>
+  <si>
+    <t>135376213</t>
+  </si>
+  <si>
+    <t>130390797</t>
+  </si>
+  <si>
+    <t>130398863</t>
+  </si>
+  <si>
+    <t>130230666</t>
+  </si>
+  <si>
+    <t>130252183</t>
+  </si>
+  <si>
+    <t>135365909</t>
+  </si>
+  <si>
+    <t>133217523</t>
+  </si>
+  <si>
+    <t>135206512</t>
+  </si>
+  <si>
+    <t>130368253</t>
+  </si>
+  <si>
+    <t>135315067</t>
+  </si>
+  <si>
+    <t>135207056</t>
+  </si>
+  <si>
+    <t>135126428</t>
+  </si>
+  <si>
+    <t>130331828</t>
+  </si>
+  <si>
+    <t>130348931</t>
+  </si>
+  <si>
+    <t>135275749</t>
+  </si>
+  <si>
+    <t>135335616</t>
+  </si>
+  <si>
+    <t>135366184</t>
+  </si>
+  <si>
+    <t>130414098</t>
+  </si>
+  <si>
+    <t>135173765</t>
+  </si>
+  <si>
+    <t>134443064</t>
+  </si>
+  <si>
+    <t>135316136</t>
+  </si>
+  <si>
+    <t>130343396</t>
+  </si>
+  <si>
+    <t>135133798</t>
+  </si>
+  <si>
+    <t>135359705</t>
+  </si>
+  <si>
+    <t>135110118</t>
+  </si>
+  <si>
+    <t>135335976</t>
+  </si>
+  <si>
+    <t>133727625</t>
+  </si>
+  <si>
+    <t>133670747</t>
+  </si>
+  <si>
+    <t>135348899</t>
+  </si>
+  <si>
+    <t>135171883</t>
+  </si>
+  <si>
+    <t>135362890</t>
+  </si>
+  <si>
+    <t>135369940</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 14.11.2025</t>
   </si>
 </sst>
 </file>
@@ -618,7 +606,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -659,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -677,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -695,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -713,7 +701,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -731,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -749,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -767,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -785,7 +773,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -803,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -821,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -839,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -857,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -875,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -893,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -911,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -929,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -947,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -965,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -983,7 +971,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1001,7 +989,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1019,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1025,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1097,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1133,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1151,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1198,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1215,7 +1203,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1223,7 +1211,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1232,7 +1220,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1240,7 +1228,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1249,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1257,7 +1245,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1266,7 +1254,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1274,7 +1262,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1283,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1291,7 +1279,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1300,7 +1288,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1308,7 +1296,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1317,7 +1305,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1325,7 +1313,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1334,7 +1322,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1342,7 +1330,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -1351,7 +1339,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1359,7 +1347,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
@@ -1368,7 +1356,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1376,7 +1364,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -1385,7 +1373,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1393,7 +1381,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
@@ -1402,7 +1390,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1410,7 +1398,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
@@ -1419,7 +1407,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1427,7 +1415,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
@@ -1436,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1444,7 +1432,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
@@ -1453,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1461,7 +1449,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
@@ -1470,7 +1458,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1478,7 +1466,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
@@ -1487,7 +1475,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1495,7 +1483,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
@@ -1504,7 +1492,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1512,7 +1500,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
@@ -1521,7 +1509,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1529,7 +1517,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
@@ -1538,7 +1526,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1546,7 +1534,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
@@ -1555,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1563,7 +1551,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
@@ -1572,43 +1560,9 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1626,31 +1580,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC9D894-A5FB-4DA8-B504-60C329363AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EE47BE-8327-4C9C-84A8-E43539E97F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25815" yWindow="1800" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,163 +54,145 @@
     <t>1070</t>
   </si>
   <si>
-    <t>130126005</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 14.11.2025</t>
-  </si>
-  <si>
-    <t>135118152</t>
-  </si>
-  <si>
-    <t>130523406</t>
-  </si>
-  <si>
-    <t>130093249</t>
-  </si>
-  <si>
-    <t>135207913</t>
-  </si>
-  <si>
-    <t>135212837</t>
-  </si>
-  <si>
-    <t>135276306</t>
-  </si>
-  <si>
-    <t>135321337</t>
-  </si>
-  <si>
     <t>134721677</t>
   </si>
   <si>
-    <t>135112142</t>
-  </si>
-  <si>
-    <t>135276828</t>
-  </si>
-  <si>
-    <t>130182329</t>
-  </si>
-  <si>
     <t>135315181</t>
   </si>
   <si>
-    <t>135216388</t>
-  </si>
-  <si>
-    <t>130117333</t>
-  </si>
-  <si>
-    <t>130727395</t>
-  </si>
-  <si>
-    <t>130272939</t>
-  </si>
-  <si>
-    <t>130157487</t>
-  </si>
-  <si>
-    <t>135315064</t>
-  </si>
-  <si>
-    <t>135376213</t>
-  </si>
-  <si>
-    <t>130390797</t>
-  </si>
-  <si>
-    <t>130398863</t>
-  </si>
-  <si>
-    <t>130230666</t>
-  </si>
-  <si>
-    <t>130252183</t>
-  </si>
-  <si>
-    <t>135365909</t>
-  </si>
-  <si>
-    <t>133217523</t>
-  </si>
-  <si>
-    <t>135206512</t>
-  </si>
-  <si>
-    <t>130368253</t>
-  </si>
-  <si>
-    <t>135315067</t>
-  </si>
-  <si>
-    <t>135207056</t>
-  </si>
-  <si>
-    <t>135126428</t>
-  </si>
-  <si>
-    <t>130331828</t>
-  </si>
-  <si>
-    <t>130348931</t>
-  </si>
-  <si>
-    <t>135275749</t>
-  </si>
-  <si>
-    <t>135335616</t>
-  </si>
-  <si>
-    <t>135366184</t>
-  </si>
-  <si>
-    <t>130414098</t>
-  </si>
-  <si>
-    <t>135173765</t>
-  </si>
-  <si>
-    <t>134443064</t>
-  </si>
-  <si>
-    <t>135316136</t>
-  </si>
-  <si>
-    <t>130343396</t>
-  </si>
-  <si>
-    <t>135133798</t>
-  </si>
-  <si>
-    <t>135359705</t>
-  </si>
-  <si>
-    <t>135110118</t>
-  </si>
-  <si>
-    <t>135335976</t>
-  </si>
-  <si>
-    <t>133727625</t>
-  </si>
-  <si>
-    <t>133670747</t>
-  </si>
-  <si>
-    <t>135348899</t>
-  </si>
-  <si>
-    <t>135171883</t>
-  </si>
-  <si>
-    <t>135362890</t>
-  </si>
-  <si>
-    <t>135369940</t>
-  </si>
-  <si>
     <t>Allianz - Cancelamento 14.11.2025</t>
+  </si>
+  <si>
+    <t>135279960</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 17.11.2025</t>
+  </si>
+  <si>
+    <t>135315141</t>
+  </si>
+  <si>
+    <t>130149941</t>
+  </si>
+  <si>
+    <t>130339680</t>
+  </si>
+  <si>
+    <t>135206364</t>
+  </si>
+  <si>
+    <t>135384749</t>
+  </si>
+  <si>
+    <t>135380568</t>
+  </si>
+  <si>
+    <t>135287057</t>
+  </si>
+  <si>
+    <t>135314872</t>
+  </si>
+  <si>
+    <t>135005990</t>
+  </si>
+  <si>
+    <t>135153668</t>
+  </si>
+  <si>
+    <t>135379757</t>
+  </si>
+  <si>
+    <t>130229358</t>
+  </si>
+  <si>
+    <t>135252585</t>
+  </si>
+  <si>
+    <t>135277136</t>
+  </si>
+  <si>
+    <t>130454881</t>
+  </si>
+  <si>
+    <t>135396897</t>
+  </si>
+  <si>
+    <t>135400496</t>
+  </si>
+  <si>
+    <t>135182290</t>
+  </si>
+  <si>
+    <t>130483844</t>
+  </si>
+  <si>
+    <t>130534660</t>
+  </si>
+  <si>
+    <t>134442567</t>
+  </si>
+  <si>
+    <t>130532847</t>
+  </si>
+  <si>
+    <t>130238811</t>
+  </si>
+  <si>
+    <t>130434851</t>
+  </si>
+  <si>
+    <t>130559004</t>
+  </si>
+  <si>
+    <t>135302866</t>
+  </si>
+  <si>
+    <t>130432309</t>
+  </si>
+  <si>
+    <t>130275112</t>
+  </si>
+  <si>
+    <t>135310871</t>
+  </si>
+  <si>
+    <t>132203973</t>
+  </si>
+  <si>
+    <t>130272161</t>
+  </si>
+  <si>
+    <t>135276369</t>
+  </si>
+  <si>
+    <t>130504874</t>
+  </si>
+  <si>
+    <t>135315688</t>
+  </si>
+  <si>
+    <t>130493027</t>
+  </si>
+  <si>
+    <t>135206574</t>
+  </si>
+  <si>
+    <t>135108831</t>
+  </si>
+  <si>
+    <t>135253974</t>
+  </si>
+  <si>
+    <t>135298767</t>
+  </si>
+  <si>
+    <t>131146738</t>
+  </si>
+  <si>
+    <t>135335661</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 17.11.2025</t>
   </si>
 </sst>
 </file>
@@ -606,7 +588,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -638,16 +620,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -656,16 +638,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -674,16 +656,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -692,16 +674,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -710,16 +692,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -728,16 +710,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -746,16 +728,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -764,16 +746,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -782,16 +764,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -800,16 +782,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -818,16 +800,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -836,16 +818,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -854,16 +836,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -872,16 +854,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -890,16 +872,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -908,16 +890,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -926,16 +908,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -944,16 +926,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -962,16 +944,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -980,16 +962,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -998,16 +980,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1016,16 +998,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1034,16 +1016,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1052,16 +1034,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1070,16 +1052,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1088,16 +1070,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1106,16 +1088,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1106,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1142,16 +1124,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1160,16 +1142,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1177,16 +1159,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1194,16 +1176,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1211,16 +1193,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1228,16 +1210,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1245,16 +1227,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1262,16 +1244,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1279,16 +1261,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1296,16 +1278,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1313,16 +1295,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1330,16 +1312,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1347,16 +1329,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1364,16 +1346,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1381,16 +1363,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1398,16 +1380,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1415,154 +1397,18 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1580,31 +1426,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EE47BE-8327-4C9C-84A8-E43539E97F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF97CF9D-5022-4011-88DE-3F7407A45BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,145 +54,106 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134721677</t>
-  </si>
-  <si>
-    <t>135315181</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 14.11.2025</t>
-  </si>
-  <si>
-    <t>135279960</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 17.11.2025</t>
-  </si>
-  <si>
-    <t>135315141</t>
-  </si>
-  <si>
-    <t>130149941</t>
-  </si>
-  <si>
-    <t>130339680</t>
-  </si>
-  <si>
-    <t>135206364</t>
-  </si>
-  <si>
-    <t>135384749</t>
-  </si>
-  <si>
-    <t>135380568</t>
-  </si>
-  <si>
-    <t>135287057</t>
-  </si>
-  <si>
-    <t>135314872</t>
-  </si>
-  <si>
-    <t>135005990</t>
-  </si>
-  <si>
-    <t>135153668</t>
-  </si>
-  <si>
-    <t>135379757</t>
-  </si>
-  <si>
-    <t>130229358</t>
-  </si>
-  <si>
-    <t>135252585</t>
-  </si>
-  <si>
-    <t>135277136</t>
-  </si>
-  <si>
-    <t>130454881</t>
-  </si>
-  <si>
-    <t>135396897</t>
-  </si>
-  <si>
-    <t>135400496</t>
-  </si>
-  <si>
-    <t>135182290</t>
-  </si>
-  <si>
-    <t>130483844</t>
-  </si>
-  <si>
-    <t>130534660</t>
-  </si>
-  <si>
-    <t>134442567</t>
-  </si>
-  <si>
-    <t>130532847</t>
-  </si>
-  <si>
-    <t>130238811</t>
-  </si>
-  <si>
-    <t>130434851</t>
-  </si>
-  <si>
-    <t>130559004</t>
-  </si>
-  <si>
-    <t>135302866</t>
-  </si>
-  <si>
-    <t>130432309</t>
-  </si>
-  <si>
-    <t>130275112</t>
-  </si>
-  <si>
-    <t>135310871</t>
-  </si>
-  <si>
-    <t>132203973</t>
-  </si>
-  <si>
-    <t>130272161</t>
-  </si>
-  <si>
-    <t>135276369</t>
-  </si>
-  <si>
-    <t>130504874</t>
-  </si>
-  <si>
-    <t>135315688</t>
-  </si>
-  <si>
-    <t>130493027</t>
-  </si>
-  <si>
-    <t>135206574</t>
-  </si>
-  <si>
-    <t>135108831</t>
-  </si>
-  <si>
-    <t>135253974</t>
-  </si>
-  <si>
-    <t>135298767</t>
-  </si>
-  <si>
-    <t>131146738</t>
-  </si>
-  <si>
-    <t>135335661</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 17.11.2025</t>
+    <t>135297311</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 18.11.2025</t>
+  </si>
+  <si>
+    <t>135151570</t>
+  </si>
+  <si>
+    <t>135359719</t>
+  </si>
+  <si>
+    <t>130248029</t>
+  </si>
+  <si>
+    <t>135271039</t>
+  </si>
+  <si>
+    <t>135146615</t>
+  </si>
+  <si>
+    <t>130601615</t>
+  </si>
+  <si>
+    <t>135227162</t>
+  </si>
+  <si>
+    <t>130360076</t>
+  </si>
+  <si>
+    <t>130579919</t>
+  </si>
+  <si>
+    <t>130239541</t>
+  </si>
+  <si>
+    <t>130522108</t>
+  </si>
+  <si>
+    <t>135314980</t>
+  </si>
+  <si>
+    <t>135287373</t>
+  </si>
+  <si>
+    <t>135394963</t>
+  </si>
+  <si>
+    <t>135309543</t>
+  </si>
+  <si>
+    <t>135315035</t>
+  </si>
+  <si>
+    <t>135287307</t>
+  </si>
+  <si>
+    <t>135048792</t>
+  </si>
+  <si>
+    <t>130501576</t>
+  </si>
+  <si>
+    <t>135174613</t>
+  </si>
+  <si>
+    <t>130272418</t>
+  </si>
+  <si>
+    <t>135342282</t>
+  </si>
+  <si>
+    <t>135328296</t>
+  </si>
+  <si>
+    <t>135173264</t>
+  </si>
+  <si>
+    <t>130375992</t>
+  </si>
+  <si>
+    <t>135402156</t>
+  </si>
+  <si>
+    <t>135106698</t>
+  </si>
+  <si>
+    <t>135395957</t>
+  </si>
+  <si>
+    <t>134759209</t>
+  </si>
+  <si>
+    <t>135416475</t>
+  </si>
+  <si>
+    <t>130537985</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -588,7 +549,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,16 +581,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -638,16 +599,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -656,16 +617,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -674,16 +635,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -692,16 +653,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -710,16 +671,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,16 +689,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -746,16 +707,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -764,16 +725,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -782,16 +743,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -800,16 +761,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -818,16 +779,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -836,16 +797,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -854,16 +815,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -872,16 +833,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -890,16 +851,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -908,16 +869,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -926,16 +887,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -944,16 +905,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -962,16 +923,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -980,16 +941,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -998,16 +959,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,16 +977,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1034,16 +995,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1052,16 +1013,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1070,16 +1031,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1088,16 +1049,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1106,16 +1067,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1085,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1142,16 +1103,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1159,16 +1120,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1176,16 +1137,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1193,222 +1154,18 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1426,31 +1183,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF97CF9D-5022-4011-88DE-3F7407A45BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E37DB1-2830-4997-946C-284ABD0C90C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1183,31 +1183,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E37DB1-2830-4997-946C-284ABD0C90C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD22F6F8-B4F8-482E-8FDE-647C3C779C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -1183,31 +1183,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD22F6F8-B4F8-482E-8FDE-647C3C779C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0A9042-400A-42C5-B1D1-4C23E33654C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="58">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,106 +54,154 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135297311</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 18.11.2025</t>
-  </si>
-  <si>
-    <t>135151570</t>
-  </si>
-  <si>
-    <t>135359719</t>
-  </si>
-  <si>
-    <t>130248029</t>
-  </si>
-  <si>
-    <t>135271039</t>
-  </si>
-  <si>
-    <t>135146615</t>
-  </si>
-  <si>
-    <t>130601615</t>
-  </si>
-  <si>
-    <t>135227162</t>
-  </si>
-  <si>
-    <t>130360076</t>
-  </si>
-  <si>
-    <t>130579919</t>
-  </si>
-  <si>
-    <t>130239541</t>
-  </si>
-  <si>
-    <t>130522108</t>
-  </si>
-  <si>
-    <t>135314980</t>
-  </si>
-  <si>
-    <t>135287373</t>
-  </si>
-  <si>
-    <t>135394963</t>
-  </si>
-  <si>
-    <t>135309543</t>
-  </si>
-  <si>
-    <t>135315035</t>
-  </si>
-  <si>
-    <t>135287307</t>
-  </si>
-  <si>
-    <t>135048792</t>
-  </si>
-  <si>
-    <t>130501576</t>
-  </si>
-  <si>
-    <t>135174613</t>
-  </si>
-  <si>
-    <t>130272418</t>
-  </si>
-  <si>
-    <t>135342282</t>
-  </si>
-  <si>
-    <t>135328296</t>
-  </si>
-  <si>
-    <t>135173264</t>
-  </si>
-  <si>
-    <t>130375992</t>
-  </si>
-  <si>
-    <t>135402156</t>
-  </si>
-  <si>
-    <t>135106698</t>
-  </si>
-  <si>
-    <t>135395957</t>
-  </si>
-  <si>
-    <t>134759209</t>
-  </si>
-  <si>
-    <t>135416475</t>
-  </si>
-  <si>
-    <t>130537985</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 18.11.2025</t>
+    <t>135388850</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 19.11.2025</t>
+  </si>
+  <si>
+    <t>135411756</t>
+  </si>
+  <si>
+    <t>135436212</t>
+  </si>
+  <si>
+    <t>135403650</t>
+  </si>
+  <si>
+    <t>130625808</t>
+  </si>
+  <si>
+    <t>135444932</t>
+  </si>
+  <si>
+    <t>135382322</t>
+  </si>
+  <si>
+    <t>135091209</t>
+  </si>
+  <si>
+    <t>130330409</t>
+  </si>
+  <si>
+    <t>133114566</t>
+  </si>
+  <si>
+    <t>135395690</t>
+  </si>
+  <si>
+    <t>135126437</t>
+  </si>
+  <si>
+    <t>135425370</t>
+  </si>
+  <si>
+    <t>135416054</t>
+  </si>
+  <si>
+    <t>135417092</t>
+  </si>
+  <si>
+    <t>135412135</t>
+  </si>
+  <si>
+    <t>130260262</t>
+  </si>
+  <si>
+    <t>135416153</t>
+  </si>
+  <si>
+    <t>130259859</t>
+  </si>
+  <si>
+    <t>135446699</t>
+  </si>
+  <si>
+    <t>135169846</t>
+  </si>
+  <si>
+    <t>135399274</t>
+  </si>
+  <si>
+    <t>135230568</t>
+  </si>
+  <si>
+    <t>135348508</t>
+  </si>
+  <si>
+    <t>135340387</t>
+  </si>
+  <si>
+    <t>135365508</t>
+  </si>
+  <si>
+    <t>135337052</t>
+  </si>
+  <si>
+    <t>135396620</t>
+  </si>
+  <si>
+    <t>135383439</t>
+  </si>
+  <si>
+    <t>135314924</t>
+  </si>
+  <si>
+    <t>135208484</t>
+  </si>
+  <si>
+    <t>135157697</t>
+  </si>
+  <si>
+    <t>130268415</t>
+  </si>
+  <si>
+    <t>130084691</t>
+  </si>
+  <si>
+    <t>135316480</t>
+  </si>
+  <si>
+    <t>135104214</t>
+  </si>
+  <si>
+    <t>130194302</t>
+  </si>
+  <si>
+    <t>130189325</t>
+  </si>
+  <si>
+    <t>130226223</t>
+  </si>
+  <si>
+    <t>133839008</t>
+  </si>
+  <si>
+    <t>133704082</t>
+  </si>
+  <si>
+    <t>135330556</t>
+  </si>
+  <si>
+    <t>130730722</t>
+  </si>
+  <si>
+    <t>135214567</t>
+  </si>
+  <si>
+    <t>135325487</t>
+  </si>
+  <si>
+    <t>135254902</t>
+  </si>
+  <si>
+    <t>132885884</t>
+  </si>
+  <si>
+    <t>135402388</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 19.11.2025</t>
   </si>
 </sst>
 </file>
@@ -549,7 +597,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -608,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -626,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -644,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -662,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -680,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -698,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -716,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -734,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -752,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -770,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -788,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -797,7 +845,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -806,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -815,7 +863,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -824,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -833,7 +881,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -842,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -851,7 +899,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -860,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -869,7 +917,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -878,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -887,7 +935,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -896,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -905,7 +953,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -914,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -923,7 +971,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -932,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -941,7 +989,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -950,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -959,7 +1007,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -968,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -977,7 +1025,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -986,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -995,7 +1043,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1004,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1013,7 +1061,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1022,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1031,7 +1079,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1040,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1049,7 +1097,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1058,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1067,7 +1115,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1076,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1085,7 +1133,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1094,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1103,7 +1151,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1112,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1120,7 +1168,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1129,7 +1177,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1137,7 +1185,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1146,7 +1194,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1154,7 +1202,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1163,9 +1211,264 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1183,31 +1486,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0A9042-400A-42C5-B1D1-4C23E33654C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C859B465-52FC-44B3-BEF3-4FA5B95D2B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="56">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,154 +54,148 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135388850</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 19.11.2025</t>
-  </si>
-  <si>
-    <t>135411756</t>
-  </si>
-  <si>
-    <t>135436212</t>
-  </si>
-  <si>
-    <t>135403650</t>
-  </si>
-  <si>
-    <t>130625808</t>
-  </si>
-  <si>
-    <t>135444932</t>
-  </si>
-  <si>
-    <t>135382322</t>
-  </si>
-  <si>
-    <t>135091209</t>
-  </si>
-  <si>
-    <t>130330409</t>
-  </si>
-  <si>
-    <t>133114566</t>
-  </si>
-  <si>
-    <t>135395690</t>
-  </si>
-  <si>
-    <t>135126437</t>
-  </si>
-  <si>
-    <t>135425370</t>
-  </si>
-  <si>
-    <t>135416054</t>
-  </si>
-  <si>
-    <t>135417092</t>
-  </si>
-  <si>
-    <t>135412135</t>
-  </si>
-  <si>
-    <t>130260262</t>
-  </si>
-  <si>
-    <t>135416153</t>
-  </si>
-  <si>
-    <t>130259859</t>
-  </si>
-  <si>
-    <t>135446699</t>
-  </si>
-  <si>
-    <t>135169846</t>
-  </si>
-  <si>
-    <t>135399274</t>
-  </si>
-  <si>
-    <t>135230568</t>
-  </si>
-  <si>
-    <t>135348508</t>
-  </si>
-  <si>
-    <t>135340387</t>
-  </si>
-  <si>
-    <t>135365508</t>
-  </si>
-  <si>
-    <t>135337052</t>
-  </si>
-  <si>
-    <t>135396620</t>
-  </si>
-  <si>
-    <t>135383439</t>
-  </si>
-  <si>
-    <t>135314924</t>
-  </si>
-  <si>
-    <t>135208484</t>
-  </si>
-  <si>
-    <t>135157697</t>
-  </si>
-  <si>
-    <t>130268415</t>
-  </si>
-  <si>
-    <t>130084691</t>
-  </si>
-  <si>
-    <t>135316480</t>
-  </si>
-  <si>
-    <t>135104214</t>
-  </si>
-  <si>
-    <t>130194302</t>
-  </si>
-  <si>
-    <t>130189325</t>
-  </si>
-  <si>
-    <t>130226223</t>
-  </si>
-  <si>
-    <t>133839008</t>
-  </si>
-  <si>
-    <t>133704082</t>
-  </si>
-  <si>
-    <t>135330556</t>
-  </si>
-  <si>
-    <t>130730722</t>
-  </si>
-  <si>
-    <t>135214567</t>
-  </si>
-  <si>
-    <t>135325487</t>
-  </si>
-  <si>
-    <t>135254902</t>
-  </si>
-  <si>
-    <t>132885884</t>
-  </si>
-  <si>
-    <t>135402388</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 19.11.2025</t>
+    <t>135342234</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 21.11.2025</t>
+  </si>
+  <si>
+    <t>135276444</t>
+  </si>
+  <si>
+    <t>130620558</t>
+  </si>
+  <si>
+    <t>135236449</t>
+  </si>
+  <si>
+    <t>135423140</t>
+  </si>
+  <si>
+    <t>135402396</t>
+  </si>
+  <si>
+    <t>130372465</t>
+  </si>
+  <si>
+    <t>130518007</t>
+  </si>
+  <si>
+    <t>134941341</t>
+  </si>
+  <si>
+    <t>130340085</t>
+  </si>
+  <si>
+    <t>135394396</t>
+  </si>
+  <si>
+    <t>135288313</t>
+  </si>
+  <si>
+    <t>134929727</t>
+  </si>
+  <si>
+    <t>130559818</t>
+  </si>
+  <si>
+    <t>135444886</t>
+  </si>
+  <si>
+    <t>135338135</t>
+  </si>
+  <si>
+    <t>135411669</t>
+  </si>
+  <si>
+    <t>135430722</t>
+  </si>
+  <si>
+    <t>135443260</t>
+  </si>
+  <si>
+    <t>135437306</t>
+  </si>
+  <si>
+    <t>135443788</t>
+  </si>
+  <si>
+    <t>135248182</t>
+  </si>
+  <si>
+    <t>130668278</t>
+  </si>
+  <si>
+    <t>135295544</t>
+  </si>
+  <si>
+    <t>135183108</t>
+  </si>
+  <si>
+    <t>135401772</t>
+  </si>
+  <si>
+    <t>130373267</t>
+  </si>
+  <si>
+    <t>135416980</t>
+  </si>
+  <si>
+    <t>130459105</t>
+  </si>
+  <si>
+    <t>135466041</t>
+  </si>
+  <si>
+    <t>135315676</t>
+  </si>
+  <si>
+    <t>135335686</t>
+  </si>
+  <si>
+    <t>135381249</t>
+  </si>
+  <si>
+    <t>135416448</t>
+  </si>
+  <si>
+    <t>135434514</t>
+  </si>
+  <si>
+    <t>135364598</t>
+  </si>
+  <si>
+    <t>130685059</t>
+  </si>
+  <si>
+    <t>135462116</t>
+  </si>
+  <si>
+    <t>130200367</t>
+  </si>
+  <si>
+    <t>134469054</t>
+  </si>
+  <si>
+    <t>135280723</t>
+  </si>
+  <si>
+    <t>135326736</t>
+  </si>
+  <si>
+    <t>130304831</t>
+  </si>
+  <si>
+    <t>130269997</t>
+  </si>
+  <si>
+    <t>130163602</t>
+  </si>
+  <si>
+    <t>135447706</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 21.11.2025</t>
   </si>
 </sst>
 </file>
@@ -597,7 +591,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -638,7 +632,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -656,7 +650,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -674,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -692,7 +686,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -710,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -728,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -746,7 +740,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -764,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -782,7 +776,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -800,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -818,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -836,7 +830,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -854,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -872,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -890,7 +884,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -908,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -926,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -944,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -962,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -980,7 +974,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -998,7 +992,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1046,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1100,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1118,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1142,7 +1136,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1160,7 +1154,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1177,7 +1171,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1194,7 +1188,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1211,7 +1205,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1228,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1245,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1262,7 +1256,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1279,7 +1273,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1296,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1313,7 +1307,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1330,7 +1324,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1347,7 +1341,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1364,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1381,7 +1375,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1398,7 +1392,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1415,7 +1409,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1432,43 +1426,9 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1486,31 +1446,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C859B465-52FC-44B3-BEF3-4FA5B95D2B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACDDF8F-1DCD-4EA1-B36C-73326E14CEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,148 +54,133 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135342234</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 21.11.2025</t>
-  </si>
-  <si>
-    <t>135276444</t>
-  </si>
-  <si>
-    <t>130620558</t>
-  </si>
-  <si>
-    <t>135236449</t>
-  </si>
-  <si>
-    <t>135423140</t>
-  </si>
-  <si>
-    <t>135402396</t>
-  </si>
-  <si>
-    <t>130372465</t>
-  </si>
-  <si>
-    <t>130518007</t>
-  </si>
-  <si>
-    <t>134941341</t>
-  </si>
-  <si>
-    <t>130340085</t>
-  </si>
-  <si>
-    <t>135394396</t>
-  </si>
-  <si>
-    <t>135288313</t>
-  </si>
-  <si>
-    <t>134929727</t>
-  </si>
-  <si>
-    <t>130559818</t>
-  </si>
-  <si>
-    <t>135444886</t>
-  </si>
-  <si>
-    <t>135338135</t>
-  </si>
-  <si>
-    <t>135411669</t>
-  </si>
-  <si>
-    <t>135430722</t>
-  </si>
-  <si>
-    <t>135443260</t>
-  </si>
-  <si>
-    <t>135437306</t>
-  </si>
-  <si>
-    <t>135443788</t>
-  </si>
-  <si>
-    <t>135248182</t>
-  </si>
-  <si>
-    <t>130668278</t>
-  </si>
-  <si>
-    <t>135295544</t>
-  </si>
-  <si>
-    <t>135183108</t>
-  </si>
-  <si>
-    <t>135401772</t>
-  </si>
-  <si>
-    <t>130373267</t>
-  </si>
-  <si>
-    <t>135416980</t>
-  </si>
-  <si>
-    <t>130459105</t>
-  </si>
-  <si>
-    <t>135466041</t>
-  </si>
-  <si>
-    <t>135315676</t>
-  </si>
-  <si>
-    <t>135335686</t>
-  </si>
-  <si>
-    <t>135381249</t>
-  </si>
-  <si>
-    <t>135416448</t>
-  </si>
-  <si>
-    <t>135434514</t>
-  </si>
-  <si>
-    <t>135364598</t>
-  </si>
-  <si>
-    <t>130685059</t>
-  </si>
-  <si>
-    <t>135462116</t>
-  </si>
-  <si>
-    <t>130200367</t>
-  </si>
-  <si>
-    <t>134469054</t>
-  </si>
-  <si>
-    <t>135280723</t>
-  </si>
-  <si>
-    <t>135326736</t>
-  </si>
-  <si>
-    <t>130304831</t>
-  </si>
-  <si>
-    <t>130269997</t>
-  </si>
-  <si>
-    <t>130163602</t>
-  </si>
-  <si>
-    <t>135447706</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 21.11.2025</t>
+    <t>135441124</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 24.11.2025</t>
+  </si>
+  <si>
+    <t>135452014</t>
+  </si>
+  <si>
+    <t>135505678</t>
+  </si>
+  <si>
+    <t>135282943</t>
+  </si>
+  <si>
+    <t>135469811</t>
+  </si>
+  <si>
+    <t>135402110</t>
+  </si>
+  <si>
+    <t>130252372</t>
+  </si>
+  <si>
+    <t>130664762</t>
+  </si>
+  <si>
+    <t>135316561</t>
+  </si>
+  <si>
+    <t>130246865</t>
+  </si>
+  <si>
+    <t>135384088</t>
+  </si>
+  <si>
+    <t>135456434</t>
+  </si>
+  <si>
+    <t>135351795</t>
+  </si>
+  <si>
+    <t>135470636</t>
+  </si>
+  <si>
+    <t>135456227</t>
+  </si>
+  <si>
+    <t>130704333</t>
+  </si>
+  <si>
+    <t>135394728</t>
+  </si>
+  <si>
+    <t>130666679</t>
+  </si>
+  <si>
+    <t>135377727</t>
+  </si>
+  <si>
+    <t>135315066</t>
+  </si>
+  <si>
+    <t>135444024</t>
+  </si>
+  <si>
+    <t>130582013</t>
+  </si>
+  <si>
+    <t>135455667</t>
+  </si>
+  <si>
+    <t>135378903</t>
+  </si>
+  <si>
+    <t>135487062</t>
+  </si>
+  <si>
+    <t>135336612</t>
+  </si>
+  <si>
+    <t>130579460</t>
+  </si>
+  <si>
+    <t>135090764</t>
+  </si>
+  <si>
+    <t>130519194</t>
+  </si>
+  <si>
+    <t>130576572</t>
+  </si>
+  <si>
+    <t>133972396</t>
+  </si>
+  <si>
+    <t>135288237</t>
+  </si>
+  <si>
+    <t>135275820</t>
+  </si>
+  <si>
+    <t>135487600</t>
+  </si>
+  <si>
+    <t>130417349</t>
+  </si>
+  <si>
+    <t>130331340</t>
+  </si>
+  <si>
+    <t>135493505</t>
+  </si>
+  <si>
+    <t>134024810</t>
+  </si>
+  <si>
+    <t>135428868</t>
+  </si>
+  <si>
+    <t>135464753</t>
+  </si>
+  <si>
+    <t>135400072</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 24.11.2025</t>
   </si>
 </sst>
 </file>
@@ -591,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -632,7 +617,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -650,7 +635,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -668,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -686,7 +671,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -704,7 +689,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -722,7 +707,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -740,7 +725,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -758,7 +743,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -776,7 +761,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -794,7 +779,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -812,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -830,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -848,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -857,7 +842,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -866,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -875,7 +860,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -884,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -893,7 +878,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -902,7 +887,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -911,7 +896,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -920,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -929,7 +914,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -938,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -947,7 +932,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -956,7 +941,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,7 +950,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -974,7 +959,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -983,7 +968,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -992,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1001,7 +986,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -1010,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1019,7 +1004,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1028,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1022,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1046,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1040,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1064,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1058,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1082,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1076,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1100,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1094,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1118,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1112,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1136,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1130,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1154,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1162,7 +1147,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1171,7 +1156,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1179,7 +1164,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1188,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1196,7 +1181,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1205,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1213,7 +1198,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1222,7 +1207,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1230,7 +1215,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1239,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1247,7 +1232,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1256,7 +1241,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1264,7 +1249,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1273,7 +1258,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1281,7 +1266,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1290,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1298,7 +1283,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1307,7 +1292,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1315,7 +1300,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -1324,7 +1309,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1332,7 +1317,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
@@ -1341,7 +1326,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1349,7 +1334,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -1358,77 +1343,9 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1446,31 +1363,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACDDF8F-1DCD-4EA1-B36C-73326E14CEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290D42F8-DD4B-4476-8F53-8DEE02B5C511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="63">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,133 +54,169 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135441124</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 24.11.2025</t>
-  </si>
-  <si>
-    <t>135452014</t>
-  </si>
-  <si>
-    <t>135505678</t>
-  </si>
-  <si>
-    <t>135282943</t>
-  </si>
-  <si>
-    <t>135469811</t>
-  </si>
-  <si>
-    <t>135402110</t>
-  </si>
-  <si>
-    <t>130252372</t>
-  </si>
-  <si>
-    <t>130664762</t>
-  </si>
-  <si>
-    <t>135316561</t>
-  </si>
-  <si>
-    <t>130246865</t>
-  </si>
-  <si>
-    <t>135384088</t>
-  </si>
-  <si>
-    <t>135456434</t>
-  </si>
-  <si>
-    <t>135351795</t>
-  </si>
-  <si>
-    <t>135470636</t>
-  </si>
-  <si>
-    <t>135456227</t>
-  </si>
-  <si>
-    <t>130704333</t>
-  </si>
-  <si>
-    <t>135394728</t>
-  </si>
-  <si>
-    <t>130666679</t>
-  </si>
-  <si>
-    <t>135377727</t>
-  </si>
-  <si>
-    <t>135315066</t>
-  </si>
-  <si>
-    <t>135444024</t>
-  </si>
-  <si>
-    <t>130582013</t>
-  </si>
-  <si>
-    <t>135455667</t>
-  </si>
-  <si>
-    <t>135378903</t>
-  </si>
-  <si>
-    <t>135487062</t>
-  </si>
-  <si>
-    <t>135336612</t>
-  </si>
-  <si>
-    <t>130579460</t>
-  </si>
-  <si>
-    <t>135090764</t>
-  </si>
-  <si>
-    <t>130519194</t>
-  </si>
-  <si>
-    <t>130576572</t>
-  </si>
-  <si>
-    <t>133972396</t>
-  </si>
-  <si>
-    <t>135288237</t>
-  </si>
-  <si>
-    <t>135275820</t>
-  </si>
-  <si>
-    <t>135487600</t>
-  </si>
-  <si>
-    <t>130417349</t>
-  </si>
-  <si>
-    <t>130331340</t>
-  </si>
-  <si>
-    <t>135493505</t>
-  </si>
-  <si>
     <t>134024810</t>
   </si>
   <si>
-    <t>135428868</t>
-  </si>
-  <si>
-    <t>135464753</t>
-  </si>
-  <si>
-    <t>135400072</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 24.11.2025</t>
+    <t>135416097</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 25.11.2025</t>
+  </si>
+  <si>
+    <t>135440916</t>
+  </si>
+  <si>
+    <t>135206385</t>
+  </si>
+  <si>
+    <t>135416459</t>
+  </si>
+  <si>
+    <t>130445130</t>
+  </si>
+  <si>
+    <t>130657154</t>
+  </si>
+  <si>
+    <t>135403042</t>
+  </si>
+  <si>
+    <t>135336926</t>
+  </si>
+  <si>
+    <t>135402800</t>
+  </si>
+  <si>
+    <t>135315082</t>
+  </si>
+  <si>
+    <t>130626321</t>
+  </si>
+  <si>
+    <t>130342199</t>
+  </si>
+  <si>
+    <t>135537702</t>
+  </si>
+  <si>
+    <t>135445921</t>
+  </si>
+  <si>
+    <t>135252748</t>
+  </si>
+  <si>
+    <t>135552550</t>
+  </si>
+  <si>
+    <t>135481824</t>
+  </si>
+  <si>
+    <t>135431683</t>
+  </si>
+  <si>
+    <t>135486931</t>
+  </si>
+  <si>
+    <t>135275067</t>
+  </si>
+  <si>
+    <t>130676410</t>
+  </si>
+  <si>
+    <t>134511145</t>
+  </si>
+  <si>
+    <t>135417359</t>
+  </si>
+  <si>
+    <t>130488824</t>
+  </si>
+  <si>
+    <t>135481603</t>
+  </si>
+  <si>
+    <t>130459311</t>
+  </si>
+  <si>
+    <t>130693290</t>
+  </si>
+  <si>
+    <t>135281281</t>
+  </si>
+  <si>
+    <t>135378468</t>
+  </si>
+  <si>
+    <t>135405595</t>
+  </si>
+  <si>
+    <t>135506618</t>
+  </si>
+  <si>
+    <t>130467933</t>
+  </si>
+  <si>
+    <t>135495816</t>
+  </si>
+  <si>
+    <t>135416393</t>
+  </si>
+  <si>
+    <t>135404181</t>
+  </si>
+  <si>
+    <t>130497515</t>
+  </si>
+  <si>
+    <t>134997397</t>
+  </si>
+  <si>
+    <t>135062231</t>
+  </si>
+  <si>
+    <t>130425340</t>
+  </si>
+  <si>
+    <t>130373896</t>
+  </si>
+  <si>
+    <t>130414302</t>
+  </si>
+  <si>
+    <t>130152280</t>
+  </si>
+  <si>
+    <t>135274836</t>
+  </si>
+  <si>
+    <t>135038260</t>
+  </si>
+  <si>
+    <t>130272303</t>
+  </si>
+  <si>
+    <t>135156500</t>
+  </si>
+  <si>
+    <t>135481665</t>
+  </si>
+  <si>
+    <t>135425444</t>
+  </si>
+  <si>
+    <t>135381032</t>
+  </si>
+  <si>
+    <t>130454849</t>
+  </si>
+  <si>
+    <t>130424253</t>
+  </si>
+  <si>
+    <t>135441266</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25.11.2025</t>
   </si>
 </sst>
 </file>
@@ -576,7 +612,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -608,16 +644,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -626,16 +662,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -644,16 +680,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -662,16 +698,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -680,16 +716,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -698,16 +734,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -716,16 +752,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -734,16 +770,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -752,16 +788,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -770,16 +806,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -788,16 +824,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -806,16 +842,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -824,16 +860,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -842,16 +878,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -860,16 +896,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -878,16 +914,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -896,16 +932,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -914,16 +950,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -932,16 +968,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -950,16 +986,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -968,16 +1004,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -986,16 +1022,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1040,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1022,16 +1058,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1040,16 +1076,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1058,16 +1094,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1076,16 +1112,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1094,16 +1130,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1112,16 +1148,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1130,16 +1166,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1147,16 +1183,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1164,16 +1200,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1181,16 +1217,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1198,16 +1234,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1215,16 +1251,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1232,16 +1268,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1249,16 +1285,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1266,16 +1302,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1283,16 +1319,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1300,16 +1336,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1317,16 +1353,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1334,18 +1370,256 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1363,31 +1637,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290D42F8-DD4B-4476-8F53-8DEE02B5C511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEF273E-A7A5-49A8-89E3-C5CFFAE0E47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,169 +54,172 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134024810</t>
-  </si>
-  <si>
-    <t>135416097</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 25.11.2025</t>
-  </si>
-  <si>
-    <t>135440916</t>
-  </si>
-  <si>
-    <t>135206385</t>
-  </si>
-  <si>
-    <t>135416459</t>
-  </si>
-  <si>
-    <t>130445130</t>
-  </si>
-  <si>
-    <t>130657154</t>
-  </si>
-  <si>
-    <t>135403042</t>
-  </si>
-  <si>
-    <t>135336926</t>
-  </si>
-  <si>
-    <t>135402800</t>
-  </si>
-  <si>
-    <t>135315082</t>
-  </si>
-  <si>
-    <t>130626321</t>
-  </si>
-  <si>
-    <t>130342199</t>
-  </si>
-  <si>
     <t>135537702</t>
   </si>
   <si>
-    <t>135445921</t>
-  </si>
-  <si>
-    <t>135252748</t>
-  </si>
-  <si>
     <t>135552550</t>
   </si>
   <si>
-    <t>135481824</t>
-  </si>
-  <si>
-    <t>135431683</t>
-  </si>
-  <si>
-    <t>135486931</t>
-  </si>
-  <si>
-    <t>135275067</t>
-  </si>
-  <si>
-    <t>130676410</t>
-  </si>
-  <si>
-    <t>134511145</t>
-  </si>
-  <si>
-    <t>135417359</t>
-  </si>
-  <si>
-    <t>130488824</t>
-  </si>
-  <si>
-    <t>135481603</t>
-  </si>
-  <si>
-    <t>130459311</t>
-  </si>
-  <si>
-    <t>130693290</t>
-  </si>
-  <si>
-    <t>135281281</t>
-  </si>
-  <si>
-    <t>135378468</t>
-  </si>
-  <si>
-    <t>135405595</t>
-  </si>
-  <si>
-    <t>135506618</t>
-  </si>
-  <si>
-    <t>130467933</t>
-  </si>
-  <si>
-    <t>135495816</t>
-  </si>
-  <si>
-    <t>135416393</t>
-  </si>
-  <si>
-    <t>135404181</t>
-  </si>
-  <si>
-    <t>130497515</t>
-  </si>
-  <si>
-    <t>134997397</t>
-  </si>
-  <si>
-    <t>135062231</t>
-  </si>
-  <si>
-    <t>130425340</t>
-  </si>
-  <si>
-    <t>130373896</t>
-  </si>
-  <si>
-    <t>130414302</t>
-  </si>
-  <si>
-    <t>130152280</t>
-  </si>
-  <si>
-    <t>135274836</t>
-  </si>
-  <si>
-    <t>135038260</t>
-  </si>
-  <si>
-    <t>130272303</t>
-  </si>
-  <si>
-    <t>135156500</t>
-  </si>
-  <si>
-    <t>135481665</t>
-  </si>
-  <si>
-    <t>135425444</t>
-  </si>
-  <si>
-    <t>135381032</t>
-  </si>
-  <si>
-    <t>130454849</t>
-  </si>
-  <si>
-    <t>130424253</t>
-  </si>
-  <si>
-    <t>135441266</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25.11.2025</t>
+    <t>130552066</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 26.11.2025</t>
+  </si>
+  <si>
+    <t>130362243</t>
+  </si>
+  <si>
+    <t>135193056</t>
+  </si>
+  <si>
+    <t>135487946</t>
+  </si>
+  <si>
+    <t>135456136</t>
+  </si>
+  <si>
+    <t>135512518</t>
+  </si>
+  <si>
+    <t>130749528</t>
+  </si>
+  <si>
+    <t>130219058</t>
+  </si>
+  <si>
+    <t>135442735</t>
+  </si>
+  <si>
+    <t>135519213</t>
+  </si>
+  <si>
+    <t>135550733</t>
+  </si>
+  <si>
+    <t>135455895</t>
+  </si>
+  <si>
+    <t>135513000</t>
+  </si>
+  <si>
+    <t>135375785</t>
+  </si>
+  <si>
+    <t>135521313</t>
+  </si>
+  <si>
+    <t>130489385</t>
+  </si>
+  <si>
+    <t>135455851</t>
+  </si>
+  <si>
+    <t>135482262</t>
+  </si>
+  <si>
+    <t>135436503</t>
+  </si>
+  <si>
+    <t>130722327</t>
+  </si>
+  <si>
+    <t>130276169</t>
+  </si>
+  <si>
+    <t>135444425</t>
+  </si>
+  <si>
+    <t>135481888</t>
+  </si>
+  <si>
+    <t>135382532</t>
+  </si>
+  <si>
+    <t>130600685</t>
+  </si>
+  <si>
+    <t>130296625</t>
+  </si>
+  <si>
+    <t>135484086</t>
+  </si>
+  <si>
+    <t>131627019</t>
+  </si>
+  <si>
+    <t>130367529</t>
+  </si>
+  <si>
+    <t>130725951</t>
+  </si>
+  <si>
+    <t>135287153</t>
+  </si>
+  <si>
+    <t>135314833</t>
+  </si>
+  <si>
+    <t>130813648</t>
+  </si>
+  <si>
+    <t>130325821</t>
+  </si>
+  <si>
+    <t>135525374</t>
+  </si>
+  <si>
+    <t>133542962</t>
+  </si>
+  <si>
+    <t>130122832</t>
+  </si>
+  <si>
+    <t>135315221</t>
+  </si>
+  <si>
+    <t>130546483</t>
+  </si>
+  <si>
+    <t>135530515</t>
+  </si>
+  <si>
+    <t>130460144</t>
+  </si>
+  <si>
+    <t>135462642</t>
+  </si>
+  <si>
+    <t>134724859</t>
+  </si>
+  <si>
+    <t>135360568</t>
+  </si>
+  <si>
+    <t>133025681</t>
+  </si>
+  <si>
+    <t>135280723</t>
+  </si>
+  <si>
+    <t>130685059</t>
+  </si>
+  <si>
+    <t>130372692</t>
+  </si>
+  <si>
+    <t>132500304</t>
+  </si>
+  <si>
+    <t>135515410</t>
+  </si>
+  <si>
+    <t>135464656</t>
+  </si>
+  <si>
+    <t>135491423</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 26.11.2025</t>
   </si>
 </sst>
 </file>
@@ -612,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -644,16 +647,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -662,16 +665,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -680,16 +683,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -698,16 +701,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -716,16 +719,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -734,16 +737,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -752,16 +755,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -770,16 +773,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -788,16 +791,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -806,16 +809,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -824,16 +827,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -842,16 +845,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -860,16 +863,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -878,16 +881,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -896,16 +899,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -914,16 +917,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -932,16 +935,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -956,10 +959,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -974,10 +977,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -992,10 +995,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1010,10 +1013,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1028,10 +1031,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1046,10 +1049,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1064,10 +1067,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1082,10 +1085,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1100,10 +1103,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1118,10 +1121,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1136,10 +1139,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1148,16 +1151,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1166,16 +1169,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1183,16 +1186,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1200,16 +1203,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1217,16 +1220,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1234,16 +1237,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1251,16 +1254,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1268,16 +1271,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1285,16 +1288,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1302,16 +1305,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1319,16 +1322,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1336,16 +1339,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1353,16 +1356,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1370,16 +1373,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1387,16 +1390,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1404,16 +1407,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1421,16 +1424,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1438,16 +1441,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1461,10 +1464,10 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1478,10 +1481,10 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1495,10 +1498,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1506,16 +1509,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1523,16 +1526,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1540,16 +1543,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1557,16 +1560,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1574,52 +1577,18 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1637,31 +1606,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEF273E-A7A5-49A8-89E3-C5CFFAE0E47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F966BA-A22E-4AFF-ABFE-241D3759453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="60">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,172 +54,160 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135537702</t>
-  </si>
-  <si>
-    <t>135552550</t>
-  </si>
-  <si>
-    <t>130552066</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 26.11.2025</t>
-  </si>
-  <si>
-    <t>130362243</t>
-  </si>
-  <si>
-    <t>135193056</t>
-  </si>
-  <si>
-    <t>135487946</t>
-  </si>
-  <si>
-    <t>135456136</t>
-  </si>
-  <si>
-    <t>135512518</t>
-  </si>
-  <si>
-    <t>130749528</t>
-  </si>
-  <si>
-    <t>130219058</t>
-  </si>
-  <si>
-    <t>135442735</t>
-  </si>
-  <si>
-    <t>135519213</t>
-  </si>
-  <si>
-    <t>135550733</t>
-  </si>
-  <si>
-    <t>135455895</t>
-  </si>
-  <si>
-    <t>135513000</t>
-  </si>
-  <si>
-    <t>135375785</t>
-  </si>
-  <si>
-    <t>135521313</t>
-  </si>
-  <si>
-    <t>130489385</t>
-  </si>
-  <si>
-    <t>135455851</t>
-  </si>
-  <si>
-    <t>135482262</t>
-  </si>
-  <si>
-    <t>135436503</t>
-  </si>
-  <si>
-    <t>130722327</t>
-  </si>
-  <si>
-    <t>130276169</t>
-  </si>
-  <si>
-    <t>135444425</t>
-  </si>
-  <si>
-    <t>135481888</t>
-  </si>
-  <si>
-    <t>135382532</t>
-  </si>
-  <si>
-    <t>130600685</t>
-  </si>
-  <si>
-    <t>130296625</t>
-  </si>
-  <si>
-    <t>135484086</t>
-  </si>
-  <si>
-    <t>131627019</t>
-  </si>
-  <si>
-    <t>130367529</t>
-  </si>
-  <si>
-    <t>130725951</t>
-  </si>
-  <si>
-    <t>135287153</t>
-  </si>
-  <si>
-    <t>135314833</t>
-  </si>
-  <si>
-    <t>130813648</t>
-  </si>
-  <si>
-    <t>130325821</t>
-  </si>
-  <si>
-    <t>135525374</t>
-  </si>
-  <si>
-    <t>133542962</t>
-  </si>
-  <si>
-    <t>130122832</t>
-  </si>
-  <si>
-    <t>135315221</t>
-  </si>
-  <si>
-    <t>130546483</t>
-  </si>
-  <si>
-    <t>135530515</t>
-  </si>
-  <si>
-    <t>130460144</t>
-  </si>
-  <si>
-    <t>135462642</t>
-  </si>
-  <si>
-    <t>134724859</t>
-  </si>
-  <si>
-    <t>135360568</t>
-  </si>
-  <si>
-    <t>133025681</t>
-  </si>
-  <si>
-    <t>135280723</t>
-  </si>
-  <si>
-    <t>130685059</t>
-  </si>
-  <si>
-    <t>130372692</t>
-  </si>
-  <si>
-    <t>132500304</t>
-  </si>
-  <si>
-    <t>135515410</t>
-  </si>
-  <si>
-    <t>135464656</t>
-  </si>
-  <si>
-    <t>135491423</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 26.11.2025</t>
+    <t>135419263</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.11.2025</t>
+  </si>
+  <si>
+    <t>135335629</t>
+  </si>
+  <si>
+    <t>135482325</t>
+  </si>
+  <si>
+    <t>130682479</t>
+  </si>
+  <si>
+    <t>135399974</t>
+  </si>
+  <si>
+    <t>135436716</t>
+  </si>
+  <si>
+    <t>135423261</t>
+  </si>
+  <si>
+    <t>135532503</t>
+  </si>
+  <si>
+    <t>130638825</t>
+  </si>
+  <si>
+    <t>135455338</t>
+  </si>
+  <si>
+    <t>135416247</t>
+  </si>
+  <si>
+    <t>135482148</t>
+  </si>
+  <si>
+    <t>130476792</t>
+  </si>
+  <si>
+    <t>130220971</t>
+  </si>
+  <si>
+    <t>135581261</t>
+  </si>
+  <si>
+    <t>135551092</t>
+  </si>
+  <si>
+    <t>135506746</t>
+  </si>
+  <si>
+    <t>135505650</t>
+  </si>
+  <si>
+    <t>135480880</t>
+  </si>
+  <si>
+    <t>135547970</t>
+  </si>
+  <si>
+    <t>135456857</t>
+  </si>
+  <si>
+    <t>135416413</t>
+  </si>
+  <si>
+    <t>130556693</t>
+  </si>
+  <si>
+    <t>135426709</t>
+  </si>
+  <si>
+    <t>135496890</t>
+  </si>
+  <si>
+    <t>135403145</t>
+  </si>
+  <si>
+    <t>130462099</t>
+  </si>
+  <si>
+    <t>135505961</t>
+  </si>
+  <si>
+    <t>135482236</t>
+  </si>
+  <si>
+    <t>130579645</t>
+  </si>
+  <si>
+    <t>135437123</t>
+  </si>
+  <si>
+    <t>130719938</t>
+  </si>
+  <si>
+    <t>135275170</t>
+  </si>
+  <si>
+    <t>130468887</t>
+  </si>
+  <si>
+    <t>130534713</t>
+  </si>
+  <si>
+    <t>135322123</t>
+  </si>
+  <si>
+    <t>135273896</t>
+  </si>
+  <si>
+    <t>130245291</t>
+  </si>
+  <si>
+    <t>135419502</t>
+  </si>
+  <si>
+    <t>135551990</t>
+  </si>
+  <si>
+    <t>131959817</t>
+  </si>
+  <si>
+    <t>131440809</t>
+  </si>
+  <si>
+    <t>135528823</t>
+  </si>
+  <si>
+    <t>135551600</t>
+  </si>
+  <si>
+    <t>135379916</t>
+  </si>
+  <si>
+    <t>135382068</t>
+  </si>
+  <si>
+    <t>135579646</t>
+  </si>
+  <si>
+    <t>135545728</t>
+  </si>
+  <si>
+    <t>135272674</t>
+  </si>
+  <si>
+    <t>135153405</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.11.2025</t>
   </si>
 </sst>
 </file>
@@ -615,7 +603,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -647,16 +635,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -665,16 +653,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -683,16 +671,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -701,16 +689,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -719,16 +707,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -737,16 +725,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -755,16 +743,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -773,16 +761,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -791,16 +779,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -809,16 +797,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -827,16 +815,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -845,16 +833,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -863,16 +851,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -881,16 +869,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -899,16 +887,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -917,16 +905,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -935,16 +923,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -953,16 +941,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -971,16 +959,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -989,16 +977,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1007,16 +995,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1025,16 +1013,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1043,16 +1031,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1061,16 +1049,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1079,16 +1067,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1097,16 +1085,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1103,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1133,16 +1121,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1151,16 +1139,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1175,10 +1163,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1192,10 +1180,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1209,10 +1197,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1226,10 +1214,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1243,10 +1231,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1260,10 +1248,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1277,10 +1265,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1294,10 +1282,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1311,10 +1299,10 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1328,10 +1316,10 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1345,10 +1333,10 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1362,10 +1350,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1379,10 +1367,10 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1396,10 +1384,10 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1413,10 +1401,10 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1430,10 +1418,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1447,10 +1435,10 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1464,10 +1452,10 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1481,10 +1469,10 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1498,10 +1486,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1515,80 +1503,12 @@
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1606,31 +1526,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F966BA-A22E-4AFF-ABFE-241D3759453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DE134F-4F7A-460D-9F58-8CB045A4EE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1526,31 +1526,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DE134F-4F7A-460D-9F58-8CB045A4EE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2406609-3622-4D01-B395-9CD9E680977A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,160 +54,88 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135419263</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 27.11.2025</t>
-  </si>
-  <si>
-    <t>135335629</t>
-  </si>
-  <si>
-    <t>135482325</t>
-  </si>
-  <si>
-    <t>130682479</t>
-  </si>
-  <si>
-    <t>135399974</t>
-  </si>
-  <si>
-    <t>135436716</t>
-  </si>
-  <si>
-    <t>135423261</t>
-  </si>
-  <si>
-    <t>135532503</t>
-  </si>
-  <si>
-    <t>130638825</t>
-  </si>
-  <si>
-    <t>135455338</t>
-  </si>
-  <si>
-    <t>135416247</t>
-  </si>
-  <si>
-    <t>135482148</t>
-  </si>
-  <si>
-    <t>130476792</t>
-  </si>
-  <si>
-    <t>130220971</t>
-  </si>
-  <si>
-    <t>135581261</t>
-  </si>
-  <si>
-    <t>135551092</t>
-  </si>
-  <si>
-    <t>135506746</t>
-  </si>
-  <si>
-    <t>135505650</t>
-  </si>
-  <si>
-    <t>135480880</t>
-  </si>
-  <si>
-    <t>135547970</t>
-  </si>
-  <si>
-    <t>135456857</t>
-  </si>
-  <si>
-    <t>135416413</t>
-  </si>
-  <si>
-    <t>130556693</t>
-  </si>
-  <si>
-    <t>135426709</t>
-  </si>
-  <si>
-    <t>135496890</t>
-  </si>
-  <si>
-    <t>135403145</t>
-  </si>
-  <si>
-    <t>130462099</t>
-  </si>
-  <si>
-    <t>135505961</t>
-  </si>
-  <si>
-    <t>135482236</t>
-  </si>
-  <si>
-    <t>130579645</t>
-  </si>
-  <si>
-    <t>135437123</t>
-  </si>
-  <si>
-    <t>130719938</t>
-  </si>
-  <si>
-    <t>135275170</t>
-  </si>
-  <si>
-    <t>130468887</t>
-  </si>
-  <si>
-    <t>130534713</t>
-  </si>
-  <si>
-    <t>135322123</t>
-  </si>
-  <si>
-    <t>135273896</t>
-  </si>
-  <si>
-    <t>130245291</t>
-  </si>
-  <si>
-    <t>135419502</t>
-  </si>
-  <si>
-    <t>135551990</t>
-  </si>
-  <si>
-    <t>131959817</t>
-  </si>
-  <si>
-    <t>131440809</t>
-  </si>
-  <si>
-    <t>135528823</t>
-  </si>
-  <si>
-    <t>135551600</t>
-  </si>
-  <si>
-    <t>135379916</t>
-  </si>
-  <si>
-    <t>135382068</t>
-  </si>
-  <si>
-    <t>135579646</t>
-  </si>
-  <si>
-    <t>135545728</t>
-  </si>
-  <si>
-    <t>135272674</t>
-  </si>
-  <si>
-    <t>135153405</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.11.2025</t>
+    <t>135533831</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 01.12.2025</t>
+  </si>
+  <si>
+    <t>135491263</t>
+  </si>
+  <si>
+    <t>135514442</t>
+  </si>
+  <si>
+    <t>135568772</t>
+  </si>
+  <si>
+    <t>135523467</t>
+  </si>
+  <si>
+    <t>135416283</t>
+  </si>
+  <si>
+    <t>134321614</t>
+  </si>
+  <si>
+    <t>130291935</t>
+  </si>
+  <si>
+    <t>135395734</t>
+  </si>
+  <si>
+    <t>135417277</t>
+  </si>
+  <si>
+    <t>135580170</t>
+  </si>
+  <si>
+    <t>135394368</t>
+  </si>
+  <si>
+    <t>135505641</t>
+  </si>
+  <si>
+    <t>135551904</t>
+  </si>
+  <si>
+    <t>135579294</t>
+  </si>
+  <si>
+    <t>130382157</t>
+  </si>
+  <si>
+    <t>135555249</t>
+  </si>
+  <si>
+    <t>135394228</t>
+  </si>
+  <si>
+    <t>130771293</t>
+  </si>
+  <si>
+    <t>135624719</t>
+  </si>
+  <si>
+    <t>135624584</t>
+  </si>
+  <si>
+    <t>130475203</t>
+  </si>
+  <si>
+    <t>130473915</t>
+  </si>
+  <si>
+    <t>130335884</t>
+  </si>
+  <si>
+    <t>134401310</t>
+  </si>
+  <si>
+    <t>135276015</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 01.12.2025</t>
   </si>
 </sst>
 </file>
@@ -603,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -644,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -662,7 +590,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -680,7 +608,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -698,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -716,7 +644,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -734,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -752,7 +680,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -770,7 +698,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -788,7 +716,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -806,7 +734,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -824,7 +752,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -842,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -860,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -878,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -896,7 +824,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -914,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -932,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -950,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -968,7 +896,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -986,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1004,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1022,7 +950,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1040,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1058,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1076,7 +1004,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1094,423 +1022,12 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1526,31 +1043,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2406609-3622-4D01-B395-9CD9E680977A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE56EFC7-1192-4AF7-BD8B-B5A25746885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="94">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -136,6 +136,180 @@
   </si>
   <si>
     <t>Allianz - Cancelamento 01.12.2025</t>
+  </si>
+  <si>
+    <t>135376931</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 28.11.2025</t>
+  </si>
+  <si>
+    <t>135505800</t>
+  </si>
+  <si>
+    <t>135482214</t>
+  </si>
+  <si>
+    <t>135472699</t>
+  </si>
+  <si>
+    <t>135448007</t>
+  </si>
+  <si>
+    <t>130489356</t>
+  </si>
+  <si>
+    <t>135557870</t>
+  </si>
+  <si>
+    <t>130497625</t>
+  </si>
+  <si>
+    <t>130408713</t>
+  </si>
+  <si>
+    <t>135191830</t>
+  </si>
+  <si>
+    <t>135547558</t>
+  </si>
+  <si>
+    <t>135318940</t>
+  </si>
+  <si>
+    <t>135505946</t>
+  </si>
+  <si>
+    <t>135482107</t>
+  </si>
+  <si>
+    <t>135506525</t>
+  </si>
+  <si>
+    <t>130420854</t>
+  </si>
+  <si>
+    <t>135276017</t>
+  </si>
+  <si>
+    <t>15911306</t>
+  </si>
+  <si>
+    <t>135280594</t>
+  </si>
+  <si>
+    <t>135505936</t>
+  </si>
+  <si>
+    <t>130415114</t>
+  </si>
+  <si>
+    <t>135447179</t>
+  </si>
+  <si>
+    <t>135494206</t>
+  </si>
+  <si>
+    <t>135536594</t>
+  </si>
+  <si>
+    <t>135481641</t>
+  </si>
+  <si>
+    <t>135339250</t>
+  </si>
+  <si>
+    <t>135481763</t>
+  </si>
+  <si>
+    <t>135456431</t>
+  </si>
+  <si>
+    <t>135276681</t>
+  </si>
+  <si>
+    <t>135416380</t>
+  </si>
+  <si>
+    <t>130694459</t>
+  </si>
+  <si>
+    <t>135455309</t>
+  </si>
+  <si>
+    <t>130406611</t>
+  </si>
+  <si>
+    <t>130417387</t>
+  </si>
+  <si>
+    <t>135497474</t>
+  </si>
+  <si>
+    <t>130643150</t>
+  </si>
+  <si>
+    <t>135416341</t>
+  </si>
+  <si>
+    <t>135531483</t>
+  </si>
+  <si>
+    <t>130275868</t>
+  </si>
+  <si>
+    <t>130415217</t>
+  </si>
+  <si>
+    <t>135461886</t>
+  </si>
+  <si>
+    <t>130582013</t>
+  </si>
+  <si>
+    <t>130490213</t>
+  </si>
+  <si>
+    <t>130622775</t>
+  </si>
+  <si>
+    <t>130457293</t>
+  </si>
+  <si>
+    <t>130627192</t>
+  </si>
+  <si>
+    <t>130428118</t>
+  </si>
+  <si>
+    <t>135499839</t>
+  </si>
+  <si>
+    <t>130587041</t>
+  </si>
+  <si>
+    <t>130259426</t>
+  </si>
+  <si>
+    <t>134370602</t>
+  </si>
+  <si>
+    <t>130098022</t>
+  </si>
+  <si>
+    <t>135505944</t>
+  </si>
+  <si>
+    <t>135522219</t>
+  </si>
+  <si>
+    <t>135560346</t>
+  </si>
+  <si>
+    <t>134511192</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 28.11.2025</t>
   </si>
 </sst>
 </file>
@@ -531,7 +705,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -1028,6 +1202,992 @@
         <v>6</v>
       </c>
       <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1043,31 +2203,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F098913-597A-4A16-A3C9-F72BAA4C8631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68452793-359C-4C1F-9C0D-B681C6A0B084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,115 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135276015</t>
-  </si>
-  <si>
-    <t>135416950</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 02.12.2025</t>
-  </si>
-  <si>
-    <t>135596142</t>
-  </si>
-  <si>
-    <t>130283538</t>
-  </si>
-  <si>
-    <t>130342923</t>
-  </si>
-  <si>
-    <t>130415169</t>
-  </si>
-  <si>
-    <t>130767478</t>
-  </si>
-  <si>
-    <t>130728631</t>
-  </si>
-  <si>
-    <t>130323183</t>
-  </si>
-  <si>
-    <t>135575775</t>
-  </si>
-  <si>
-    <t>130649777</t>
-  </si>
-  <si>
-    <t>135581088</t>
-  </si>
-  <si>
-    <t>130721415</t>
-  </si>
-  <si>
-    <t>130694349</t>
-  </si>
-  <si>
-    <t>135272905</t>
-  </si>
-  <si>
-    <t>130736487</t>
-  </si>
-  <si>
-    <t>135481849</t>
-  </si>
-  <si>
-    <t>130278180</t>
-  </si>
-  <si>
-    <t>130614177</t>
-  </si>
-  <si>
-    <t>130768421</t>
-  </si>
-  <si>
-    <t>135533519</t>
-  </si>
-  <si>
-    <t>130440338</t>
-  </si>
-  <si>
-    <t>135403199</t>
-  </si>
-  <si>
-    <t>130698091</t>
-  </si>
-  <si>
-    <t>130593362</t>
-  </si>
-  <si>
-    <t>135462249</t>
-  </si>
-  <si>
-    <t>130297078</t>
-  </si>
-  <si>
-    <t>130549924</t>
-  </si>
-  <si>
-    <t>130267255</t>
-  </si>
-  <si>
-    <t>135407363</t>
-  </si>
-  <si>
-    <t>135581856</t>
-  </si>
-  <si>
-    <t>134469054</t>
-  </si>
-  <si>
-    <t>130250157</t>
-  </si>
-  <si>
-    <t>135342637</t>
-  </si>
-  <si>
-    <t>135482238</t>
-  </si>
-  <si>
-    <t>135453838</t>
-  </si>
-  <si>
-    <t>135631884</t>
-  </si>
-  <si>
-    <t>135416173</t>
-  </si>
-  <si>
-    <t>135487438</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 02.12.2025</t>
+    <t>130688117</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 03.12.2025</t>
+  </si>
+  <si>
+    <t>134986546</t>
+  </si>
+  <si>
+    <t>135481900</t>
+  </si>
+  <si>
+    <t>130786729</t>
+  </si>
+  <si>
+    <t>135381076</t>
+  </si>
+  <si>
+    <t>130736676</t>
+  </si>
+  <si>
+    <t>135535900</t>
+  </si>
+  <si>
+    <t>130470288</t>
+  </si>
+  <si>
+    <t>135555022</t>
+  </si>
+  <si>
+    <t>135577700</t>
+  </si>
+  <si>
+    <t>135505973</t>
+  </si>
+  <si>
+    <t>135405271</t>
+  </si>
+  <si>
+    <t>130522993</t>
+  </si>
+  <si>
+    <t>130676622</t>
+  </si>
+  <si>
+    <t>134743599</t>
+  </si>
+  <si>
+    <t>135404817</t>
+  </si>
+  <si>
+    <t>130706638</t>
+  </si>
+  <si>
+    <t>135647706</t>
+  </si>
+  <si>
+    <t>130676493</t>
+  </si>
+  <si>
+    <t>130464275</t>
+  </si>
+  <si>
+    <t>135481742</t>
+  </si>
+  <si>
+    <t>135624743</t>
+  </si>
+  <si>
+    <t>130661989</t>
+  </si>
+  <si>
+    <t>134150470</t>
+  </si>
+  <si>
+    <t>130386571</t>
+  </si>
+  <si>
+    <t>130550817</t>
+  </si>
+  <si>
+    <t>130532317</t>
+  </si>
+  <si>
+    <t>135574859</t>
+  </si>
+  <si>
+    <t>132350484</t>
+  </si>
+  <si>
+    <t>130249975</t>
+  </si>
+  <si>
+    <t>132314182</t>
+  </si>
+  <si>
+    <t>133302306</t>
+  </si>
+  <si>
+    <t>135482298</t>
+  </si>
+  <si>
+    <t>130906205</t>
+  </si>
+  <si>
+    <t>134393979</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 03.12.2025</t>
   </si>
 </sst>
 </file>
@@ -570,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -602,16 +590,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -620,16 +608,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -638,16 +626,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,16 +644,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -674,16 +662,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -692,16 +680,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -710,16 +698,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -728,16 +716,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -746,16 +734,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -764,16 +752,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -782,16 +770,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -800,16 +788,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,16 +806,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -836,16 +824,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -854,16 +842,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -872,16 +860,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -890,16 +878,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -908,16 +896,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -926,16 +914,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -944,16 +932,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -962,16 +950,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -980,16 +968,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -998,16 +986,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1016,16 +1004,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1034,16 +1022,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1052,16 +1040,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1070,16 +1058,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1087,16 +1075,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1110,10 +1098,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1127,10 +1115,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1144,10 +1132,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1161,10 +1149,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1178,10 +1166,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1195,10 +1183,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1212,80 +1200,12 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1303,31 +1223,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68452793-359C-4C1F-9C0D-B681C6A0B084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C6CC7-0F93-4089-A2F4-76A4E1190375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,115 +54,190 @@
     <t>1070</t>
   </si>
   <si>
-    <t>130688117</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 03.12.2025</t>
-  </si>
-  <si>
-    <t>134986546</t>
-  </si>
-  <si>
-    <t>135481900</t>
-  </si>
-  <si>
-    <t>130786729</t>
-  </si>
-  <si>
-    <t>135381076</t>
-  </si>
-  <si>
-    <t>130736676</t>
-  </si>
-  <si>
-    <t>135535900</t>
-  </si>
-  <si>
-    <t>130470288</t>
-  </si>
-  <si>
-    <t>135555022</t>
-  </si>
-  <si>
-    <t>135577700</t>
-  </si>
-  <si>
-    <t>135505973</t>
-  </si>
-  <si>
-    <t>135405271</t>
-  </si>
-  <si>
-    <t>130522993</t>
-  </si>
-  <si>
-    <t>130676622</t>
-  </si>
-  <si>
-    <t>134743599</t>
-  </si>
-  <si>
-    <t>135404817</t>
-  </si>
-  <si>
-    <t>130706638</t>
-  </si>
-  <si>
-    <t>135647706</t>
-  </si>
-  <si>
-    <t>130676493</t>
-  </si>
-  <si>
-    <t>130464275</t>
-  </si>
-  <si>
-    <t>135481742</t>
-  </si>
-  <si>
-    <t>135624743</t>
-  </si>
-  <si>
-    <t>130661989</t>
-  </si>
-  <si>
-    <t>134150470</t>
-  </si>
-  <si>
-    <t>130386571</t>
-  </si>
-  <si>
-    <t>130550817</t>
-  </si>
-  <si>
-    <t>130532317</t>
-  </si>
-  <si>
-    <t>135574859</t>
-  </si>
-  <si>
-    <t>132350484</t>
-  </si>
-  <si>
-    <t>130249975</t>
-  </si>
-  <si>
-    <t>132314182</t>
-  </si>
-  <si>
-    <t>133302306</t>
-  </si>
-  <si>
-    <t>135482298</t>
-  </si>
-  <si>
-    <t>130906205</t>
-  </si>
-  <si>
-    <t>134393979</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 03.12.2025</t>
+    <t>135436343</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 04.12.2025</t>
+  </si>
+  <si>
+    <t>135552146</t>
+  </si>
+  <si>
+    <t>135535568</t>
+  </si>
+  <si>
+    <t>130570847</t>
+  </si>
+  <si>
+    <t>135582236</t>
+  </si>
+  <si>
+    <t>130587608</t>
+  </si>
+  <si>
+    <t>130582638</t>
+  </si>
+  <si>
+    <t>130456113</t>
+  </si>
+  <si>
+    <t>135481816</t>
+  </si>
+  <si>
+    <t>130329761</t>
+  </si>
+  <si>
+    <t>135416323</t>
+  </si>
+  <si>
+    <t>130473372</t>
+  </si>
+  <si>
+    <t>130554184</t>
+  </si>
+  <si>
+    <t>135624614</t>
+  </si>
+  <si>
+    <t>135505910</t>
+  </si>
+  <si>
+    <t>130544864</t>
+  </si>
+  <si>
+    <t>135573842</t>
+  </si>
+  <si>
+    <t>130770055</t>
+  </si>
+  <si>
+    <t>130489339</t>
+  </si>
+  <si>
+    <t>130950991</t>
+  </si>
+  <si>
+    <t>135481855</t>
+  </si>
+  <si>
+    <t>130713334</t>
+  </si>
+  <si>
+    <t>130771017</t>
+  </si>
+  <si>
+    <t>135573325</t>
+  </si>
+  <si>
+    <t>130431354</t>
+  </si>
+  <si>
+    <t>130636209</t>
+  </si>
+  <si>
+    <t>135626230</t>
+  </si>
+  <si>
+    <t>130588630</t>
+  </si>
+  <si>
+    <t>135418518</t>
+  </si>
+  <si>
+    <t>135579240</t>
+  </si>
+  <si>
+    <t>135551156</t>
+  </si>
+  <si>
+    <t>130380928</t>
+  </si>
+  <si>
+    <t>133572640</t>
+  </si>
+  <si>
+    <t>135505786</t>
+  </si>
+  <si>
+    <t>135560276</t>
+  </si>
+  <si>
+    <t>135455282</t>
+  </si>
+  <si>
+    <t>135630786</t>
+  </si>
+  <si>
+    <t>135276432</t>
+  </si>
+  <si>
+    <t>135481741</t>
+  </si>
+  <si>
+    <t>135625381</t>
+  </si>
+  <si>
+    <t>130638720</t>
+  </si>
+  <si>
+    <t>130256258</t>
+  </si>
+  <si>
+    <t>130528310</t>
+  </si>
+  <si>
+    <t>130475547</t>
+  </si>
+  <si>
+    <t>130597457</t>
+  </si>
+  <si>
+    <t>130374160</t>
+  </si>
+  <si>
+    <t>130555490</t>
+  </si>
+  <si>
+    <t>135678326</t>
+  </si>
+  <si>
+    <t>135650005</t>
+  </si>
+  <si>
+    <t>131981941</t>
+  </si>
+  <si>
+    <t>135460498</t>
+  </si>
+  <si>
+    <t>131020834</t>
+  </si>
+  <si>
+    <t>135416158</t>
+  </si>
+  <si>
+    <t>131188734</t>
+  </si>
+  <si>
+    <t>135093575</t>
+  </si>
+  <si>
+    <t>130259426</t>
+  </si>
+  <si>
+    <t>135505755</t>
+  </si>
+  <si>
+    <t>134442436</t>
+  </si>
+  <si>
+    <t>132965569</t>
+  </si>
+  <si>
+    <t>135416427</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 04.12.2025</t>
   </si>
 </sst>
 </file>
@@ -558,7 +633,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -599,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -617,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -635,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -653,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -671,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -689,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -725,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -743,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -761,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -779,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -797,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -815,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -833,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -851,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -869,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -887,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -905,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -923,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -941,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -959,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -977,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -995,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1013,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1031,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1049,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1067,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1084,7 +1159,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1101,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1118,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1135,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1152,7 +1227,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1244,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1186,7 +1261,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1203,9 +1278,434 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1223,31 +1723,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C6CC7-0F93-4089-A2F4-76A4E1190375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E736C4F2-2327-48E2-80D4-BCA0C035F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="66">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,190 +54,178 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135436343</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 04.12.2025</t>
-  </si>
-  <si>
-    <t>135552146</t>
-  </si>
-  <si>
-    <t>135535568</t>
-  </si>
-  <si>
-    <t>130570847</t>
-  </si>
-  <si>
-    <t>135582236</t>
-  </si>
-  <si>
-    <t>130587608</t>
-  </si>
-  <si>
-    <t>130582638</t>
-  </si>
-  <si>
-    <t>130456113</t>
-  </si>
-  <si>
-    <t>135481816</t>
-  </si>
-  <si>
-    <t>130329761</t>
-  </si>
-  <si>
-    <t>135416323</t>
-  </si>
-  <si>
-    <t>130473372</t>
-  </si>
-  <si>
-    <t>130554184</t>
-  </si>
-  <si>
-    <t>135624614</t>
-  </si>
-  <si>
-    <t>135505910</t>
-  </si>
-  <si>
-    <t>130544864</t>
-  </si>
-  <si>
-    <t>135573842</t>
-  </si>
-  <si>
-    <t>130770055</t>
-  </si>
-  <si>
-    <t>130489339</t>
-  </si>
-  <si>
-    <t>130950991</t>
-  </si>
-  <si>
-    <t>135481855</t>
-  </si>
-  <si>
-    <t>130713334</t>
-  </si>
-  <si>
-    <t>130771017</t>
-  </si>
-  <si>
-    <t>135573325</t>
-  </si>
-  <si>
-    <t>130431354</t>
-  </si>
-  <si>
-    <t>130636209</t>
-  </si>
-  <si>
-    <t>135626230</t>
-  </si>
-  <si>
-    <t>130588630</t>
-  </si>
-  <si>
-    <t>135418518</t>
-  </si>
-  <si>
-    <t>135579240</t>
-  </si>
-  <si>
-    <t>135551156</t>
-  </si>
-  <si>
-    <t>130380928</t>
-  </si>
-  <si>
-    <t>133572640</t>
-  </si>
-  <si>
-    <t>135505786</t>
-  </si>
-  <si>
-    <t>135560276</t>
-  </si>
-  <si>
-    <t>135455282</t>
-  </si>
-  <si>
-    <t>135630786</t>
-  </si>
-  <si>
-    <t>135276432</t>
-  </si>
-  <si>
-    <t>135481741</t>
-  </si>
-  <si>
-    <t>135625381</t>
-  </si>
-  <si>
-    <t>130638720</t>
-  </si>
-  <si>
-    <t>130256258</t>
-  </si>
-  <si>
-    <t>130528310</t>
-  </si>
-  <si>
-    <t>130475547</t>
-  </si>
-  <si>
-    <t>130597457</t>
-  </si>
-  <si>
-    <t>130374160</t>
-  </si>
-  <si>
-    <t>130555490</t>
-  </si>
-  <si>
-    <t>135678326</t>
-  </si>
-  <si>
     <t>135650005</t>
   </si>
   <si>
-    <t>131981941</t>
-  </si>
-  <si>
-    <t>135460498</t>
-  </si>
-  <si>
-    <t>131020834</t>
-  </si>
-  <si>
-    <t>135416158</t>
-  </si>
-  <si>
-    <t>131188734</t>
-  </si>
-  <si>
-    <t>135093575</t>
-  </si>
-  <si>
-    <t>130259426</t>
-  </si>
-  <si>
-    <t>135505755</t>
-  </si>
-  <si>
-    <t>134442436</t>
-  </si>
-  <si>
-    <t>132965569</t>
-  </si>
-  <si>
-    <t>135416427</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 04.12.2025</t>
+    <t>135481437</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.12.2025</t>
+  </si>
+  <si>
+    <t>130524048</t>
+  </si>
+  <si>
+    <t>130770540</t>
+  </si>
+  <si>
+    <t>135654216</t>
+  </si>
+  <si>
+    <t>135654069</t>
+  </si>
+  <si>
+    <t>135517068</t>
+  </si>
+  <si>
+    <t>135505634</t>
+  </si>
+  <si>
+    <t>135512520</t>
+  </si>
+  <si>
+    <t>135535455</t>
+  </si>
+  <si>
+    <t>135581331</t>
+  </si>
+  <si>
+    <t>135643836</t>
+  </si>
+  <si>
+    <t>130742364</t>
+  </si>
+  <si>
+    <t>135528154</t>
+  </si>
+  <si>
+    <t>135576150</t>
+  </si>
+  <si>
+    <t>135487685</t>
+  </si>
+  <si>
+    <t>130538175</t>
+  </si>
+  <si>
+    <t>135645850</t>
+  </si>
+  <si>
+    <t>135710077</t>
+  </si>
+  <si>
+    <t>135711461</t>
+  </si>
+  <si>
+    <t>130688103</t>
+  </si>
+  <si>
+    <t>135507567</t>
+  </si>
+  <si>
+    <t>135482354</t>
+  </si>
+  <si>
+    <t>135578996</t>
+  </si>
+  <si>
+    <t>135538097</t>
+  </si>
+  <si>
+    <t>135514153</t>
+  </si>
+  <si>
+    <t>131127134</t>
+  </si>
+  <si>
+    <t>135528270</t>
+  </si>
+  <si>
+    <t>135577259</t>
+  </si>
+  <si>
+    <t>135551752</t>
+  </si>
+  <si>
+    <t>130678093</t>
+  </si>
+  <si>
+    <t>135692720</t>
+  </si>
+  <si>
+    <t>130805550</t>
+  </si>
+  <si>
+    <t>135580271</t>
+  </si>
+  <si>
+    <t>135482458</t>
+  </si>
+  <si>
+    <t>135507940</t>
+  </si>
+  <si>
+    <t>130488204</t>
+  </si>
+  <si>
+    <t>135583140</t>
+  </si>
+  <si>
+    <t>135624730</t>
+  </si>
+  <si>
+    <t>135455145</t>
+  </si>
+  <si>
+    <t>135624304</t>
+  </si>
+  <si>
+    <t>130804387</t>
+  </si>
+  <si>
+    <t>135417011</t>
+  </si>
+  <si>
+    <t>135638011</t>
+  </si>
+  <si>
+    <t>130642664</t>
+  </si>
+  <si>
+    <t>135426308</t>
+  </si>
+  <si>
+    <t>130468134</t>
+  </si>
+  <si>
+    <t>130902905</t>
+  </si>
+  <si>
+    <t>130359497</t>
+  </si>
+  <si>
+    <t>134093917</t>
+  </si>
+  <si>
+    <t>130538807</t>
+  </si>
+  <si>
+    <t>130335884</t>
+  </si>
+  <si>
+    <t>135595755</t>
+  </si>
+  <si>
+    <t>130865824</t>
+  </si>
+  <si>
+    <t>135535274</t>
+  </si>
+  <si>
+    <t>135532886</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 05.12.2025</t>
   </si>
 </sst>
 </file>
@@ -633,7 +621,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -665,16 +653,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -683,16 +671,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -701,16 +689,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -719,16 +707,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -737,16 +725,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -755,16 +743,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -773,16 +761,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -791,16 +779,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -809,16 +797,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -827,16 +815,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -845,16 +833,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -863,16 +851,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -887,10 +875,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -905,10 +893,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -923,10 +911,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -941,10 +929,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -959,10 +947,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -977,10 +965,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -995,10 +983,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1013,10 +1001,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1031,10 +1019,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1049,10 +1037,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1067,10 +1055,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1085,10 +1073,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1103,10 +1091,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1121,10 +1109,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1139,10 +1127,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1156,10 +1144,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1173,10 +1161,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1190,10 +1178,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1207,10 +1195,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1224,10 +1212,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1241,10 +1229,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1258,10 +1246,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1275,10 +1263,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1292,10 +1280,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1309,10 +1297,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1326,10 +1314,10 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1343,10 +1331,10 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1360,10 +1348,10 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1377,10 +1365,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1394,10 +1382,10 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1411,10 +1399,10 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1428,10 +1416,10 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1445,10 +1433,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1462,10 +1450,10 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1479,10 +1467,10 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1496,10 +1484,10 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1513,10 +1501,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1530,10 +1518,10 @@
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1547,10 +1535,10 @@
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1564,10 +1552,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1581,10 +1569,10 @@
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1598,10 +1586,10 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1615,10 +1603,10 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1632,80 +1620,12 @@
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1723,31 +1643,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E736C4F2-2327-48E2-80D4-BCA0C035F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE6C601-01BD-46CE-9559-B2C48F67E710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1230" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="76">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,178 +54,208 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135650005</t>
-  </si>
-  <si>
-    <t>135481437</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 05.12.2025</t>
-  </si>
-  <si>
-    <t>130524048</t>
-  </si>
-  <si>
-    <t>130770540</t>
-  </si>
-  <si>
-    <t>135654216</t>
-  </si>
-  <si>
-    <t>135654069</t>
-  </si>
-  <si>
-    <t>135517068</t>
-  </si>
-  <si>
-    <t>135505634</t>
-  </si>
-  <si>
-    <t>135512520</t>
-  </si>
-  <si>
-    <t>135535455</t>
-  </si>
-  <si>
-    <t>135581331</t>
-  </si>
-  <si>
-    <t>135643836</t>
-  </si>
-  <si>
-    <t>130742364</t>
-  </si>
-  <si>
-    <t>135528154</t>
-  </si>
-  <si>
-    <t>135576150</t>
-  </si>
-  <si>
-    <t>135487685</t>
-  </si>
-  <si>
-    <t>130538175</t>
-  </si>
-  <si>
-    <t>135645850</t>
-  </si>
-  <si>
-    <t>135710077</t>
-  </si>
-  <si>
-    <t>135711461</t>
-  </si>
-  <si>
-    <t>130688103</t>
-  </si>
-  <si>
-    <t>135507567</t>
-  </si>
-  <si>
-    <t>135482354</t>
-  </si>
-  <si>
-    <t>135578996</t>
-  </si>
-  <si>
-    <t>135538097</t>
-  </si>
-  <si>
-    <t>135514153</t>
-  </si>
-  <si>
-    <t>131127134</t>
-  </si>
-  <si>
-    <t>135528270</t>
-  </si>
-  <si>
-    <t>135577259</t>
-  </si>
-  <si>
-    <t>135551752</t>
-  </si>
-  <si>
-    <t>130678093</t>
-  </si>
-  <si>
-    <t>135692720</t>
-  </si>
-  <si>
-    <t>130805550</t>
-  </si>
-  <si>
-    <t>135580271</t>
-  </si>
-  <si>
-    <t>135482458</t>
-  </si>
-  <si>
-    <t>135507940</t>
-  </si>
-  <si>
-    <t>130488204</t>
-  </si>
-  <si>
-    <t>135583140</t>
-  </si>
-  <si>
-    <t>135624730</t>
-  </si>
-  <si>
-    <t>135455145</t>
-  </si>
-  <si>
-    <t>135624304</t>
-  </si>
-  <si>
-    <t>130804387</t>
-  </si>
-  <si>
-    <t>135417011</t>
-  </si>
-  <si>
-    <t>135638011</t>
-  </si>
-  <si>
-    <t>130642664</t>
-  </si>
-  <si>
-    <t>135426308</t>
-  </si>
-  <si>
-    <t>130468134</t>
-  </si>
-  <si>
-    <t>130902905</t>
-  </si>
-  <si>
-    <t>130359497</t>
-  </si>
-  <si>
-    <t>134093917</t>
-  </si>
-  <si>
-    <t>130538807</t>
-  </si>
-  <si>
-    <t>130335884</t>
-  </si>
-  <si>
-    <t>135595755</t>
-  </si>
-  <si>
-    <t>130865824</t>
-  </si>
-  <si>
     <t>135535274</t>
   </si>
   <si>
-    <t>135532886</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 05.12.2025</t>
+    <t>135481501</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 08.12.2025</t>
+  </si>
+  <si>
+    <t>135573997</t>
+  </si>
+  <si>
+    <t>135481767</t>
+  </si>
+  <si>
+    <t>135669937</t>
+  </si>
+  <si>
+    <t>135481999</t>
+  </si>
+  <si>
+    <t>135529800</t>
+  </si>
+  <si>
+    <t>135662128</t>
+  </si>
+  <si>
+    <t>135741466</t>
+  </si>
+  <si>
+    <t>135674294</t>
+  </si>
+  <si>
+    <t>130817464</t>
+  </si>
+  <si>
+    <t>135694083</t>
+  </si>
+  <si>
+    <t>135550879</t>
+  </si>
+  <si>
+    <t>135505978</t>
+  </si>
+  <si>
+    <t>135409260</t>
+  </si>
+  <si>
+    <t>134993080</t>
+  </si>
+  <si>
+    <t>135652591</t>
+  </si>
+  <si>
+    <t>131329702</t>
+  </si>
+  <si>
+    <t>135645225</t>
+  </si>
+  <si>
+    <t>135561870</t>
+  </si>
+  <si>
+    <t>135624302</t>
+  </si>
+  <si>
+    <t>135377688</t>
+  </si>
+  <si>
+    <t>135416191</t>
+  </si>
+  <si>
+    <t>135444993</t>
+  </si>
+  <si>
+    <t>135536973</t>
+  </si>
+  <si>
+    <t>135580852</t>
+  </si>
+  <si>
+    <t>135741622</t>
+  </si>
+  <si>
+    <t>130628439</t>
+  </si>
+  <si>
+    <t>135168930</t>
+  </si>
+  <si>
+    <t>135702329</t>
+  </si>
+  <si>
+    <t>135563669</t>
+  </si>
+  <si>
+    <t>130716343</t>
+  </si>
+  <si>
+    <t>135699210</t>
+  </si>
+  <si>
+    <t>130770071</t>
+  </si>
+  <si>
+    <t>135647669</t>
+  </si>
+  <si>
+    <t>133866947</t>
+  </si>
+  <si>
+    <t>135700374</t>
+  </si>
+  <si>
+    <t>135611830</t>
+  </si>
+  <si>
+    <t>135578230</t>
+  </si>
+  <si>
+    <t>135378146</t>
+  </si>
+  <si>
+    <t>135583587</t>
+  </si>
+  <si>
+    <t>135556994</t>
+  </si>
+  <si>
+    <t>135573372</t>
+  </si>
+  <si>
+    <t>130677690</t>
+  </si>
+  <si>
+    <t>135599826</t>
+  </si>
+  <si>
+    <t>135625788</t>
+  </si>
+  <si>
+    <t>130309705</t>
+  </si>
+  <si>
+    <t>130679578</t>
+  </si>
+  <si>
+    <t>135560705</t>
+  </si>
+  <si>
+    <t>130544864</t>
+  </si>
+  <si>
+    <t>135410631</t>
+  </si>
+  <si>
+    <t>135275891</t>
+  </si>
+  <si>
+    <t>135699083</t>
+  </si>
+  <si>
+    <t>135675870</t>
+  </si>
+  <si>
+    <t>130545576</t>
+  </si>
+  <si>
+    <t>130340100</t>
+  </si>
+  <si>
+    <t>130462594</t>
+  </si>
+  <si>
+    <t>135536803</t>
+  </si>
+  <si>
+    <t>135581138</t>
+  </si>
+  <si>
+    <t>135372386</t>
+  </si>
+  <si>
+    <t>132146245</t>
+  </si>
+  <si>
+    <t>135418181</t>
+  </si>
+  <si>
+    <t>134744239</t>
+  </si>
+  <si>
+    <t>134255140</t>
+  </si>
+  <si>
+    <t>135630129</t>
+  </si>
+  <si>
+    <t>135606632</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 08.12.2025</t>
   </si>
 </sst>
 </file>
@@ -621,7 +651,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -662,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -680,7 +710,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -698,7 +728,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -716,7 +746,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -734,7 +764,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -752,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -770,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -779,7 +809,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -788,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -797,7 +827,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -806,7 +836,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -815,7 +845,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -824,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -833,7 +863,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -842,7 +872,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -851,7 +881,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -860,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -878,7 +908,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -896,7 +926,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -914,7 +944,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -932,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -950,7 +980,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -968,7 +998,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -986,7 +1016,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1004,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1022,7 +1052,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1040,7 +1070,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1058,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1076,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1142,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1130,7 +1160,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1147,7 +1177,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1164,7 +1194,7 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1198,7 +1228,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1215,7 +1245,7 @@
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1232,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1249,7 +1279,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1266,7 +1296,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1283,7 +1313,7 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1300,7 +1330,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1317,7 +1347,7 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1334,7 +1364,7 @@
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1351,7 +1381,7 @@
         <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1368,7 +1398,7 @@
         <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1385,7 +1415,7 @@
         <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1402,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1419,7 +1449,7 @@
         <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1436,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1453,7 +1483,7 @@
         <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1470,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1487,7 +1517,7 @@
         <v>10</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1504,7 +1534,7 @@
         <v>10</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1521,7 +1551,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1538,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1555,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1572,7 +1602,7 @@
         <v>10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1589,7 +1619,7 @@
         <v>10</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1606,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1623,9 +1653,179 @@
         <v>10</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1643,31 +1843,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7208C55-1EB8-45D9-A093-90F802638BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C6573C-602F-49B8-930C-11F9BFAFD9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,151 +54,139 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135003730</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 28.10.2025</t>
-  </si>
-  <si>
-    <t>135092299</t>
-  </si>
-  <si>
-    <t>135096367</t>
-  </si>
-  <si>
-    <t>134893487</t>
-  </si>
-  <si>
-    <t>135106629</t>
-  </si>
-  <si>
-    <t>134897197</t>
-  </si>
-  <si>
-    <t>135024331</t>
-  </si>
-  <si>
-    <t>135009335</t>
-  </si>
-  <si>
-    <t>134402522</t>
-  </si>
-  <si>
-    <t>135011662</t>
-  </si>
-  <si>
-    <t>135103101</t>
-  </si>
-  <si>
-    <t>135095994</t>
-  </si>
-  <si>
-    <t>133058479</t>
-  </si>
-  <si>
-    <t>134285775</t>
-  </si>
-  <si>
-    <t>130315191</t>
-  </si>
-  <si>
-    <t>130095985</t>
-  </si>
-  <si>
-    <t>135146962</t>
-  </si>
-  <si>
-    <t>130264118</t>
-  </si>
-  <si>
-    <t>135100006</t>
-  </si>
-  <si>
-    <t>134640424</t>
-  </si>
-  <si>
-    <t>135114338</t>
-  </si>
-  <si>
-    <t>135060555</t>
-  </si>
-  <si>
-    <t>134898597</t>
-  </si>
-  <si>
-    <t>130203575</t>
-  </si>
-  <si>
-    <t>135106816</t>
-  </si>
-  <si>
-    <t>134916396</t>
-  </si>
-  <si>
-    <t>130241563</t>
-  </si>
-  <si>
-    <t>134640382</t>
-  </si>
-  <si>
-    <t>134856490</t>
-  </si>
-  <si>
-    <t>135101782</t>
-  </si>
-  <si>
-    <t>135106611</t>
-  </si>
-  <si>
-    <t>130306862</t>
-  </si>
-  <si>
-    <t>134282987</t>
-  </si>
-  <si>
-    <t>134920573</t>
-  </si>
-  <si>
-    <t>130351974</t>
-  </si>
-  <si>
-    <t>135028444</t>
-  </si>
-  <si>
-    <t>134874102</t>
-  </si>
-  <si>
-    <t>134858646</t>
-  </si>
-  <si>
-    <t>135118005</t>
-  </si>
-  <si>
-    <t>132923191</t>
-  </si>
-  <si>
-    <t>135129372</t>
-  </si>
-  <si>
-    <t>129917574</t>
-  </si>
-  <si>
-    <t>135106834</t>
-  </si>
-  <si>
-    <t>135109798</t>
-  </si>
-  <si>
-    <t>135097460</t>
-  </si>
-  <si>
-    <t>134863976</t>
-  </si>
-  <si>
-    <t>134229560</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 28.10.2025</t>
+    <t>135898766</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 19.12.2025</t>
+  </si>
+  <si>
+    <t>130956278</t>
+  </si>
+  <si>
+    <t>135896317</t>
+  </si>
+  <si>
+    <t>130950724</t>
+  </si>
+  <si>
+    <t>135416480</t>
+  </si>
+  <si>
+    <t>130643173</t>
+  </si>
+  <si>
+    <t>135669905</t>
+  </si>
+  <si>
+    <t>130699925</t>
+  </si>
+  <si>
+    <t>135408447</t>
+  </si>
+  <si>
+    <t>135819115</t>
+  </si>
+  <si>
+    <t>135762373</t>
+  </si>
+  <si>
+    <t>130822581</t>
+  </si>
+  <si>
+    <t>135926970</t>
+  </si>
+  <si>
+    <t>130650591</t>
+  </si>
+  <si>
+    <t>135931820</t>
+  </si>
+  <si>
+    <t>130777426</t>
+  </si>
+  <si>
+    <t>135925147</t>
+  </si>
+  <si>
+    <t>130822493</t>
+  </si>
+  <si>
+    <t>135911447</t>
+  </si>
+  <si>
+    <t>135823573</t>
+  </si>
+  <si>
+    <t>135647619</t>
+  </si>
+  <si>
+    <t>135816762</t>
+  </si>
+  <si>
+    <t>135694470</t>
+  </si>
+  <si>
+    <t>135821949</t>
+  </si>
+  <si>
+    <t>131009491</t>
+  </si>
+  <si>
+    <t>135879961</t>
+  </si>
+  <si>
+    <t>130910839</t>
+  </si>
+  <si>
+    <t>135942800</t>
+  </si>
+  <si>
+    <t>135823567</t>
+  </si>
+  <si>
+    <t>135694680</t>
+  </si>
+  <si>
+    <t>135791047</t>
+  </si>
+  <si>
+    <t>135823672</t>
+  </si>
+  <si>
+    <t>133301873</t>
+  </si>
+  <si>
+    <t>132372741</t>
+  </si>
+  <si>
+    <t>135808481</t>
+  </si>
+  <si>
+    <t>135841409</t>
+  </si>
+  <si>
+    <t>130774997</t>
+  </si>
+  <si>
+    <t>135811720</t>
+  </si>
+  <si>
+    <t>135870815</t>
+  </si>
+  <si>
+    <t>135875849</t>
+  </si>
+  <si>
+    <t>135801246</t>
+  </si>
+  <si>
+    <t>135880696</t>
+  </si>
+  <si>
+    <t>132368231</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 19.12.2025</t>
   </si>
 </sst>
 </file>
@@ -594,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -635,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -653,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -671,7 +659,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -689,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -707,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -725,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -743,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -761,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -779,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -797,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -815,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -833,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -851,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -869,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -887,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -905,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -923,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -941,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -959,7 +947,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -977,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -995,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1031,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1049,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1067,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1085,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1103,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1121,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1139,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1157,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1175,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1193,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1211,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1229,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1247,7 +1235,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1264,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1281,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1298,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1315,7 +1303,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1332,7 +1320,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1349,7 +1337,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1366,7 +1354,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1383,77 +1371,9 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1471,31 +1391,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C6573C-602F-49B8-930C-11F9BFAFD9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795DE5CA-7AD1-45D1-A953-314C72BC29D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="64">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,139 +54,172 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135898766</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 19.12.2025</t>
-  </si>
-  <si>
-    <t>130956278</t>
-  </si>
-  <si>
-    <t>135896317</t>
-  </si>
-  <si>
-    <t>130950724</t>
-  </si>
-  <si>
-    <t>135416480</t>
-  </si>
-  <si>
-    <t>130643173</t>
-  </si>
-  <si>
-    <t>135669905</t>
-  </si>
-  <si>
-    <t>130699925</t>
-  </si>
-  <si>
-    <t>135408447</t>
-  </si>
-  <si>
-    <t>135819115</t>
-  </si>
-  <si>
-    <t>135762373</t>
-  </si>
-  <si>
-    <t>130822581</t>
-  </si>
-  <si>
-    <t>135926970</t>
-  </si>
-  <si>
-    <t>130650591</t>
-  </si>
-  <si>
-    <t>135931820</t>
-  </si>
-  <si>
-    <t>130777426</t>
-  </si>
-  <si>
-    <t>135925147</t>
-  </si>
-  <si>
-    <t>130822493</t>
-  </si>
-  <si>
-    <t>135911447</t>
-  </si>
-  <si>
-    <t>135823573</t>
-  </si>
-  <si>
-    <t>135647619</t>
-  </si>
-  <si>
-    <t>135816762</t>
-  </si>
-  <si>
-    <t>135694470</t>
-  </si>
-  <si>
-    <t>135821949</t>
-  </si>
-  <si>
-    <t>131009491</t>
-  </si>
-  <si>
-    <t>135879961</t>
-  </si>
-  <si>
-    <t>130910839</t>
-  </si>
-  <si>
-    <t>135942800</t>
-  </si>
-  <si>
-    <t>135823567</t>
-  </si>
-  <si>
-    <t>135694680</t>
-  </si>
-  <si>
-    <t>135791047</t>
-  </si>
-  <si>
-    <t>135823672</t>
-  </si>
-  <si>
-    <t>133301873</t>
-  </si>
-  <si>
-    <t>132372741</t>
-  </si>
-  <si>
-    <t>135808481</t>
-  </si>
-  <si>
-    <t>135841409</t>
-  </si>
-  <si>
-    <t>130774997</t>
-  </si>
-  <si>
-    <t>135811720</t>
-  </si>
-  <si>
-    <t>135870815</t>
-  </si>
-  <si>
-    <t>135875849</t>
-  </si>
-  <si>
-    <t>135801246</t>
-  </si>
-  <si>
-    <t>135880696</t>
-  </si>
-  <si>
-    <t>132368231</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 19.12.2025</t>
+    <t>130756394</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 22.12.2025</t>
+  </si>
+  <si>
+    <t>135989386</t>
+  </si>
+  <si>
+    <t>135559077</t>
+  </si>
+  <si>
+    <t>131082502</t>
+  </si>
+  <si>
+    <t>135864256</t>
+  </si>
+  <si>
+    <t>135746492</t>
+  </si>
+  <si>
+    <t>135977195</t>
+  </si>
+  <si>
+    <t>135881441</t>
+  </si>
+  <si>
+    <t>135583099</t>
+  </si>
+  <si>
+    <t>135782631</t>
+  </si>
+  <si>
+    <t>135927952</t>
+  </si>
+  <si>
+    <t>135821845</t>
+  </si>
+  <si>
+    <t>135579330</t>
+  </si>
+  <si>
+    <t>130799485</t>
+  </si>
+  <si>
+    <t>135811245</t>
+  </si>
+  <si>
+    <t>135673173</t>
+  </si>
+  <si>
+    <t>135800568</t>
+  </si>
+  <si>
+    <t>135670737</t>
+  </si>
+  <si>
+    <t>135647615</t>
+  </si>
+  <si>
+    <t>135034198</t>
+  </si>
+  <si>
+    <t>135722215</t>
+  </si>
+  <si>
+    <t>130794357</t>
+  </si>
+  <si>
+    <t>135649339</t>
+  </si>
+  <si>
+    <t>130687714</t>
+  </si>
+  <si>
+    <t>135693086</t>
+  </si>
+  <si>
+    <t>135988641</t>
+  </si>
+  <si>
+    <t>135748028</t>
+  </si>
+  <si>
+    <t>135556816</t>
+  </si>
+  <si>
+    <t>135945091</t>
+  </si>
+  <si>
+    <t>135581068</t>
+  </si>
+  <si>
+    <t>130816474</t>
+  </si>
+  <si>
+    <t>135890986</t>
+  </si>
+  <si>
+    <t>135741508</t>
+  </si>
+  <si>
+    <t>135861676</t>
+  </si>
+  <si>
+    <t>130959567</t>
+  </si>
+  <si>
+    <t>131000232</t>
+  </si>
+  <si>
+    <t>135888974</t>
+  </si>
+  <si>
+    <t>131002976</t>
+  </si>
+  <si>
+    <t>135712336</t>
+  </si>
+  <si>
+    <t>132437098</t>
+  </si>
+  <si>
+    <t>135988240</t>
+  </si>
+  <si>
+    <t>135850567</t>
+  </si>
+  <si>
+    <t>130810490</t>
+  </si>
+  <si>
+    <t>130739798</t>
+  </si>
+  <si>
+    <t>135988781</t>
+  </si>
+  <si>
+    <t>135980242</t>
+  </si>
+  <si>
+    <t>130808815</t>
+  </si>
+  <si>
+    <t>135829029</t>
+  </si>
+  <si>
+    <t>135885250</t>
+  </si>
+  <si>
+    <t>135656669</t>
+  </si>
+  <si>
+    <t>135894268</t>
+  </si>
+  <si>
+    <t>135885633</t>
+  </si>
+  <si>
+    <t>133287821</t>
+  </si>
+  <si>
+    <t>135921411</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.12.2025</t>
   </si>
 </sst>
 </file>
@@ -582,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -623,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -641,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -659,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -677,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -695,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -713,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -731,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -749,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -767,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -785,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -803,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -821,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -839,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -857,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -875,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -893,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -911,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -929,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -947,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -983,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1001,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1019,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1199,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1217,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1235,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1252,7 +1285,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1269,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1286,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1303,7 +1336,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1320,7 +1353,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1337,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1354,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1371,9 +1404,213 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1391,31 +1628,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795DE5CA-7AD1-45D1-A953-314C72BC29D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55911F0-259D-47D4-ACC2-AB8994763200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,172 +54,130 @@
     <t>1070</t>
   </si>
   <si>
-    <t>130756394</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 22.12.2025</t>
-  </si>
-  <si>
-    <t>135989386</t>
-  </si>
-  <si>
-    <t>135559077</t>
-  </si>
-  <si>
-    <t>131082502</t>
-  </si>
-  <si>
-    <t>135864256</t>
-  </si>
-  <si>
-    <t>135746492</t>
-  </si>
-  <si>
-    <t>135977195</t>
-  </si>
-  <si>
-    <t>135881441</t>
-  </si>
-  <si>
-    <t>135583099</t>
-  </si>
-  <si>
-    <t>135782631</t>
-  </si>
-  <si>
-    <t>135927952</t>
-  </si>
-  <si>
-    <t>135821845</t>
-  </si>
-  <si>
-    <t>135579330</t>
-  </si>
-  <si>
-    <t>130799485</t>
-  </si>
-  <si>
-    <t>135811245</t>
-  </si>
-  <si>
-    <t>135673173</t>
-  </si>
-  <si>
-    <t>135800568</t>
-  </si>
-  <si>
-    <t>135670737</t>
-  </si>
-  <si>
-    <t>135647615</t>
-  </si>
-  <si>
-    <t>135034198</t>
-  </si>
-  <si>
-    <t>135722215</t>
-  </si>
-  <si>
-    <t>130794357</t>
-  </si>
-  <si>
-    <t>135649339</t>
-  </si>
-  <si>
-    <t>130687714</t>
-  </si>
-  <si>
-    <t>135693086</t>
-  </si>
-  <si>
-    <t>135988641</t>
-  </si>
-  <si>
-    <t>135748028</t>
-  </si>
-  <si>
-    <t>135556816</t>
-  </si>
-  <si>
-    <t>135945091</t>
-  </si>
-  <si>
-    <t>135581068</t>
-  </si>
-  <si>
-    <t>130816474</t>
-  </si>
-  <si>
-    <t>135890986</t>
-  </si>
-  <si>
-    <t>135741508</t>
-  </si>
-  <si>
-    <t>135861676</t>
-  </si>
-  <si>
-    <t>130959567</t>
-  </si>
-  <si>
-    <t>131000232</t>
-  </si>
-  <si>
-    <t>135888974</t>
-  </si>
-  <si>
-    <t>131002976</t>
-  </si>
-  <si>
-    <t>135712336</t>
-  </si>
-  <si>
-    <t>132437098</t>
-  </si>
-  <si>
-    <t>135988240</t>
-  </si>
-  <si>
-    <t>135850567</t>
-  </si>
-  <si>
-    <t>130810490</t>
-  </si>
-  <si>
-    <t>130739798</t>
-  </si>
-  <si>
-    <t>135988781</t>
-  </si>
-  <si>
-    <t>135980242</t>
-  </si>
-  <si>
-    <t>130808815</t>
-  </si>
-  <si>
-    <t>135829029</t>
-  </si>
-  <si>
-    <t>135885250</t>
-  </si>
-  <si>
-    <t>135656669</t>
-  </si>
-  <si>
-    <t>135894268</t>
-  </si>
-  <si>
-    <t>135885633</t>
-  </si>
-  <si>
-    <t>133287821</t>
-  </si>
-  <si>
-    <t>135921411</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.12.2025</t>
+    <t>130916913</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 24.12.2025</t>
+  </si>
+  <si>
+    <t>133019146</t>
+  </si>
+  <si>
+    <t>135984203</t>
+  </si>
+  <si>
+    <t>135973563</t>
+  </si>
+  <si>
+    <t>135970949</t>
+  </si>
+  <si>
+    <t>136010831</t>
+  </si>
+  <si>
+    <t>135904895</t>
+  </si>
+  <si>
+    <t>135741583</t>
+  </si>
+  <si>
+    <t>135823745</t>
+  </si>
+  <si>
+    <t>135894661</t>
+  </si>
+  <si>
+    <t>135836003</t>
+  </si>
+  <si>
+    <t>135999500</t>
+  </si>
+  <si>
+    <t>135693328</t>
+  </si>
+  <si>
+    <t>135947426</t>
+  </si>
+  <si>
+    <t>135989494</t>
+  </si>
+  <si>
+    <t>135894780</t>
+  </si>
+  <si>
+    <t>135811457</t>
+  </si>
+  <si>
+    <t>135982159</t>
+  </si>
+  <si>
+    <t>135581351</t>
+  </si>
+  <si>
+    <t>135824707</t>
+  </si>
+  <si>
+    <t>130749014</t>
+  </si>
+  <si>
+    <t>135931101</t>
+  </si>
+  <si>
+    <t>131167854</t>
+  </si>
+  <si>
+    <t>135911773</t>
+  </si>
+  <si>
+    <t>134800480</t>
+  </si>
+  <si>
+    <t>134042093</t>
+  </si>
+  <si>
+    <t>135905418</t>
+  </si>
+  <si>
+    <t>135820428</t>
+  </si>
+  <si>
+    <t>131192244</t>
+  </si>
+  <si>
+    <t>135990098</t>
+  </si>
+  <si>
+    <t>135997309</t>
+  </si>
+  <si>
+    <t>135982898</t>
+  </si>
+  <si>
+    <t>135741640</t>
+  </si>
+  <si>
+    <t>135989303</t>
+  </si>
+  <si>
+    <t>135812302</t>
+  </si>
+  <si>
+    <t>135988387</t>
+  </si>
+  <si>
+    <t>131181046</t>
+  </si>
+  <si>
+    <t>135989098</t>
+  </si>
+  <si>
+    <t>135977228</t>
+  </si>
+  <si>
+    <t>135506546</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 24.12.2025</t>
   </si>
 </sst>
 </file>
@@ -615,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -656,7 +614,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -674,7 +632,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -692,7 +650,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -710,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -728,7 +686,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -746,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -764,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -782,7 +740,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -800,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -818,7 +776,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -836,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -854,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -872,7 +830,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -890,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -908,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -917,7 +875,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -926,7 +884,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -935,7 +893,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -944,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -953,7 +911,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -962,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -971,7 +929,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -980,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -989,7 +947,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -998,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1007,7 +965,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -1016,7 +974,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1025,7 +983,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -1034,7 +992,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1001,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1052,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1019,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1070,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1079,7 +1037,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1088,7 +1046,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1055,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1106,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1073,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1124,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1091,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1142,7 +1100,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1109,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1160,7 +1118,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1127,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1178,7 +1136,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1145,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1196,7 +1154,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1205,7 +1163,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1214,7 +1172,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1223,7 +1181,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1232,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1241,7 +1199,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1250,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1259,7 +1217,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1268,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1276,7 +1234,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1285,7 +1243,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1293,7 +1251,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1302,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1310,7 +1268,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1319,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1327,7 +1285,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1336,7 +1294,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1344,7 +1302,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -1353,7 +1311,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1361,7 +1319,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
@@ -1370,7 +1328,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1378,7 +1336,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -1387,7 +1345,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1395,7 +1353,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
@@ -1404,213 +1362,9 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1628,31 +1382,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55911F0-259D-47D4-ACC2-AB8994763200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8AB8F3-946C-4C56-8E8F-02C798A6AC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,73 @@
     <t>1070</t>
   </si>
   <si>
-    <t>130916913</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 24.12.2025</t>
-  </si>
-  <si>
-    <t>133019146</t>
-  </si>
-  <si>
-    <t>135984203</t>
-  </si>
-  <si>
-    <t>135973563</t>
-  </si>
-  <si>
-    <t>135970949</t>
-  </si>
-  <si>
-    <t>136010831</t>
-  </si>
-  <si>
-    <t>135904895</t>
-  </si>
-  <si>
-    <t>135741583</t>
-  </si>
-  <si>
-    <t>135823745</t>
-  </si>
-  <si>
-    <t>135894661</t>
-  </si>
-  <si>
-    <t>135836003</t>
-  </si>
-  <si>
-    <t>135999500</t>
-  </si>
-  <si>
-    <t>135693328</t>
-  </si>
-  <si>
-    <t>135947426</t>
-  </si>
-  <si>
-    <t>135989494</t>
-  </si>
-  <si>
-    <t>135894780</t>
-  </si>
-  <si>
-    <t>135811457</t>
-  </si>
-  <si>
-    <t>135982159</t>
-  </si>
-  <si>
-    <t>135581351</t>
-  </si>
-  <si>
-    <t>135824707</t>
-  </si>
-  <si>
-    <t>130749014</t>
-  </si>
-  <si>
-    <t>135931101</t>
-  </si>
-  <si>
-    <t>131167854</t>
-  </si>
-  <si>
-    <t>135911773</t>
-  </si>
-  <si>
-    <t>134800480</t>
-  </si>
-  <si>
-    <t>134042093</t>
-  </si>
-  <si>
-    <t>135905418</t>
-  </si>
-  <si>
-    <t>135820428</t>
-  </si>
-  <si>
-    <t>131192244</t>
-  </si>
-  <si>
-    <t>135990098</t>
-  </si>
-  <si>
-    <t>135997309</t>
-  </si>
-  <si>
-    <t>135982898</t>
-  </si>
-  <si>
-    <t>135741640</t>
-  </si>
-  <si>
-    <t>135989303</t>
-  </si>
-  <si>
-    <t>135812302</t>
-  </si>
-  <si>
-    <t>135988387</t>
-  </si>
-  <si>
-    <t>131181046</t>
-  </si>
-  <si>
-    <t>135989098</t>
-  </si>
-  <si>
-    <t>135977228</t>
-  </si>
-  <si>
-    <t>135506546</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 24.12.2025</t>
+    <t>135782680</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 26.12.2025</t>
+  </si>
+  <si>
+    <t>130755278</t>
+  </si>
+  <si>
+    <t>135713571</t>
+  </si>
+  <si>
+    <t>130861889</t>
+  </si>
+  <si>
+    <t>135988421</t>
+  </si>
+  <si>
+    <t>131060321</t>
+  </si>
+  <si>
+    <t>131224423</t>
+  </si>
+  <si>
+    <t>131007001</t>
+  </si>
+  <si>
+    <t>135234812</t>
+  </si>
+  <si>
+    <t>130919718</t>
+  </si>
+  <si>
+    <t>135811608</t>
+  </si>
+  <si>
+    <t>135788273</t>
+  </si>
+  <si>
+    <t>135741610</t>
+  </si>
+  <si>
+    <t>135925519</t>
+  </si>
+  <si>
+    <t>134603424</t>
+  </si>
+  <si>
+    <t>135989581</t>
+  </si>
+  <si>
+    <t>135601067</t>
+  </si>
+  <si>
+    <t>135003403</t>
+  </si>
+  <si>
+    <t>136016372</t>
+  </si>
+  <si>
+    <t>135507671</t>
+  </si>
+  <si>
+    <t>135811064</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 26.12.2025</t>
   </si>
 </sst>
 </file>
@@ -573,7 +516,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -632,7 +575,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -650,7 +593,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -668,7 +611,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -686,7 +629,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -704,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -722,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -740,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -758,7 +701,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -776,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -794,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -812,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -830,7 +773,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -848,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -866,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -875,7 +818,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -884,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -893,7 +836,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -902,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -911,7 +854,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -920,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -929,7 +872,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -938,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -947,7 +890,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -956,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -965,7 +908,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -974,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -982,391 +925,43 @@
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F33"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F34"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F35"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1382,31 +977,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8AB8F3-946C-4C56-8E8F-02C798A6AC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF81CF53-1AA5-4A67-9E35-37AC3FB63300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="61">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,163 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135782680</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 26.12.2025</t>
-  </si>
-  <si>
-    <t>130755278</t>
-  </si>
-  <si>
-    <t>135713571</t>
-  </si>
-  <si>
-    <t>130861889</t>
-  </si>
-  <si>
-    <t>135988421</t>
-  </si>
-  <si>
-    <t>131060321</t>
-  </si>
-  <si>
-    <t>131224423</t>
-  </si>
-  <si>
-    <t>131007001</t>
-  </si>
-  <si>
-    <t>135234812</t>
-  </si>
-  <si>
-    <t>130919718</t>
-  </si>
-  <si>
-    <t>135811608</t>
-  </si>
-  <si>
-    <t>135788273</t>
-  </si>
-  <si>
-    <t>135741610</t>
-  </si>
-  <si>
-    <t>135925519</t>
-  </si>
-  <si>
-    <t>134603424</t>
-  </si>
-  <si>
-    <t>135989581</t>
-  </si>
-  <si>
-    <t>135601067</t>
-  </si>
-  <si>
-    <t>135003403</t>
-  </si>
-  <si>
-    <t>136016372</t>
-  </si>
-  <si>
-    <t>135507671</t>
-  </si>
-  <si>
-    <t>135811064</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 26.12.2025</t>
+    <t>135788133</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 29.12.2025</t>
+  </si>
+  <si>
+    <t>135989526</t>
+  </si>
+  <si>
+    <t>131041743</t>
+  </si>
+  <si>
+    <t>135980698</t>
+  </si>
+  <si>
+    <t>136010770</t>
+  </si>
+  <si>
+    <t>135823351</t>
+  </si>
+  <si>
+    <t>136010858</t>
+  </si>
+  <si>
+    <t>136030486</t>
+  </si>
+  <si>
+    <t>135657152</t>
+  </si>
+  <si>
+    <t>131062403</t>
+  </si>
+  <si>
+    <t>135698032</t>
+  </si>
+  <si>
+    <t>130864230</t>
+  </si>
+  <si>
+    <t>135898563</t>
+  </si>
+  <si>
+    <t>135823743</t>
+  </si>
+  <si>
+    <t>135741722</t>
+  </si>
+  <si>
+    <t>135817473</t>
+  </si>
+  <si>
+    <t>135989585</t>
+  </si>
+  <si>
+    <t>136036835</t>
+  </si>
+  <si>
+    <t>130856076</t>
+  </si>
+  <si>
+    <t>136028594</t>
+  </si>
+  <si>
+    <t>135859018</t>
+  </si>
+  <si>
+    <t>130861348</t>
+  </si>
+  <si>
+    <t>135875575</t>
+  </si>
+  <si>
+    <t>136023323</t>
+  </si>
+  <si>
+    <t>135984847</t>
+  </si>
+  <si>
+    <t>135810751</t>
+  </si>
+  <si>
+    <t>135931553</t>
+  </si>
+  <si>
+    <t>136008653</t>
+  </si>
+  <si>
+    <t>135675314</t>
+  </si>
+  <si>
+    <t>135823809</t>
+  </si>
+  <si>
+    <t>136012125</t>
+  </si>
+  <si>
+    <t>135951435</t>
+  </si>
+  <si>
+    <t>135987706</t>
+  </si>
+  <si>
+    <t>135985532</t>
+  </si>
+  <si>
+    <t>130805901</t>
+  </si>
+  <si>
+    <t>130715916</t>
+  </si>
+  <si>
+    <t>135759795</t>
+  </si>
+  <si>
+    <t>136030920</t>
+  </si>
+  <si>
+    <t>136031310</t>
+  </si>
+  <si>
+    <t>130937428</t>
+  </si>
+  <si>
+    <t>135811417</t>
+  </si>
+  <si>
+    <t>131116751</t>
+  </si>
+  <si>
+    <t>133982654</t>
+  </si>
+  <si>
+    <t>136036923</t>
+  </si>
+  <si>
+    <t>134978311</t>
+  </si>
+  <si>
+    <t>131367190</t>
+  </si>
+  <si>
+    <t>130764555</t>
+  </si>
+  <si>
+    <t>136026905</t>
+  </si>
+  <si>
+    <t>135713364</t>
+  </si>
+  <si>
+    <t>135989236</t>
+  </si>
+  <si>
+    <t>135624817</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 29.12.2025</t>
   </si>
 </sst>
 </file>
@@ -516,7 +606,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -557,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -575,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -593,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -611,7 +701,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -629,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -647,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -665,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -683,7 +773,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -701,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -719,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -737,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -755,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -773,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -791,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -809,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -827,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -845,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -863,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -881,7 +971,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -899,7 +989,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -917,51 +1007,552 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -977,31 +1568,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF81CF53-1AA5-4A67-9E35-37AC3FB63300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE58EA46-957B-4903-8CF2-8098D81A3133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="48">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,163 +54,124 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135788133</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 29.12.2025</t>
-  </si>
-  <si>
-    <t>135989526</t>
-  </si>
-  <si>
-    <t>131041743</t>
-  </si>
-  <si>
-    <t>135980698</t>
-  </si>
-  <si>
-    <t>136010770</t>
-  </si>
-  <si>
-    <t>135823351</t>
-  </si>
-  <si>
-    <t>136010858</t>
-  </si>
-  <si>
-    <t>136030486</t>
-  </si>
-  <si>
-    <t>135657152</t>
-  </si>
-  <si>
-    <t>131062403</t>
-  </si>
-  <si>
-    <t>135698032</t>
-  </si>
-  <si>
-    <t>130864230</t>
-  </si>
-  <si>
-    <t>135898563</t>
-  </si>
-  <si>
-    <t>135823743</t>
-  </si>
-  <si>
-    <t>135741722</t>
-  </si>
-  <si>
-    <t>135817473</t>
-  </si>
-  <si>
-    <t>135989585</t>
-  </si>
-  <si>
-    <t>136036835</t>
-  </si>
-  <si>
-    <t>130856076</t>
-  </si>
-  <si>
-    <t>136028594</t>
-  </si>
-  <si>
-    <t>135859018</t>
-  </si>
-  <si>
-    <t>130861348</t>
-  </si>
-  <si>
-    <t>135875575</t>
-  </si>
-  <si>
-    <t>136023323</t>
-  </si>
-  <si>
-    <t>135984847</t>
-  </si>
-  <si>
-    <t>135810751</t>
-  </si>
-  <si>
-    <t>135931553</t>
-  </si>
-  <si>
-    <t>136008653</t>
-  </si>
-  <si>
-    <t>135675314</t>
-  </si>
-  <si>
-    <t>135823809</t>
-  </si>
-  <si>
-    <t>136012125</t>
-  </si>
-  <si>
-    <t>135951435</t>
-  </si>
-  <si>
-    <t>135987706</t>
-  </si>
-  <si>
-    <t>135985532</t>
-  </si>
-  <si>
-    <t>130805901</t>
-  </si>
-  <si>
-    <t>130715916</t>
-  </si>
-  <si>
-    <t>135759795</t>
-  </si>
-  <si>
-    <t>136030920</t>
-  </si>
-  <si>
-    <t>136031310</t>
-  </si>
-  <si>
-    <t>130937428</t>
-  </si>
-  <si>
-    <t>135811417</t>
-  </si>
-  <si>
-    <t>131116751</t>
-  </si>
-  <si>
-    <t>133982654</t>
-  </si>
-  <si>
-    <t>136036923</t>
-  </si>
-  <si>
-    <t>134978311</t>
-  </si>
-  <si>
-    <t>131367190</t>
-  </si>
-  <si>
-    <t>130764555</t>
-  </si>
-  <si>
-    <t>136026905</t>
-  </si>
-  <si>
-    <t>135713364</t>
-  </si>
-  <si>
-    <t>135989236</t>
-  </si>
-  <si>
-    <t>135624817</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 29.12.2025</t>
+    <t>136036962</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 31.12.2025</t>
+  </si>
+  <si>
+    <t>135741648</t>
+  </si>
+  <si>
+    <t>136054456</t>
+  </si>
+  <si>
+    <t>135823376</t>
+  </si>
+  <si>
+    <t>135989477</t>
+  </si>
+  <si>
+    <t>130804545</t>
+  </si>
+  <si>
+    <t>136024604</t>
+  </si>
+  <si>
+    <t>136010668</t>
+  </si>
+  <si>
+    <t>135989035</t>
+  </si>
+  <si>
+    <t>135989066</t>
+  </si>
+  <si>
+    <t>130902979</t>
+  </si>
+  <si>
+    <t>136008550</t>
+  </si>
+  <si>
+    <t>136054602</t>
+  </si>
+  <si>
+    <t>136029946</t>
+  </si>
+  <si>
+    <t>135979952</t>
+  </si>
+  <si>
+    <t>136045371</t>
+  </si>
+  <si>
+    <t>136025478</t>
+  </si>
+  <si>
+    <t>136067408</t>
+  </si>
+  <si>
+    <t>135983939</t>
+  </si>
+  <si>
+    <t>130874754</t>
+  </si>
+  <si>
+    <t>136032999</t>
+  </si>
+  <si>
+    <t>136068924</t>
+  </si>
+  <si>
+    <t>136027642</t>
+  </si>
+  <si>
+    <t>136010910</t>
+  </si>
+  <si>
+    <t>135989442</t>
+  </si>
+  <si>
+    <t>135989184</t>
+  </si>
+  <si>
+    <t>130854531</t>
+  </si>
+  <si>
+    <t>136028957</t>
+  </si>
+  <si>
+    <t>130947014</t>
+  </si>
+  <si>
+    <t>131062074</t>
+  </si>
+  <si>
+    <t>136031709</t>
+  </si>
+  <si>
+    <t>135850530</t>
+  </si>
+  <si>
+    <t>136028454</t>
+  </si>
+  <si>
+    <t>136032105</t>
+  </si>
+  <si>
+    <t>131109574</t>
+  </si>
+  <si>
+    <t>135787331</t>
+  </si>
+  <si>
+    <t>134168130</t>
+  </si>
+  <si>
+    <t>134905266</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 31.12.2025</t>
   </si>
 </sst>
 </file>
@@ -606,7 +567,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -647,7 +608,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -665,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -683,7 +644,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -701,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -719,7 +680,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -737,7 +698,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -755,7 +716,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -773,7 +734,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -791,7 +752,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -809,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -827,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -845,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -863,7 +824,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -881,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -899,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -917,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -935,7 +896,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -953,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -971,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -989,7 +950,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1007,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1025,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1004,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1079,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1094,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1112,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1130,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1148,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1205,7 +1166,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1223,7 +1184,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1241,7 +1202,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1259,7 +1220,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1276,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1293,7 +1254,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1301,7 +1262,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1310,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1318,7 +1279,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1327,230 +1288,9 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1568,31 +1308,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2896B6D3-5125-4B7D-985E-975AD14C2006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60F0BBD-8A74-4587-BA56-DB30F7E9ADBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="73">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,199 @@
     <t>1070</t>
   </si>
   <si>
-    <t>136057393</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 02.01.2026</t>
-  </si>
-  <si>
-    <t>135693547</t>
-  </si>
-  <si>
-    <t>135989559</t>
-  </si>
-  <si>
-    <t>136076697</t>
-  </si>
-  <si>
-    <t>131017510</t>
-  </si>
-  <si>
-    <t>136078065</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 02.01.2026</t>
+    <t>136077855</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.01.2026</t>
+  </si>
+  <si>
+    <t>136071618</t>
+  </si>
+  <si>
+    <t>136010947</t>
+  </si>
+  <si>
+    <t>136066694</t>
+  </si>
+  <si>
+    <t>136022313</t>
+  </si>
+  <si>
+    <t>135675808</t>
+  </si>
+  <si>
+    <t>136037019</t>
+  </si>
+  <si>
+    <t>130952250</t>
+  </si>
+  <si>
+    <t>136078015</t>
+  </si>
+  <si>
+    <t>131093218</t>
+  </si>
+  <si>
+    <t>131163735</t>
+  </si>
+  <si>
+    <t>136078047</t>
+  </si>
+  <si>
+    <t>136030636</t>
+  </si>
+  <si>
+    <t>136077821</t>
+  </si>
+  <si>
+    <t>131081850</t>
+  </si>
+  <si>
+    <t>136010951</t>
+  </si>
+  <si>
+    <t>135990486</t>
+  </si>
+  <si>
+    <t>136042833</t>
+  </si>
+  <si>
+    <t>136097099</t>
+  </si>
+  <si>
+    <t>131030567</t>
+  </si>
+  <si>
+    <t>130863544</t>
+  </si>
+  <si>
+    <t>131067588</t>
+  </si>
+  <si>
+    <t>136032949</t>
+  </si>
+  <si>
+    <t>136062948</t>
+  </si>
+  <si>
+    <t>135989321</t>
+  </si>
+  <si>
+    <t>135989523</t>
+  </si>
+  <si>
+    <t>131073081</t>
+  </si>
+  <si>
+    <t>136077945</t>
+  </si>
+  <si>
+    <t>135286056</t>
+  </si>
+  <si>
+    <t>136078064</t>
+  </si>
+  <si>
+    <t>136078275</t>
+  </si>
+  <si>
+    <t>136025054</t>
+  </si>
+  <si>
+    <t>130825621</t>
+  </si>
+  <si>
+    <t>130798767</t>
+  </si>
+  <si>
+    <t>130842720</t>
+  </si>
+  <si>
+    <t>135989465</t>
+  </si>
+  <si>
+    <t>135981995</t>
+  </si>
+  <si>
+    <t>135980666</t>
+  </si>
+  <si>
+    <t>136084942</t>
+  </si>
+  <si>
+    <t>136037643</t>
+  </si>
+  <si>
+    <t>136046963</t>
+  </si>
+  <si>
+    <t>136085559</t>
+  </si>
+  <si>
+    <t>135989573</t>
+  </si>
+  <si>
+    <t>136045509</t>
+  </si>
+  <si>
+    <t>135701936</t>
+  </si>
+  <si>
+    <t>135556110</t>
+  </si>
+  <si>
+    <t>136025901</t>
+  </si>
+  <si>
+    <t>136028197</t>
+  </si>
+  <si>
+    <t>130958138</t>
+  </si>
+  <si>
+    <t>133948859</t>
+  </si>
+  <si>
+    <t>136010666</t>
+  </si>
+  <si>
+    <t>136048906</t>
+  </si>
+  <si>
+    <t>136036834</t>
+  </si>
+  <si>
+    <t>136028962</t>
+  </si>
+  <si>
+    <t>136033535</t>
+  </si>
+  <si>
+    <t>136077893</t>
+  </si>
+  <si>
+    <t>131022266</t>
+  </si>
+  <si>
+    <t>135989122</t>
+  </si>
+  <si>
+    <t>136085467</t>
+  </si>
+  <si>
+    <t>136024875</t>
+  </si>
+  <si>
+    <t>136060331</t>
+  </si>
+  <si>
+    <t>133841565</t>
+  </si>
+  <si>
+    <t>135989809</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 05.01.2026</t>
   </si>
 </sst>
 </file>
@@ -471,7 +642,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -512,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -530,7 +701,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -548,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -584,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -602,96 +773,1009 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -707,31 +1791,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60F0BBD-8A74-4587-BA56-DB30F7E9ADBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238BFD67-16DE-4518-A0BA-EE9382DAB373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="54">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,199 +54,142 @@
     <t>1070</t>
   </si>
   <si>
-    <t>136077855</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 05.01.2026</t>
-  </si>
-  <si>
-    <t>136071618</t>
-  </si>
-  <si>
-    <t>136010947</t>
-  </si>
-  <si>
-    <t>136066694</t>
-  </si>
-  <si>
-    <t>136022313</t>
-  </si>
-  <si>
-    <t>135675808</t>
-  </si>
-  <si>
-    <t>136037019</t>
-  </si>
-  <si>
-    <t>130952250</t>
-  </si>
-  <si>
-    <t>136078015</t>
-  </si>
-  <si>
-    <t>131093218</t>
-  </si>
-  <si>
-    <t>131163735</t>
-  </si>
-  <si>
-    <t>136078047</t>
-  </si>
-  <si>
-    <t>136030636</t>
-  </si>
-  <si>
-    <t>136077821</t>
-  </si>
-  <si>
-    <t>131081850</t>
-  </si>
-  <si>
-    <t>136010951</t>
-  </si>
-  <si>
-    <t>135990486</t>
-  </si>
-  <si>
-    <t>136042833</t>
-  </si>
-  <si>
-    <t>136097099</t>
-  </si>
-  <si>
-    <t>131030567</t>
-  </si>
-  <si>
-    <t>130863544</t>
-  </si>
-  <si>
-    <t>131067588</t>
-  </si>
-  <si>
-    <t>136032949</t>
-  </si>
-  <si>
-    <t>136062948</t>
-  </si>
-  <si>
-    <t>135989321</t>
-  </si>
-  <si>
-    <t>135989523</t>
-  </si>
-  <si>
-    <t>131073081</t>
-  </si>
-  <si>
-    <t>136077945</t>
-  </si>
-  <si>
-    <t>135286056</t>
-  </si>
-  <si>
-    <t>136078064</t>
-  </si>
-  <si>
-    <t>136078275</t>
-  </si>
-  <si>
-    <t>136025054</t>
-  </si>
-  <si>
-    <t>130825621</t>
-  </si>
-  <si>
-    <t>130798767</t>
-  </si>
-  <si>
-    <t>130842720</t>
-  </si>
-  <si>
-    <t>135989465</t>
-  </si>
-  <si>
-    <t>135981995</t>
-  </si>
-  <si>
-    <t>135980666</t>
-  </si>
-  <si>
-    <t>136084942</t>
-  </si>
-  <si>
-    <t>136037643</t>
-  </si>
-  <si>
-    <t>136046963</t>
-  </si>
-  <si>
-    <t>136085559</t>
-  </si>
-  <si>
-    <t>135989573</t>
-  </si>
-  <si>
-    <t>136045509</t>
-  </si>
-  <si>
-    <t>135701936</t>
-  </si>
-  <si>
-    <t>135556110</t>
-  </si>
-  <si>
-    <t>136025901</t>
-  </si>
-  <si>
-    <t>136028197</t>
-  </si>
-  <si>
-    <t>130958138</t>
-  </si>
-  <si>
-    <t>133948859</t>
-  </si>
-  <si>
-    <t>136010666</t>
-  </si>
-  <si>
-    <t>136048906</t>
-  </si>
-  <si>
-    <t>136036834</t>
-  </si>
-  <si>
-    <t>136028962</t>
-  </si>
-  <si>
-    <t>136033535</t>
-  </si>
-  <si>
-    <t>136077893</t>
-  </si>
-  <si>
-    <t>131022266</t>
-  </si>
-  <si>
-    <t>135989122</t>
-  </si>
-  <si>
-    <t>136085467</t>
-  </si>
-  <si>
-    <t>136024875</t>
-  </si>
-  <si>
-    <t>136060331</t>
-  </si>
-  <si>
-    <t>133841565</t>
-  </si>
-  <si>
-    <t>135989809</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 05.01.2026</t>
+    <t>136078171</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 06.01.2026</t>
+  </si>
+  <si>
+    <t>130962151</t>
+  </si>
+  <si>
+    <t>135600351</t>
+  </si>
+  <si>
+    <t>130841591</t>
+  </si>
+  <si>
+    <t>136060851</t>
+  </si>
+  <si>
+    <t>131101418</t>
+  </si>
+  <si>
+    <t>131205285</t>
+  </si>
+  <si>
+    <t>136050258</t>
+  </si>
+  <si>
+    <t>136077975</t>
+  </si>
+  <si>
+    <t>136077917</t>
+  </si>
+  <si>
+    <t>136077765</t>
+  </si>
+  <si>
+    <t>130815885</t>
+  </si>
+  <si>
+    <t>136025659</t>
+  </si>
+  <si>
+    <t>135981500</t>
+  </si>
+  <si>
+    <t>136032853</t>
+  </si>
+  <si>
+    <t>135977005</t>
+  </si>
+  <si>
+    <t>131135063</t>
+  </si>
+  <si>
+    <t>135988919</t>
+  </si>
+  <si>
+    <t>136102206</t>
+  </si>
+  <si>
+    <t>130801806</t>
+  </si>
+  <si>
+    <t>136077952</t>
+  </si>
+  <si>
+    <t>135988636</t>
+  </si>
+  <si>
+    <t>136092530</t>
+  </si>
+  <si>
+    <t>131092090</t>
+  </si>
+  <si>
+    <t>136010859</t>
+  </si>
+  <si>
+    <t>134857751</t>
+  </si>
+  <si>
+    <t>136077985</t>
+  </si>
+  <si>
+    <t>130924880</t>
+  </si>
+  <si>
+    <t>136103065</t>
+  </si>
+  <si>
+    <t>135989458</t>
+  </si>
+  <si>
+    <t>136100305</t>
+  </si>
+  <si>
+    <t>133268555</t>
+  </si>
+  <si>
+    <t>136010834</t>
+  </si>
+  <si>
+    <t>136077912</t>
+  </si>
+  <si>
+    <t>136092590</t>
+  </si>
+  <si>
+    <t>131017397</t>
+  </si>
+  <si>
+    <t>132599688</t>
+  </si>
+  <si>
+    <t>135821343</t>
+  </si>
+  <si>
+    <t>136058203</t>
+  </si>
+  <si>
+    <t>136032042</t>
+  </si>
+  <si>
+    <t>136010933</t>
+  </si>
+  <si>
+    <t>133464860</t>
+  </si>
+  <si>
+    <t>136062995</t>
+  </si>
+  <si>
+    <t>135713221</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 06.01.2026</t>
   </si>
 </sst>
 </file>
@@ -642,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -683,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -701,7 +644,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -719,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -737,7 +680,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -755,7 +698,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -773,7 +716,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -791,7 +734,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -809,7 +752,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -827,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -845,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -863,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -881,7 +824,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -899,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -917,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -935,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -953,7 +896,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -971,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -989,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1007,7 +950,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1025,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1043,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1004,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1079,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1094,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1112,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1130,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1205,7 +1148,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1223,7 +1166,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1241,7 +1184,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1259,7 +1202,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1277,7 +1220,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1295,7 +1238,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1303,7 +1246,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1312,7 +1255,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1320,7 +1263,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1329,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1337,7 +1280,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1346,7 +1289,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1354,7 +1297,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1363,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1371,7 +1314,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -1380,7 +1323,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1388,7 +1331,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
@@ -1397,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1405,7 +1348,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -1414,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1422,7 +1365,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
@@ -1431,7 +1374,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1439,7 +1382,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
@@ -1448,7 +1391,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1456,7 +1399,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
@@ -1465,315 +1408,9 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1791,31 +1428,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238BFD67-16DE-4518-A0BA-EE9382DAB373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDE99D7-A191-44D6-84E4-C6374BD86F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,142 +54,145 @@
     <t>1070</t>
   </si>
   <si>
-    <t>136078171</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 06.01.2026</t>
-  </si>
-  <si>
-    <t>130962151</t>
-  </si>
-  <si>
-    <t>135600351</t>
-  </si>
-  <si>
-    <t>130841591</t>
-  </si>
-  <si>
-    <t>136060851</t>
-  </si>
-  <si>
-    <t>131101418</t>
-  </si>
-  <si>
-    <t>131205285</t>
-  </si>
-  <si>
-    <t>136050258</t>
-  </si>
-  <si>
-    <t>136077975</t>
-  </si>
-  <si>
-    <t>136077917</t>
-  </si>
-  <si>
-    <t>136077765</t>
-  </si>
-  <si>
-    <t>130815885</t>
-  </si>
-  <si>
-    <t>136025659</t>
-  </si>
-  <si>
-    <t>135981500</t>
-  </si>
-  <si>
-    <t>136032853</t>
-  </si>
-  <si>
-    <t>135977005</t>
-  </si>
-  <si>
-    <t>131135063</t>
-  </si>
-  <si>
-    <t>135988919</t>
-  </si>
-  <si>
-    <t>136102206</t>
-  </si>
-  <si>
-    <t>130801806</t>
-  </si>
-  <si>
-    <t>136077952</t>
-  </si>
-  <si>
-    <t>135988636</t>
-  </si>
-  <si>
-    <t>136092530</t>
-  </si>
-  <si>
-    <t>131092090</t>
-  </si>
-  <si>
-    <t>136010859</t>
-  </si>
-  <si>
-    <t>134857751</t>
-  </si>
-  <si>
-    <t>136077985</t>
-  </si>
-  <si>
-    <t>130924880</t>
-  </si>
-  <si>
-    <t>136103065</t>
-  </si>
-  <si>
-    <t>135989458</t>
-  </si>
-  <si>
-    <t>136100305</t>
-  </si>
-  <si>
-    <t>133268555</t>
-  </si>
-  <si>
-    <t>136010834</t>
-  </si>
-  <si>
-    <t>136077912</t>
-  </si>
-  <si>
-    <t>136092590</t>
-  </si>
-  <si>
-    <t>131017397</t>
-  </si>
-  <si>
-    <t>132599688</t>
-  </si>
-  <si>
-    <t>135821343</t>
-  </si>
-  <si>
-    <t>136058203</t>
-  </si>
-  <si>
-    <t>136032042</t>
-  </si>
-  <si>
     <t>136010933</t>
   </si>
   <si>
-    <t>133464860</t>
-  </si>
-  <si>
-    <t>136062995</t>
-  </si>
-  <si>
-    <t>135713221</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 06.01.2026</t>
+    <t>136010937</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 07.01.2026</t>
+  </si>
+  <si>
+    <t>130906499</t>
+  </si>
+  <si>
+    <t>136056852</t>
+  </si>
+  <si>
+    <t>136106420</t>
+  </si>
+  <si>
+    <t>135989545</t>
+  </si>
+  <si>
+    <t>136026603</t>
+  </si>
+  <si>
+    <t>136103486</t>
+  </si>
+  <si>
+    <t>131167854</t>
+  </si>
+  <si>
+    <t>136092691</t>
+  </si>
+  <si>
+    <t>136043333</t>
+  </si>
+  <si>
+    <t>135978810</t>
+  </si>
+  <si>
+    <t>136060629</t>
+  </si>
+  <si>
+    <t>136036958</t>
+  </si>
+  <si>
+    <t>136092550</t>
+  </si>
+  <si>
+    <t>130842083</t>
+  </si>
+  <si>
+    <t>131018330</t>
+  </si>
+  <si>
+    <t>136030407</t>
+  </si>
+  <si>
+    <t>130918727</t>
+  </si>
+  <si>
+    <t>136058792</t>
+  </si>
+  <si>
+    <t>136077930</t>
+  </si>
+  <si>
+    <t>136010963</t>
+  </si>
+  <si>
+    <t>136036828</t>
+  </si>
+  <si>
+    <t>136036975</t>
+  </si>
+  <si>
+    <t>135989261</t>
+  </si>
+  <si>
+    <t>135989553</t>
+  </si>
+  <si>
+    <t>131176872</t>
+  </si>
+  <si>
+    <t>131059331</t>
+  </si>
+  <si>
+    <t>135989542</t>
+  </si>
+  <si>
+    <t>136077876</t>
+  </si>
+  <si>
+    <t>136077769</t>
+  </si>
+  <si>
+    <t>131243520</t>
+  </si>
+  <si>
+    <t>136129045</t>
+  </si>
+  <si>
+    <t>130877899</t>
+  </si>
+  <si>
+    <t>136061916</t>
+  </si>
+  <si>
+    <t>136078022</t>
+  </si>
+  <si>
+    <t>136013155</t>
+  </si>
+  <si>
+    <t>134518866</t>
+  </si>
+  <si>
+    <t>131095174</t>
+  </si>
+  <si>
+    <t>135213445</t>
+  </si>
+  <si>
+    <t>136037002</t>
+  </si>
+  <si>
+    <t>134567879</t>
+  </si>
+  <si>
+    <t>134388747</t>
+  </si>
+  <si>
+    <t>136078076</t>
+  </si>
+  <si>
+    <t>136099174</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 07.01.2026</t>
   </si>
 </sst>
 </file>
@@ -617,16 +620,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -635,16 +638,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -653,16 +656,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -671,16 +674,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -689,16 +692,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -707,16 +710,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -725,16 +728,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -749,10 +752,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -767,10 +770,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -785,10 +788,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -803,10 +806,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -821,10 +824,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -839,10 +842,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -857,10 +860,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -875,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -893,10 +896,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -911,10 +914,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -929,10 +932,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -947,10 +950,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,10 +968,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -983,10 +986,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1001,10 +1004,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1019,10 +1022,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1037,10 +1040,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1055,10 +1058,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1073,10 +1076,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1091,10 +1094,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1109,10 +1112,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1127,10 +1130,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1145,10 +1148,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1163,10 +1166,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1181,10 +1184,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1199,10 +1202,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1217,10 +1220,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1235,10 +1238,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1246,16 +1249,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1263,16 +1266,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1280,16 +1283,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1297,16 +1300,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1314,16 +1317,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1331,16 +1334,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1348,16 +1351,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1365,16 +1368,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1382,16 +1385,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1399,16 +1402,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1428,31 +1431,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDE99D7-A191-44D6-84E4-C6374BD86F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267DDB69-63D4-422A-8E39-EBAD846DA8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="48">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,145 +54,124 @@
     <t>1070</t>
   </si>
   <si>
-    <t>136010933</t>
-  </si>
-  <si>
-    <t>136010937</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 07.01.2026</t>
-  </si>
-  <si>
-    <t>130906499</t>
-  </si>
-  <si>
-    <t>136056852</t>
-  </si>
-  <si>
-    <t>136106420</t>
-  </si>
-  <si>
-    <t>135989545</t>
-  </si>
-  <si>
-    <t>136026603</t>
-  </si>
-  <si>
-    <t>136103486</t>
-  </si>
-  <si>
-    <t>131167854</t>
-  </si>
-  <si>
-    <t>136092691</t>
-  </si>
-  <si>
-    <t>136043333</t>
-  </si>
-  <si>
-    <t>135978810</t>
-  </si>
-  <si>
-    <t>136060629</t>
-  </si>
-  <si>
-    <t>136036958</t>
-  </si>
-  <si>
-    <t>136092550</t>
-  </si>
-  <si>
     <t>130842083</t>
   </si>
   <si>
-    <t>131018330</t>
-  </si>
-  <si>
-    <t>136030407</t>
-  </si>
-  <si>
-    <t>130918727</t>
-  </si>
-  <si>
-    <t>136058792</t>
-  </si>
-  <si>
-    <t>136077930</t>
-  </si>
-  <si>
-    <t>136010963</t>
-  </si>
-  <si>
-    <t>136036828</t>
-  </si>
-  <si>
-    <t>136036975</t>
-  </si>
-  <si>
-    <t>135989261</t>
-  </si>
-  <si>
-    <t>135989553</t>
-  </si>
-  <si>
-    <t>131176872</t>
-  </si>
-  <si>
-    <t>131059331</t>
-  </si>
-  <si>
-    <t>135989542</t>
-  </si>
-  <si>
-    <t>136077876</t>
-  </si>
-  <si>
-    <t>136077769</t>
-  </si>
-  <si>
-    <t>131243520</t>
-  </si>
-  <si>
-    <t>136129045</t>
-  </si>
-  <si>
-    <t>130877899</t>
-  </si>
-  <si>
-    <t>136061916</t>
-  </si>
-  <si>
-    <t>136078022</t>
-  </si>
-  <si>
-    <t>136013155</t>
-  </si>
-  <si>
-    <t>134518866</t>
-  </si>
-  <si>
-    <t>131095174</t>
-  </si>
-  <si>
-    <t>135213445</t>
-  </si>
-  <si>
-    <t>136037002</t>
-  </si>
-  <si>
-    <t>134567879</t>
-  </si>
-  <si>
-    <t>134388747</t>
-  </si>
-  <si>
-    <t>136078076</t>
-  </si>
-  <si>
-    <t>136099174</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 07.01.2026</t>
+    <t>136092618</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 08.01.2026</t>
+  </si>
+  <si>
+    <t>130985800</t>
+  </si>
+  <si>
+    <t>135986551</t>
+  </si>
+  <si>
+    <t>136026208</t>
+  </si>
+  <si>
+    <t>136037013</t>
+  </si>
+  <si>
+    <t>136169567</t>
+  </si>
+  <si>
+    <t>135989355</t>
+  </si>
+  <si>
+    <t>130753536</t>
+  </si>
+  <si>
+    <t>136109209</t>
+  </si>
+  <si>
+    <t>136162567</t>
+  </si>
+  <si>
+    <t>136025484</t>
+  </si>
+  <si>
+    <t>136092632</t>
+  </si>
+  <si>
+    <t>135533444</t>
+  </si>
+  <si>
+    <t>130930820</t>
+  </si>
+  <si>
+    <t>136036953</t>
+  </si>
+  <si>
+    <t>136058288</t>
+  </si>
+  <si>
+    <t>136010902</t>
+  </si>
+  <si>
+    <t>136010776</t>
+  </si>
+  <si>
+    <t>135710687</t>
+  </si>
+  <si>
+    <t>136119522</t>
+  </si>
+  <si>
+    <t>136131511</t>
+  </si>
+  <si>
+    <t>130907601</t>
+  </si>
+  <si>
+    <t>131061990</t>
+  </si>
+  <si>
+    <t>136162346</t>
+  </si>
+  <si>
+    <t>136047559</t>
+  </si>
+  <si>
+    <t>136010920</t>
+  </si>
+  <si>
+    <t>130979078</t>
+  </si>
+  <si>
+    <t>136102596</t>
+  </si>
+  <si>
+    <t>136077941</t>
+  </si>
+  <si>
+    <t>136048497</t>
+  </si>
+  <si>
+    <t>136014125</t>
+  </si>
+  <si>
+    <t>136063712</t>
+  </si>
+  <si>
+    <t>136081473</t>
+  </si>
+  <si>
+    <t>135989551</t>
+  </si>
+  <si>
+    <t>131841184</t>
+  </si>
+  <si>
+    <t>136077898</t>
+  </si>
+  <si>
+    <t>136135631</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 08.01.2026</t>
   </si>
 </sst>
 </file>
@@ -588,7 +567,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -629,7 +608,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -647,7 +626,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -665,7 +644,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -683,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -701,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -719,7 +698,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,7 +707,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -737,7 +716,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -746,7 +725,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -755,7 +734,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -764,7 +743,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -773,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -782,7 +761,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -791,7 +770,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -800,7 +779,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -809,7 +788,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -818,7 +797,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -827,7 +806,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -836,7 +815,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -845,7 +824,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -854,7 +833,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -863,7 +842,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -872,7 +851,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -881,7 +860,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -890,7 +869,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -899,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -908,7 +887,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -917,7 +896,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -926,7 +905,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -935,7 +914,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -944,7 +923,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -953,7 +932,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -962,7 +941,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -971,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -980,7 +959,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -989,7 +968,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -998,7 +977,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -1007,7 +986,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,7 +995,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1025,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1013,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1043,7 +1022,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1031,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1061,7 +1040,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1049,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1079,7 +1058,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1067,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1097,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1085,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1115,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1130,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1148,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1166,7 @@
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1205,7 +1184,7 @@
         <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1223,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1241,7 +1220,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1258,7 +1237,7 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1275,7 +1254,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1292,128 +1271,9 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1431,31 +1291,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267DDB69-63D4-422A-8E39-EBAD846DA8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20E13D0-446E-4E13-8B4A-5A7371623C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="60">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,124 +54,160 @@
     <t>1070</t>
   </si>
   <si>
-    <t>130842083</t>
-  </si>
-  <si>
-    <t>136092618</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 08.01.2026</t>
-  </si>
-  <si>
-    <t>130985800</t>
-  </si>
-  <si>
-    <t>135986551</t>
-  </si>
-  <si>
-    <t>136026208</t>
-  </si>
-  <si>
-    <t>136037013</t>
-  </si>
-  <si>
-    <t>136169567</t>
-  </si>
-  <si>
-    <t>135989355</t>
-  </si>
-  <si>
-    <t>130753536</t>
-  </si>
-  <si>
-    <t>136109209</t>
-  </si>
-  <si>
-    <t>136162567</t>
-  </si>
-  <si>
-    <t>136025484</t>
-  </si>
-  <si>
-    <t>136092632</t>
-  </si>
-  <si>
-    <t>135533444</t>
-  </si>
-  <si>
-    <t>130930820</t>
-  </si>
-  <si>
-    <t>136036953</t>
-  </si>
-  <si>
-    <t>136058288</t>
-  </si>
-  <si>
-    <t>136010902</t>
-  </si>
-  <si>
-    <t>136010776</t>
-  </si>
-  <si>
-    <t>135710687</t>
-  </si>
-  <si>
-    <t>136119522</t>
-  </si>
-  <si>
-    <t>136131511</t>
-  </si>
-  <si>
-    <t>130907601</t>
-  </si>
-  <si>
-    <t>131061990</t>
-  </si>
-  <si>
-    <t>136162346</t>
-  </si>
-  <si>
-    <t>136047559</t>
-  </si>
-  <si>
-    <t>136010920</t>
-  </si>
-  <si>
-    <t>130979078</t>
-  </si>
-  <si>
-    <t>136102596</t>
-  </si>
-  <si>
-    <t>136077941</t>
-  </si>
-  <si>
-    <t>136048497</t>
-  </si>
-  <si>
-    <t>136014125</t>
-  </si>
-  <si>
-    <t>136063712</t>
-  </si>
-  <si>
-    <t>136081473</t>
-  </si>
-  <si>
-    <t>135989551</t>
-  </si>
-  <si>
-    <t>131841184</t>
-  </si>
-  <si>
-    <t>136077898</t>
-  </si>
-  <si>
-    <t>136135631</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 08.01.2026</t>
+    <t>136044447</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 09.01.2026</t>
+  </si>
+  <si>
+    <t>136044939</t>
+  </si>
+  <si>
+    <t>136078166</t>
+  </si>
+  <si>
+    <t>131055504</t>
+  </si>
+  <si>
+    <t>136022997</t>
+  </si>
+  <si>
+    <t>136139635</t>
+  </si>
+  <si>
+    <t>135988857</t>
+  </si>
+  <si>
+    <t>136078038</t>
+  </si>
+  <si>
+    <t>130918252</t>
+  </si>
+  <si>
+    <t>136077915</t>
+  </si>
+  <si>
+    <t>130804139</t>
+  </si>
+  <si>
+    <t>136112701</t>
+  </si>
+  <si>
+    <t>136062944</t>
+  </si>
+  <si>
+    <t>136057712</t>
+  </si>
+  <si>
+    <t>135979280</t>
+  </si>
+  <si>
+    <t>131373260</t>
+  </si>
+  <si>
+    <t>136063555</t>
+  </si>
+  <si>
+    <t>136010687</t>
+  </si>
+  <si>
+    <t>135123193</t>
+  </si>
+  <si>
+    <t>130887366</t>
+  </si>
+  <si>
+    <t>136067258</t>
+  </si>
+  <si>
+    <t>136072571</t>
+  </si>
+  <si>
+    <t>136010798</t>
+  </si>
+  <si>
+    <t>131139453</t>
+  </si>
+  <si>
+    <t>131017963</t>
+  </si>
+  <si>
+    <t>135892725</t>
+  </si>
+  <si>
+    <t>130919943</t>
+  </si>
+  <si>
+    <t>135850575</t>
+  </si>
+  <si>
+    <t>136036888</t>
+  </si>
+  <si>
+    <t>130942722</t>
+  </si>
+  <si>
+    <t>136141649</t>
+  </si>
+  <si>
+    <t>131129113</t>
+  </si>
+  <si>
+    <t>130949134</t>
+  </si>
+  <si>
+    <t>136129330</t>
+  </si>
+  <si>
+    <t>136027790</t>
+  </si>
+  <si>
+    <t>136057640</t>
+  </si>
+  <si>
+    <t>136015860</t>
+  </si>
+  <si>
+    <t>131207651</t>
+  </si>
+  <si>
+    <t>136099894</t>
+  </si>
+  <si>
+    <t>136010874</t>
+  </si>
+  <si>
+    <t>136077852</t>
+  </si>
+  <si>
+    <t>131211096</t>
+  </si>
+  <si>
+    <t>135989537</t>
+  </si>
+  <si>
+    <t>136163327</t>
+  </si>
+  <si>
+    <t>130932442</t>
+  </si>
+  <si>
+    <t>135989453</t>
+  </si>
+  <si>
+    <t>131048505</t>
+  </si>
+  <si>
+    <t>135231011</t>
+  </si>
+  <si>
+    <t>130777571</t>
+  </si>
+  <si>
+    <t>134359310</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 09.01.2026</t>
   </si>
 </sst>
 </file>
@@ -567,7 +603,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -599,16 +635,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -617,16 +653,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -635,16 +671,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -653,16 +689,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -671,16 +707,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -689,16 +725,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,16 +743,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -725,16 +761,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -743,16 +779,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -761,16 +797,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -779,16 +815,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -797,16 +833,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -815,16 +851,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -833,16 +869,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -851,16 +887,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -869,16 +905,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -887,16 +923,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -905,16 +941,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -923,16 +959,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -941,16 +977,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -959,16 +995,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -977,16 +1013,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -995,16 +1031,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1013,16 +1049,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1031,16 +1067,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1049,16 +1085,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1067,16 +1103,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1085,16 +1121,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1109,10 +1145,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1127,10 +1163,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1145,10 +1181,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1163,10 +1199,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1181,10 +1217,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1199,10 +1235,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1217,10 +1253,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1234,10 +1270,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1251,10 +1287,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1268,12 +1304,233 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1291,31 +1548,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20E13D0-446E-4E13-8B4A-5A7371623C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D2C60-A66B-4C21-9C8D-69AF3E6A0C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="106">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,6 +54,144 @@
     <t>1070</t>
   </si>
   <si>
+    <t>135984364</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 12.01.2026</t>
+  </si>
+  <si>
+    <t>131070144</t>
+  </si>
+  <si>
+    <t>136129551</t>
+  </si>
+  <si>
+    <t>136010909</t>
+  </si>
+  <si>
+    <t>136077802</t>
+  </si>
+  <si>
+    <t>136077911</t>
+  </si>
+  <si>
+    <t>136010823</t>
+  </si>
+  <si>
+    <t>136046700</t>
+  </si>
+  <si>
+    <t>136078050</t>
+  </si>
+  <si>
+    <t>130962056</t>
+  </si>
+  <si>
+    <t>136010671</t>
+  </si>
+  <si>
+    <t>136137607</t>
+  </si>
+  <si>
+    <t>136072543</t>
+  </si>
+  <si>
+    <t>135988860</t>
+  </si>
+  <si>
+    <t>135989142</t>
+  </si>
+  <si>
+    <t>136054808</t>
+  </si>
+  <si>
+    <t>130911253</t>
+  </si>
+  <si>
+    <t>136010817</t>
+  </si>
+  <si>
+    <t>136078071</t>
+  </si>
+  <si>
+    <t>136077858</t>
+  </si>
+  <si>
+    <t>136117434</t>
+  </si>
+  <si>
+    <t>136036950</t>
+  </si>
+  <si>
+    <t>136077909</t>
+  </si>
+  <si>
+    <t>131113367</t>
+  </si>
+  <si>
+    <t>136024636</t>
+  </si>
+  <si>
+    <t>136152318</t>
+  </si>
+  <si>
+    <t>136010758</t>
+  </si>
+  <si>
+    <t>135783001</t>
+  </si>
+  <si>
+    <t>130978318</t>
+  </si>
+  <si>
+    <t>135977303</t>
+  </si>
+  <si>
+    <t>130748754</t>
+  </si>
+  <si>
+    <t>136068660</t>
+  </si>
+  <si>
+    <t>136134815</t>
+  </si>
+  <si>
+    <t>134622619</t>
+  </si>
+  <si>
+    <t>131112824</t>
+  </si>
+  <si>
+    <t>136167643</t>
+  </si>
+  <si>
+    <t>131584718</t>
+  </si>
+  <si>
+    <t>135627560</t>
+  </si>
+  <si>
+    <t>136077903</t>
+  </si>
+  <si>
+    <t>136108871</t>
+  </si>
+  <si>
+    <t>136136884</t>
+  </si>
+  <si>
+    <t>135744809</t>
+  </si>
+  <si>
+    <t>133500646</t>
+  </si>
+  <si>
+    <t>136050666</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 12.01.2026</t>
+  </si>
+  <si>
     <t>136044447</t>
   </si>
   <si>
@@ -207,7 +345,7 @@
     <t>134359310</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 09.01.2026</t>
+    <t>Allianz - Cancelamento 09.01.2026 (1)</t>
   </si>
 </sst>
 </file>
@@ -603,7 +741,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -644,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -662,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -680,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -698,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -716,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -734,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -752,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -770,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -788,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -806,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -824,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -842,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -860,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -878,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -896,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -914,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -932,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -950,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -968,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -986,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1004,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1022,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1040,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1058,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1076,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1130,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1148,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1166,7 +1304,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1184,7 +1322,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1202,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1220,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1238,7 +1376,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1256,7 +1394,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1273,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1290,7 +1428,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1307,7 +1445,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1324,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1341,7 +1479,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1358,7 +1496,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1375,7 +1513,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1392,7 +1530,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1409,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1417,16 +1555,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1434,16 +1572,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1451,16 +1589,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1468,16 +1606,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1485,16 +1623,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1502,16 +1640,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1519,18 +1657,766 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3091C9C9-41B1-464A-BF45-5B9187BAC152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6312C637-6512-4F6F-A8B3-8E0FB5AD90A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,94 +54,130 @@
     <t>1070</t>
   </si>
   <si>
-    <t>135783001</t>
-  </si>
-  <si>
-    <t>136108871</t>
-  </si>
-  <si>
-    <t>135252902</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 13.01.2026</t>
-  </si>
-  <si>
-    <t>136078030</t>
-  </si>
-  <si>
-    <t>130906510</t>
-  </si>
-  <si>
-    <t>135003437</t>
-  </si>
-  <si>
-    <t>135456265</t>
-  </si>
-  <si>
-    <t>131145726</t>
-  </si>
-  <si>
-    <t>131288926</t>
-  </si>
-  <si>
-    <t>136073167</t>
-  </si>
-  <si>
-    <t>136206060</t>
-  </si>
-  <si>
-    <t>136025155</t>
-  </si>
-  <si>
-    <t>130966921</t>
-  </si>
-  <si>
-    <t>136109668</t>
-  </si>
-  <si>
-    <t>130878817</t>
-  </si>
-  <si>
-    <t>136010905</t>
-  </si>
-  <si>
-    <t>136170958</t>
-  </si>
-  <si>
-    <t>131136135</t>
-  </si>
-  <si>
-    <t>131060906</t>
-  </si>
-  <si>
-    <t>131093742</t>
-  </si>
-  <si>
-    <t>131220288</t>
-  </si>
-  <si>
-    <t>136092697</t>
-  </si>
-  <si>
-    <t>135850379</t>
-  </si>
-  <si>
-    <t>136064490</t>
-  </si>
-  <si>
-    <t>134334222</t>
-  </si>
-  <si>
-    <t>136135786</t>
-  </si>
-  <si>
-    <t>135986855</t>
-  </si>
-  <si>
-    <t>136109245</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 13.01.2026</t>
+    <t>136010757</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 14.01.2026</t>
+  </si>
+  <si>
+    <t>136252093</t>
+  </si>
+  <si>
+    <t>136167525</t>
+  </si>
+  <si>
+    <t>135816840</t>
+  </si>
+  <si>
+    <t>136092511</t>
+  </si>
+  <si>
+    <t>136139910</t>
+  </si>
+  <si>
+    <t>136010891</t>
+  </si>
+  <si>
+    <t>136078044</t>
+  </si>
+  <si>
+    <t>136102411</t>
+  </si>
+  <si>
+    <t>136060816</t>
+  </si>
+  <si>
+    <t>130872355</t>
+  </si>
+  <si>
+    <t>131068243</t>
+  </si>
+  <si>
+    <t>136165161</t>
+  </si>
+  <si>
+    <t>136036879</t>
+  </si>
+  <si>
+    <t>131291950</t>
+  </si>
+  <si>
+    <t>136223496</t>
+  </si>
+  <si>
+    <t>130972526</t>
+  </si>
+  <si>
+    <t>136168444</t>
+  </si>
+  <si>
+    <t>136169709</t>
+  </si>
+  <si>
+    <t>136053761</t>
+  </si>
+  <si>
+    <t>136169426</t>
+  </si>
+  <si>
+    <t>136168788</t>
+  </si>
+  <si>
+    <t>136077868</t>
+  </si>
+  <si>
+    <t>136186278</t>
+  </si>
+  <si>
+    <t>136092562</t>
+  </si>
+  <si>
+    <t>130830714</t>
+  </si>
+  <si>
+    <t>136169330</t>
+  </si>
+  <si>
+    <t>136178204</t>
+  </si>
+  <si>
+    <t>136118081</t>
+  </si>
+  <si>
+    <t>130876358</t>
+  </si>
+  <si>
+    <t>136032813</t>
+  </si>
+  <si>
+    <t>136010694</t>
+  </si>
+  <si>
+    <t>133732536</t>
+  </si>
+  <si>
+    <t>136182606</t>
+  </si>
+  <si>
+    <t>136066877</t>
+  </si>
+  <si>
+    <t>132566681</t>
+  </si>
+  <si>
+    <t>136161447</t>
+  </si>
+  <si>
+    <t>136010817</t>
+  </si>
+  <si>
+    <t>136143625</t>
+  </si>
+  <si>
+    <t>136109182</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -537,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -569,16 +605,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -587,16 +623,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -605,16 +641,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,16 +659,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -641,16 +677,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -659,16 +695,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -677,16 +713,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -695,16 +731,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -713,16 +749,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -731,16 +767,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -749,16 +785,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -767,16 +803,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -785,16 +821,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,16 +839,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -827,10 +863,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,10 +881,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -863,10 +899,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -881,10 +917,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -899,10 +935,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -917,10 +953,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -935,10 +971,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -953,10 +989,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -971,10 +1007,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -989,10 +1025,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1001,16 +1037,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1019,16 +1055,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1037,16 +1073,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1055,16 +1091,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1073,21 +1109,208 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1103,31 +1326,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6312C637-6512-4F6F-A8B3-8E0FB5AD90A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,135 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>136010757</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 14.01.2026</t>
-  </si>
-  <si>
-    <t>136252093</t>
-  </si>
-  <si>
-    <t>136167525</t>
-  </si>
-  <si>
-    <t>135816840</t>
-  </si>
-  <si>
-    <t>136092511</t>
-  </si>
-  <si>
-    <t>136139910</t>
-  </si>
-  <si>
-    <t>136010891</t>
-  </si>
-  <si>
-    <t>136078044</t>
-  </si>
-  <si>
-    <t>136102411</t>
-  </si>
-  <si>
-    <t>136060816</t>
-  </si>
-  <si>
-    <t>130872355</t>
-  </si>
-  <si>
-    <t>131068243</t>
-  </si>
-  <si>
-    <t>136165161</t>
-  </si>
-  <si>
-    <t>136036879</t>
-  </si>
-  <si>
-    <t>131291950</t>
-  </si>
-  <si>
-    <t>136223496</t>
-  </si>
-  <si>
-    <t>130972526</t>
-  </si>
-  <si>
-    <t>136168444</t>
-  </si>
-  <si>
-    <t>136169709</t>
-  </si>
-  <si>
-    <t>136053761</t>
-  </si>
-  <si>
-    <t>136169426</t>
-  </si>
-  <si>
-    <t>136168788</t>
-  </si>
-  <si>
-    <t>136077868</t>
-  </si>
-  <si>
-    <t>136186278</t>
-  </si>
-  <si>
-    <t>136092562</t>
-  </si>
-  <si>
-    <t>130830714</t>
-  </si>
-  <si>
-    <t>136169330</t>
-  </si>
-  <si>
-    <t>136178204</t>
-  </si>
-  <si>
-    <t>136118081</t>
-  </si>
-  <si>
-    <t>130876358</t>
-  </si>
-  <si>
-    <t>136032813</t>
-  </si>
-  <si>
-    <t>136010694</t>
-  </si>
-  <si>
-    <t>133732536</t>
-  </si>
-  <si>
-    <t>136182606</t>
-  </si>
-  <si>
-    <t>136066877</t>
-  </si>
-  <si>
-    <t>132566681</t>
-  </si>
-  <si>
-    <t>136161447</t>
-  </si>
-  <si>
-    <t>136010817</t>
-  </si>
-  <si>
-    <t>136143625</t>
-  </si>
-  <si>
-    <t>136109182</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -573,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -604,711 +475,436 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CA3711-1C5A-4EA1-A2CB-6EA1B95C4F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="98">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,279 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136026628</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 15.01.2026</t>
+  </si>
+  <si>
+    <t>136077946</t>
+  </si>
+  <si>
+    <t>136077778</t>
+  </si>
+  <si>
+    <t>135989158</t>
+  </si>
+  <si>
+    <t>136030549</t>
+  </si>
+  <si>
+    <t>130939526</t>
+  </si>
+  <si>
+    <t>131012400</t>
+  </si>
+  <si>
+    <t>136168719</t>
+  </si>
+  <si>
+    <t>133349239</t>
+  </si>
+  <si>
+    <t>136077889</t>
+  </si>
+  <si>
+    <t>136168165</t>
+  </si>
+  <si>
+    <t>136010926</t>
+  </si>
+  <si>
+    <t>131234353</t>
+  </si>
+  <si>
+    <t>131205997</t>
+  </si>
+  <si>
+    <t>130905695</t>
+  </si>
+  <si>
+    <t>136042952</t>
+  </si>
+  <si>
+    <t>131149398</t>
+  </si>
+  <si>
+    <t>136061958</t>
+  </si>
+  <si>
+    <t>136160738</t>
+  </si>
+  <si>
+    <t>136138344</t>
+  </si>
+  <si>
+    <t>136037030</t>
+  </si>
+  <si>
+    <t>136177585</t>
+  </si>
+  <si>
+    <t>136250671</t>
+  </si>
+  <si>
+    <t>131084394</t>
+  </si>
+  <si>
+    <t>136026175</t>
+  </si>
+  <si>
+    <t>136036811</t>
+  </si>
+  <si>
+    <t>131017977</t>
+  </si>
+  <si>
+    <t>136282395</t>
+  </si>
+  <si>
+    <t>130909179</t>
+  </si>
+  <si>
+    <t>136129134</t>
+  </si>
+  <si>
+    <t>136137576</t>
+  </si>
+  <si>
+    <t>136092736</t>
+  </si>
+  <si>
+    <t>136078058</t>
+  </si>
+  <si>
+    <t>131128956</t>
+  </si>
+  <si>
+    <t>136168756</t>
+  </si>
+  <si>
+    <t>136134755</t>
+  </si>
+  <si>
+    <t>136167860</t>
+  </si>
+  <si>
+    <t>131005845</t>
+  </si>
+  <si>
+    <t>130949957</t>
+  </si>
+  <si>
+    <t>136186545</t>
+  </si>
+  <si>
+    <t>135981322</t>
+  </si>
+  <si>
+    <t>131205611</t>
+  </si>
+  <si>
+    <t>135811722</t>
+  </si>
+  <si>
+    <t>136212755</t>
+  </si>
+  <si>
+    <t>135850351</t>
+  </si>
+  <si>
+    <t>131148528</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 15.01.2026</t>
+  </si>
+  <si>
+    <t>131123965</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 16.01.2026</t>
+  </si>
+  <si>
+    <t>136036911</t>
+  </si>
+  <si>
+    <t>136092540</t>
+  </si>
+  <si>
+    <t>136211146</t>
+  </si>
+  <si>
+    <t>136025055</t>
+  </si>
+  <si>
+    <t>131221381</t>
+  </si>
+  <si>
+    <t>136077877</t>
+  </si>
+  <si>
+    <t>130842083</t>
+  </si>
+  <si>
+    <t>136092552</t>
+  </si>
+  <si>
+    <t>136301015</t>
+  </si>
+  <si>
+    <t>135656310</t>
+  </si>
+  <si>
+    <t>131375158</t>
+  </si>
+  <si>
+    <t>136206043</t>
+  </si>
+  <si>
+    <t>136078012</t>
+  </si>
+  <si>
+    <t>132199671</t>
+  </si>
+  <si>
+    <t>131112740</t>
+  </si>
+  <si>
+    <t>136194667</t>
+  </si>
+  <si>
+    <t>131266244</t>
+  </si>
+  <si>
+    <t>130983867</t>
+  </si>
+  <si>
+    <t>136300887</t>
+  </si>
+  <si>
+    <t>136194700</t>
+  </si>
+  <si>
+    <t>136275694</t>
+  </si>
+  <si>
+    <t>136024853</t>
+  </si>
+  <si>
+    <t>136166685</t>
+  </si>
+  <si>
+    <t>131251384</t>
+  </si>
+  <si>
+    <t>130934427</t>
+  </si>
+  <si>
+    <t>136030637</t>
+  </si>
+  <si>
+    <t>136216946</t>
+  </si>
+  <si>
+    <t>136221640</t>
+  </si>
+  <si>
+    <t>136109245</t>
+  </si>
+  <si>
+    <t>136166035</t>
+  </si>
+  <si>
+    <t>136113877</t>
+  </si>
+  <si>
+    <t>136027248</t>
+  </si>
+  <si>
+    <t>136058550</t>
+  </si>
+  <si>
+    <t>130906472</t>
+  </si>
+  <si>
+    <t>130931712</t>
+  </si>
+  <si>
+    <t>136201137</t>
+  </si>
+  <si>
+    <t>136198871</t>
+  </si>
+  <si>
+    <t>136143522</t>
+  </si>
+  <si>
+    <t>134109455</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 16.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +717,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,436 +748,1532 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -922,31 +2291,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CA3711-1C5A-4EA1-A2CB-6EA1B95C4F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5E338C-C992-4F98-85CB-B662D84B7F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="52">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,277 +51,139 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136026628</t>
+    <t>136059769</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 15.01.2026</t>
-  </si>
-  <si>
-    <t>136077946</t>
-  </si>
-  <si>
-    <t>136077778</t>
-  </si>
-  <si>
-    <t>135989158</t>
-  </si>
-  <si>
-    <t>136030549</t>
-  </si>
-  <si>
-    <t>130939526</t>
-  </si>
-  <si>
-    <t>131012400</t>
-  </si>
-  <si>
-    <t>136168719</t>
-  </si>
-  <si>
-    <t>133349239</t>
-  </si>
-  <si>
-    <t>136077889</t>
-  </si>
-  <si>
-    <t>136168165</t>
-  </si>
-  <si>
-    <t>136010926</t>
-  </si>
-  <si>
-    <t>131234353</t>
-  </si>
-  <si>
-    <t>131205997</t>
-  </si>
-  <si>
-    <t>130905695</t>
-  </si>
-  <si>
-    <t>136042952</t>
-  </si>
-  <si>
-    <t>131149398</t>
-  </si>
-  <si>
-    <t>136061958</t>
-  </si>
-  <si>
-    <t>136160738</t>
-  </si>
-  <si>
-    <t>136138344</t>
-  </si>
-  <si>
-    <t>136037030</t>
-  </si>
-  <si>
-    <t>136177585</t>
-  </si>
-  <si>
-    <t>136250671</t>
-  </si>
-  <si>
-    <t>131084394</t>
-  </si>
-  <si>
-    <t>136026175</t>
-  </si>
-  <si>
-    <t>136036811</t>
-  </si>
-  <si>
-    <t>131017977</t>
-  </si>
-  <si>
-    <t>136282395</t>
-  </si>
-  <si>
-    <t>130909179</t>
-  </si>
-  <si>
-    <t>136129134</t>
-  </si>
-  <si>
-    <t>136137576</t>
-  </si>
-  <si>
-    <t>136092736</t>
-  </si>
-  <si>
-    <t>136078058</t>
-  </si>
-  <si>
-    <t>131128956</t>
-  </si>
-  <si>
-    <t>136168756</t>
-  </si>
-  <si>
-    <t>136134755</t>
-  </si>
-  <si>
-    <t>136167860</t>
-  </si>
-  <si>
-    <t>131005845</t>
-  </si>
-  <si>
-    <t>130949957</t>
-  </si>
-  <si>
-    <t>136186545</t>
-  </si>
-  <si>
-    <t>135981322</t>
-  </si>
-  <si>
-    <t>131205611</t>
-  </si>
-  <si>
-    <t>135811722</t>
-  </si>
-  <si>
-    <t>136212755</t>
-  </si>
-  <si>
-    <t>135850351</t>
-  </si>
-  <si>
-    <t>131148528</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 15.01.2026</t>
-  </si>
-  <si>
-    <t>131123965</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 16.01.2026</t>
-  </si>
-  <si>
-    <t>136036911</t>
-  </si>
-  <si>
-    <t>136092540</t>
-  </si>
-  <si>
-    <t>136211146</t>
-  </si>
-  <si>
-    <t>136025055</t>
-  </si>
-  <si>
-    <t>131221381</t>
-  </si>
-  <si>
-    <t>136077877</t>
-  </si>
-  <si>
-    <t>130842083</t>
-  </si>
-  <si>
-    <t>136092552</t>
-  </si>
-  <si>
-    <t>136301015</t>
-  </si>
-  <si>
-    <t>135656310</t>
-  </si>
-  <si>
-    <t>131375158</t>
-  </si>
-  <si>
-    <t>136206043</t>
-  </si>
-  <si>
-    <t>136078012</t>
-  </si>
-  <si>
-    <t>132199671</t>
-  </si>
-  <si>
-    <t>131112740</t>
-  </si>
-  <si>
-    <t>136194667</t>
-  </si>
-  <si>
-    <t>131266244</t>
-  </si>
-  <si>
-    <t>130983867</t>
-  </si>
-  <si>
-    <t>136300887</t>
-  </si>
-  <si>
-    <t>136194700</t>
-  </si>
-  <si>
-    <t>136275694</t>
-  </si>
-  <si>
-    <t>136024853</t>
-  </si>
-  <si>
-    <t>136166685</t>
-  </si>
-  <si>
-    <t>131251384</t>
-  </si>
-  <si>
-    <t>130934427</t>
-  </si>
-  <si>
-    <t>136030637</t>
-  </si>
-  <si>
-    <t>136216946</t>
-  </si>
-  <si>
-    <t>136221640</t>
-  </si>
-  <si>
-    <t>136109245</t>
-  </si>
-  <si>
-    <t>136166035</t>
-  </si>
-  <si>
-    <t>136113877</t>
-  </si>
-  <si>
-    <t>136027248</t>
-  </si>
-  <si>
-    <t>136058550</t>
-  </si>
-  <si>
-    <t>130906472</t>
-  </si>
-  <si>
-    <t>130931712</t>
-  </si>
-  <si>
-    <t>136201137</t>
-  </si>
-  <si>
-    <t>136198871</t>
-  </si>
-  <si>
-    <t>136143522</t>
-  </si>
-  <si>
-    <t>134109455</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 16.01.2026</t>
+    <t>Nup- Cancelamento 19.01.2026</t>
+  </si>
+  <si>
+    <t>134990093</t>
+  </si>
+  <si>
+    <t>136206580</t>
+  </si>
+  <si>
+    <t>136201566</t>
+  </si>
+  <si>
+    <t>136321025</t>
+  </si>
+  <si>
+    <t>136036984</t>
+  </si>
+  <si>
+    <t>136036906</t>
+  </si>
+  <si>
+    <t>131099394</t>
+  </si>
+  <si>
+    <t>136077905</t>
+  </si>
+  <si>
+    <t>136078083</t>
+  </si>
+  <si>
+    <t>136212827</t>
+  </si>
+  <si>
+    <t>136229219</t>
+  </si>
+  <si>
+    <t>136063538</t>
+  </si>
+  <si>
+    <t>136037093</t>
+  </si>
+  <si>
+    <t>136169245</t>
+  </si>
+  <si>
+    <t>136300991</t>
+  </si>
+  <si>
+    <t>133339165</t>
+  </si>
+  <si>
+    <t>131014208</t>
+  </si>
+  <si>
+    <t>130977866</t>
+  </si>
+  <si>
+    <t>131630345</t>
+  </si>
+  <si>
+    <t>131113664</t>
+  </si>
+  <si>
+    <t>130886267</t>
+  </si>
+  <si>
+    <t>136194676</t>
+  </si>
+  <si>
+    <t>136194570</t>
+  </si>
+  <si>
+    <t>130934217</t>
+  </si>
+  <si>
+    <t>131058874</t>
+  </si>
+  <si>
+    <t>136059990</t>
+  </si>
+  <si>
+    <t>130845460</t>
+  </si>
+  <si>
+    <t>136321500</t>
+  </si>
+  <si>
+    <t>136036957</t>
+  </si>
+  <si>
+    <t>131159376</t>
+  </si>
+  <si>
+    <t>136202833</t>
+  </si>
+  <si>
+    <t>136144691</t>
+  </si>
+  <si>
+    <t>136119018</t>
+  </si>
+  <si>
+    <t>136168685</t>
+  </si>
+  <si>
+    <t>136295200</t>
+  </si>
+  <si>
+    <t>136132033</t>
+  </si>
+  <si>
+    <t>131140074</t>
+  </si>
+  <si>
+    <t>136063340</t>
+  </si>
+  <si>
+    <t>136194612</t>
+  </si>
+  <si>
+    <t>136037029</t>
+  </si>
+  <si>
+    <t>131202605</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 19.01.2026</t>
   </si>
 </sst>
 </file>
@@ -717,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -758,7 +620,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -776,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -794,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -812,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -830,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -848,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -866,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -884,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -902,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -920,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -938,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -956,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -974,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -992,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1010,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1028,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1046,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1064,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1082,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1100,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1118,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1127,7 +989,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
@@ -1136,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1007,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
@@ -1154,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1025,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -1172,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1043,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -1190,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1199,7 +1061,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
@@ -1208,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1217,7 +1079,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
@@ -1226,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1235,7 +1097,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -1244,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1253,7 +1115,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
@@ -1262,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1271,7 +1133,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
@@ -1280,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1289,7 +1151,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>8</v>
@@ -1298,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1307,7 +1169,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -1316,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1325,7 +1187,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
@@ -1334,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1343,7 +1205,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
@@ -1352,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1361,7 +1223,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
@@ -1370,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1378,7 +1240,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -1387,7 +1249,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1395,7 +1257,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
@@ -1404,7 +1266,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1412,7 +1274,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
@@ -1421,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1429,7 +1291,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
@@ -1438,7 +1300,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1446,7 +1308,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -1455,7 +1317,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1463,7 +1325,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>8</v>
@@ -1472,7 +1334,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1480,7 +1342,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>8</v>
@@ -1489,7 +1351,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1497,7 +1359,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>8</v>
@@ -1506,774 +1368,9 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E89" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2291,31 +1388,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5E338C-C992-4F98-85CB-B662D84B7F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64416FC3-C7D9-42D3-8F02-5D03A78EDB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,139 +51,130 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136059769</t>
+    <t>131258960</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 19.01.2026</t>
-  </si>
-  <si>
-    <t>134990093</t>
-  </si>
-  <si>
-    <t>136206580</t>
-  </si>
-  <si>
-    <t>136201566</t>
-  </si>
-  <si>
-    <t>136321025</t>
-  </si>
-  <si>
-    <t>136036984</t>
-  </si>
-  <si>
-    <t>136036906</t>
-  </si>
-  <si>
-    <t>131099394</t>
-  </si>
-  <si>
-    <t>136077905</t>
-  </si>
-  <si>
-    <t>136078083</t>
-  </si>
-  <si>
-    <t>136212827</t>
-  </si>
-  <si>
-    <t>136229219</t>
-  </si>
-  <si>
-    <t>136063538</t>
-  </si>
-  <si>
-    <t>136037093</t>
-  </si>
-  <si>
-    <t>136169245</t>
-  </si>
-  <si>
-    <t>136300991</t>
-  </si>
-  <si>
-    <t>133339165</t>
-  </si>
-  <si>
-    <t>131014208</t>
-  </si>
-  <si>
-    <t>130977866</t>
-  </si>
-  <si>
-    <t>131630345</t>
-  </si>
-  <si>
-    <t>131113664</t>
-  </si>
-  <si>
-    <t>130886267</t>
-  </si>
-  <si>
-    <t>136194676</t>
-  </si>
-  <si>
-    <t>136194570</t>
-  </si>
-  <si>
-    <t>130934217</t>
-  </si>
-  <si>
-    <t>131058874</t>
-  </si>
-  <si>
-    <t>136059990</t>
-  </si>
-  <si>
-    <t>130845460</t>
-  </si>
-  <si>
-    <t>136321500</t>
-  </si>
-  <si>
-    <t>136036957</t>
-  </si>
-  <si>
-    <t>131159376</t>
-  </si>
-  <si>
-    <t>136202833</t>
-  </si>
-  <si>
-    <t>136144691</t>
-  </si>
-  <si>
-    <t>136119018</t>
-  </si>
-  <si>
-    <t>136168685</t>
-  </si>
-  <si>
-    <t>136295200</t>
-  </si>
-  <si>
-    <t>136132033</t>
-  </si>
-  <si>
-    <t>131140074</t>
-  </si>
-  <si>
-    <t>136063340</t>
-  </si>
-  <si>
-    <t>136194612</t>
-  </si>
-  <si>
-    <t>136037029</t>
-  </si>
-  <si>
-    <t>131202605</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 19.01.2026</t>
+    <t>Nup- Cancelamento 20.01.2026</t>
+  </si>
+  <si>
+    <t>136071192</t>
+  </si>
+  <si>
+    <t>135661202</t>
+  </si>
+  <si>
+    <t>136212631</t>
+  </si>
+  <si>
+    <t>136340139</t>
+  </si>
+  <si>
+    <t>135920546</t>
+  </si>
+  <si>
+    <t>136213381</t>
+  </si>
+  <si>
+    <t>136129518</t>
+  </si>
+  <si>
+    <t>131271471</t>
+  </si>
+  <si>
+    <t>131367148</t>
+  </si>
+  <si>
+    <t>131367515</t>
+  </si>
+  <si>
+    <t>131348900</t>
+  </si>
+  <si>
+    <t>131225101</t>
+  </si>
+  <si>
+    <t>132725685</t>
+  </si>
+  <si>
+    <t>136148971</t>
+  </si>
+  <si>
+    <t>136202136</t>
+  </si>
+  <si>
+    <t>136224733</t>
+  </si>
+  <si>
+    <t>136077859</t>
+  </si>
+  <si>
+    <t>136137716</t>
+  </si>
+  <si>
+    <t>136175292</t>
+  </si>
+  <si>
+    <t>136078029</t>
+  </si>
+  <si>
+    <t>136300638</t>
+  </si>
+  <si>
+    <t>136092667</t>
+  </si>
+  <si>
+    <t>136167751</t>
+  </si>
+  <si>
+    <t>136078157</t>
+  </si>
+  <si>
+    <t>136300598</t>
+  </si>
+  <si>
+    <t>131145348</t>
+  </si>
+  <si>
+    <t>136240866</t>
+  </si>
+  <si>
+    <t>136103355</t>
+  </si>
+  <si>
+    <t>136062334</t>
+  </si>
+  <si>
+    <t>136214419</t>
+  </si>
+  <si>
+    <t>136040838</t>
+  </si>
+  <si>
+    <t>136077773</t>
+  </si>
+  <si>
+    <t>136203435</t>
+  </si>
+  <si>
+    <t>131272676</t>
+  </si>
+  <si>
+    <t>136077996</t>
+  </si>
+  <si>
+    <t>132069021</t>
+  </si>
+  <si>
+    <t>132619416</t>
+  </si>
+  <si>
+    <t>136104083</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 20.01.2026</t>
   </si>
 </sst>
 </file>
@@ -579,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,7 +611,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -638,7 +629,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -656,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -674,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -692,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -710,7 +701,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -746,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -764,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -782,7 +773,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -800,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -818,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -827,7 +818,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
@@ -836,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -845,7 +836,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
@@ -854,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -863,7 +854,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -872,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -881,7 +872,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -890,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -899,7 +890,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -908,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -917,7 +908,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
@@ -926,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -935,7 +926,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
@@ -944,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -953,7 +944,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -962,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -971,7 +962,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
@@ -980,7 +971,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -998,7 +989,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1025,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1097,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1142,7 +1133,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1160,7 +1151,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1178,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1196,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1214,7 +1205,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1232,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1249,7 +1240,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1266,7 +1257,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1283,7 +1274,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1300,7 +1291,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1317,60 +1308,9 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64416FC3-C7D9-42D3-8F02-5D03A78EDB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90777500-8072-4937-821B-86E3616FBC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="68">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,130 +51,187 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>131258960</t>
+    <t>136057938</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 20.01.2026</t>
-  </si>
-  <si>
-    <t>136071192</t>
-  </si>
-  <si>
-    <t>135661202</t>
-  </si>
-  <si>
-    <t>136212631</t>
-  </si>
-  <si>
-    <t>136340139</t>
-  </si>
-  <si>
-    <t>135920546</t>
-  </si>
-  <si>
-    <t>136213381</t>
-  </si>
-  <si>
-    <t>136129518</t>
-  </si>
-  <si>
-    <t>131271471</t>
-  </si>
-  <si>
-    <t>131367148</t>
-  </si>
-  <si>
-    <t>131367515</t>
-  </si>
-  <si>
-    <t>131348900</t>
-  </si>
-  <si>
-    <t>131225101</t>
-  </si>
-  <si>
-    <t>132725685</t>
-  </si>
-  <si>
-    <t>136148971</t>
-  </si>
-  <si>
-    <t>136202136</t>
-  </si>
-  <si>
-    <t>136224733</t>
-  </si>
-  <si>
-    <t>136077859</t>
-  </si>
-  <si>
-    <t>136137716</t>
-  </si>
-  <si>
-    <t>136175292</t>
-  </si>
-  <si>
-    <t>136078029</t>
-  </si>
-  <si>
-    <t>136300638</t>
-  </si>
-  <si>
-    <t>136092667</t>
-  </si>
-  <si>
-    <t>136167751</t>
-  </si>
-  <si>
-    <t>136078157</t>
-  </si>
-  <si>
-    <t>136300598</t>
-  </si>
-  <si>
-    <t>131145348</t>
-  </si>
-  <si>
-    <t>136240866</t>
-  </si>
-  <si>
-    <t>136103355</t>
-  </si>
-  <si>
-    <t>136062334</t>
-  </si>
-  <si>
-    <t>136214419</t>
-  </si>
-  <si>
-    <t>136040838</t>
-  </si>
-  <si>
-    <t>136077773</t>
-  </si>
-  <si>
-    <t>136203435</t>
-  </si>
-  <si>
-    <t>131272676</t>
-  </si>
-  <si>
-    <t>136077996</t>
-  </si>
-  <si>
-    <t>132069021</t>
-  </si>
-  <si>
-    <t>132619416</t>
-  </si>
-  <si>
-    <t>136104083</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 20.01.2026</t>
+    <t>Nup- Cancelamento 21.01.2026</t>
+  </si>
+  <si>
+    <t>136151885</t>
+  </si>
+  <si>
+    <t>136102666</t>
+  </si>
+  <si>
+    <t>135866740</t>
+  </si>
+  <si>
+    <t>135989429</t>
+  </si>
+  <si>
+    <t>136268554</t>
+  </si>
+  <si>
+    <t>136275713</t>
+  </si>
+  <si>
+    <t>136270104</t>
+  </si>
+  <si>
+    <t>130841591</t>
+  </si>
+  <si>
+    <t>136176261</t>
+  </si>
+  <si>
+    <t>131295587</t>
+  </si>
+  <si>
+    <t>136129230</t>
+  </si>
+  <si>
+    <t>136169303</t>
+  </si>
+  <si>
+    <t>131257409</t>
+  </si>
+  <si>
+    <t>135741524</t>
+  </si>
+  <si>
+    <t>136246076</t>
+  </si>
+  <si>
+    <t>136279831</t>
+  </si>
+  <si>
+    <t>131053262</t>
+  </si>
+  <si>
+    <t>136168803</t>
+  </si>
+  <si>
+    <t>136269251</t>
+  </si>
+  <si>
+    <t>136339840</t>
+  </si>
+  <si>
+    <t>131363873</t>
+  </si>
+  <si>
+    <t>131104975</t>
+  </si>
+  <si>
+    <t>136117445</t>
+  </si>
+  <si>
+    <t>136061296</t>
+  </si>
+  <si>
+    <t>135535031</t>
+  </si>
+  <si>
+    <t>135989543</t>
+  </si>
+  <si>
+    <t>136166659</t>
+  </si>
+  <si>
+    <t>131429557</t>
+  </si>
+  <si>
+    <t>131084763</t>
+  </si>
+  <si>
+    <t>136109270</t>
+  </si>
+  <si>
+    <t>136077976</t>
+  </si>
+  <si>
+    <t>135516206</t>
+  </si>
+  <si>
+    <t>131288493</t>
+  </si>
+  <si>
+    <t>136077880</t>
+  </si>
+  <si>
+    <t>130964658</t>
+  </si>
+  <si>
+    <t>136258212</t>
+  </si>
+  <si>
+    <t>136259803</t>
+  </si>
+  <si>
+    <t>135783562</t>
+  </si>
+  <si>
+    <t>136232228</t>
+  </si>
+  <si>
+    <t>131266972</t>
+  </si>
+  <si>
+    <t>136077831</t>
+  </si>
+  <si>
+    <t>136169275</t>
+  </si>
+  <si>
+    <t>136257444</t>
+  </si>
+  <si>
+    <t>136246942</t>
+  </si>
+  <si>
+    <t>135416096</t>
+  </si>
+  <si>
+    <t>136109368</t>
+  </si>
+  <si>
+    <t>136267964</t>
+  </si>
+  <si>
+    <t>133809533</t>
+  </si>
+  <si>
+    <t>130947014</t>
+  </si>
+  <si>
+    <t>136077870</t>
+  </si>
+  <si>
+    <t>134504293</t>
+  </si>
+  <si>
+    <t>136228058</t>
+  </si>
+  <si>
+    <t>134118650</t>
+  </si>
+  <si>
+    <t>136187216</t>
+  </si>
+  <si>
+    <t>136010863</t>
+  </si>
+  <si>
+    <t>136155643</t>
+  </si>
+  <si>
+    <t>135003642</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 21.01.2026</t>
   </si>
 </sst>
 </file>
@@ -570,7 +627,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -611,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -629,7 +686,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -647,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -683,7 +740,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -701,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -719,7 +776,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -737,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -755,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -773,7 +830,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -791,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -809,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,7 +875,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
@@ -827,7 +884,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -836,7 +893,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
@@ -845,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -854,7 +911,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -863,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -872,7 +929,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -881,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -890,7 +947,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -899,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -908,7 +965,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
@@ -917,7 +974,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -926,7 +983,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
@@ -935,7 +992,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -944,7 +1001,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -953,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -962,7 +1019,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
@@ -971,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -980,7 +1037,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
@@ -989,7 +1046,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -998,7 +1055,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
@@ -1007,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1073,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -1025,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1091,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -1043,7 +1100,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1109,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
@@ -1061,7 +1118,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1127,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
@@ -1079,7 +1136,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1145,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -1097,7 +1154,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1163,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
@@ -1115,7 +1172,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1181,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
@@ -1133,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1142,7 +1199,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>8</v>
@@ -1151,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1160,7 +1217,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -1169,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1178,7 +1235,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
@@ -1187,7 +1244,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1196,7 +1253,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
@@ -1205,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1214,7 +1271,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
@@ -1223,7 +1280,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1231,7 +1288,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -1240,7 +1297,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1248,7 +1305,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
@@ -1257,7 +1314,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1265,7 +1322,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
@@ -1274,7 +1331,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1282,7 +1339,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
@@ -1291,7 +1348,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1299,7 +1356,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -1308,9 +1365,315 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90777500-8072-4937-821B-86E3616FBC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F7E663-A3D6-4EC9-BC8D-7EE2D6B9BB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,187 +51,106 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136057938</t>
+    <t>136281558</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 21.01.2026</t>
-  </si>
-  <si>
-    <t>136151885</t>
-  </si>
-  <si>
-    <t>136102666</t>
-  </si>
-  <si>
-    <t>135866740</t>
-  </si>
-  <si>
-    <t>135989429</t>
-  </si>
-  <si>
-    <t>136268554</t>
-  </si>
-  <si>
-    <t>136275713</t>
+    <t>Nup- Cancelamento 22.01.2026</t>
+  </si>
+  <si>
+    <t>131257293</t>
+  </si>
+  <si>
+    <t>136167477</t>
+  </si>
+  <si>
+    <t>136285762</t>
+  </si>
+  <si>
+    <t>136201518</t>
+  </si>
+  <si>
+    <t>136378479</t>
+  </si>
+  <si>
+    <t>136331715</t>
+  </si>
+  <si>
+    <t>131027964</t>
   </si>
   <si>
     <t>136270104</t>
   </si>
   <si>
-    <t>130841591</t>
-  </si>
-  <si>
-    <t>136176261</t>
-  </si>
-  <si>
-    <t>131295587</t>
-  </si>
-  <si>
-    <t>136129230</t>
-  </si>
-  <si>
-    <t>136169303</t>
-  </si>
-  <si>
-    <t>131257409</t>
-  </si>
-  <si>
-    <t>135741524</t>
-  </si>
-  <si>
-    <t>136246076</t>
-  </si>
-  <si>
-    <t>136279831</t>
-  </si>
-  <si>
-    <t>131053262</t>
-  </si>
-  <si>
-    <t>136168803</t>
-  </si>
-  <si>
-    <t>136269251</t>
-  </si>
-  <si>
-    <t>136339840</t>
-  </si>
-  <si>
-    <t>131363873</t>
-  </si>
-  <si>
-    <t>131104975</t>
-  </si>
-  <si>
-    <t>136117445</t>
-  </si>
-  <si>
-    <t>136061296</t>
-  </si>
-  <si>
-    <t>135535031</t>
-  </si>
-  <si>
-    <t>135989543</t>
-  </si>
-  <si>
-    <t>136166659</t>
-  </si>
-  <si>
-    <t>131429557</t>
-  </si>
-  <si>
-    <t>131084763</t>
-  </si>
-  <si>
-    <t>136109270</t>
-  </si>
-  <si>
-    <t>136077976</t>
-  </si>
-  <si>
-    <t>135516206</t>
-  </si>
-  <si>
-    <t>131288493</t>
-  </si>
-  <si>
-    <t>136077880</t>
-  </si>
-  <si>
-    <t>130964658</t>
-  </si>
-  <si>
-    <t>136258212</t>
-  </si>
-  <si>
-    <t>136259803</t>
-  </si>
-  <si>
-    <t>135783562</t>
-  </si>
-  <si>
-    <t>136232228</t>
-  </si>
-  <si>
-    <t>131266972</t>
-  </si>
-  <si>
-    <t>136077831</t>
-  </si>
-  <si>
-    <t>136169275</t>
-  </si>
-  <si>
-    <t>136257444</t>
-  </si>
-  <si>
-    <t>136246942</t>
-  </si>
-  <si>
-    <t>135416096</t>
-  </si>
-  <si>
-    <t>136109368</t>
-  </si>
-  <si>
-    <t>136267964</t>
-  </si>
-  <si>
-    <t>133809533</t>
-  </si>
-  <si>
-    <t>130947014</t>
-  </si>
-  <si>
-    <t>136077870</t>
-  </si>
-  <si>
-    <t>134504293</t>
-  </si>
-  <si>
-    <t>136228058</t>
-  </si>
-  <si>
-    <t>134118650</t>
-  </si>
-  <si>
-    <t>136187216</t>
-  </si>
-  <si>
-    <t>136010863</t>
-  </si>
-  <si>
-    <t>136155643</t>
-  </si>
-  <si>
-    <t>135003642</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 21.01.2026</t>
+    <t>136118211</t>
+  </si>
+  <si>
+    <t>136253350</t>
+  </si>
+  <si>
+    <t>131372330</t>
+  </si>
+  <si>
+    <t>132353824</t>
+  </si>
+  <si>
+    <t>131053315</t>
+  </si>
+  <si>
+    <t>130993991</t>
+  </si>
+  <si>
+    <t>136061723</t>
+  </si>
+  <si>
+    <t>136194739</t>
+  </si>
+  <si>
+    <t>136157269</t>
+  </si>
+  <si>
+    <t>136340254</t>
+  </si>
+  <si>
+    <t>131102444</t>
+  </si>
+  <si>
+    <t>136300441</t>
+  </si>
+  <si>
+    <t>136340228</t>
+  </si>
+  <si>
+    <t>131348900</t>
+  </si>
+  <si>
+    <t>130970409</t>
+  </si>
+  <si>
+    <t>136378410</t>
+  </si>
+  <si>
+    <t>136346068</t>
+  </si>
+  <si>
+    <t>136283836</t>
+  </si>
+  <si>
+    <t>136010939</t>
+  </si>
+  <si>
+    <t>136030221</t>
+  </si>
+  <si>
+    <t>135330029</t>
+  </si>
+  <si>
+    <t>136213523</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.01.2026</t>
   </si>
 </sst>
 </file>
@@ -627,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -668,7 +587,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -686,7 +605,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -704,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -722,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -740,7 +659,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -758,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -776,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -794,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -812,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -830,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -848,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -866,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -884,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -902,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -920,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -938,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -956,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -974,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -992,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1010,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1028,7 +947,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1046,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1064,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1082,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1100,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1118,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1136,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1154,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1172,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1190,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1208,474 +1127,12 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F32"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F7E663-A3D6-4EC9-BC8D-7EE2D6B9BB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177243B5-0B5C-4955-9435-EEE17CF3FD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,106 +51,133 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136281558</t>
+    <t>Nup- Cancelamento 23.01.2026</t>
+  </si>
+  <si>
+    <t>131191106</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 22.01.2026</t>
-  </si>
-  <si>
-    <t>131257293</t>
-  </si>
-  <si>
-    <t>136167477</t>
-  </si>
-  <si>
-    <t>136285762</t>
-  </si>
-  <si>
-    <t>136201518</t>
-  </si>
-  <si>
-    <t>136378479</t>
-  </si>
-  <si>
-    <t>136331715</t>
-  </si>
-  <si>
-    <t>131027964</t>
-  </si>
-  <si>
-    <t>136270104</t>
-  </si>
-  <si>
-    <t>136118211</t>
-  </si>
-  <si>
-    <t>136253350</t>
-  </si>
-  <si>
-    <t>131372330</t>
-  </si>
-  <si>
-    <t>132353824</t>
-  </si>
-  <si>
-    <t>131053315</t>
-  </si>
-  <si>
-    <t>130993991</t>
-  </si>
-  <si>
-    <t>136061723</t>
-  </si>
-  <si>
-    <t>136194739</t>
-  </si>
-  <si>
-    <t>136157269</t>
-  </si>
-  <si>
-    <t>136340254</t>
-  </si>
-  <si>
-    <t>131102444</t>
-  </si>
-  <si>
-    <t>136300441</t>
-  </si>
-  <si>
-    <t>136340228</t>
-  </si>
-  <si>
-    <t>131348900</t>
-  </si>
-  <si>
-    <t>130970409</t>
-  </si>
-  <si>
-    <t>136378410</t>
-  </si>
-  <si>
-    <t>136346068</t>
-  </si>
-  <si>
-    <t>136283836</t>
-  </si>
-  <si>
-    <t>136010939</t>
-  </si>
-  <si>
-    <t>136030221</t>
-  </si>
-  <si>
-    <t>135330029</t>
-  </si>
-  <si>
-    <t>136213523</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.01.2026</t>
+    <t>136343149</t>
+  </si>
+  <si>
+    <t>136078024</t>
+  </si>
+  <si>
+    <t>136220387</t>
+  </si>
+  <si>
+    <t>136242835</t>
+  </si>
+  <si>
+    <t>136139452</t>
+  </si>
+  <si>
+    <t>136311233</t>
+  </si>
+  <si>
+    <t>136302910</t>
+  </si>
+  <si>
+    <t>131371443</t>
+  </si>
+  <si>
+    <t>136166790</t>
+  </si>
+  <si>
+    <t>131380882</t>
+  </si>
+  <si>
+    <t>131422388</t>
+  </si>
+  <si>
+    <t>131161894</t>
+  </si>
+  <si>
+    <t>136302384</t>
+  </si>
+  <si>
+    <t>136168575</t>
+  </si>
+  <si>
+    <t>136378016</t>
+  </si>
+  <si>
+    <t>136300559</t>
+  </si>
+  <si>
+    <t>136308579</t>
+  </si>
+  <si>
+    <t>136222059</t>
+  </si>
+  <si>
+    <t>136302684</t>
+  </si>
+  <si>
+    <t>136300440</t>
+  </si>
+  <si>
+    <t>131109845</t>
+  </si>
+  <si>
+    <t>131315280</t>
+  </si>
+  <si>
+    <t>131136324</t>
+  </si>
+  <si>
+    <t>135574983</t>
+  </si>
+  <si>
+    <t>136337379</t>
+  </si>
+  <si>
+    <t>130878313</t>
+  </si>
+  <si>
+    <t>136125228</t>
+  </si>
+  <si>
+    <t>136301014</t>
+  </si>
+  <si>
+    <t>136168903</t>
+  </si>
+  <si>
+    <t>136107554</t>
+  </si>
+  <si>
+    <t>136104238</t>
+  </si>
+  <si>
+    <t>136300775</t>
+  </si>
+  <si>
+    <t>136334631</t>
+  </si>
+  <si>
+    <t>130872131</t>
+  </si>
+  <si>
+    <t>135023702</t>
+  </si>
+  <si>
+    <t>136356001</t>
+  </si>
+  <si>
+    <t>133870044</t>
+  </si>
+  <si>
+    <t>136305826</t>
+  </si>
+  <si>
+    <t>134342134</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 23.01.2026</t>
   </si>
 </sst>
 </file>
@@ -546,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -578,16 +605,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -599,13 +626,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -617,13 +644,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -635,13 +662,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -653,13 +680,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -671,13 +698,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -689,13 +716,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -707,13 +734,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -725,13 +752,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -743,13 +770,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -758,16 +785,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -776,16 +803,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -794,16 +821,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -812,16 +839,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -830,16 +857,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -848,16 +875,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -866,16 +893,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -884,16 +911,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -902,16 +929,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -920,16 +947,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -938,16 +965,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -956,16 +983,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -974,16 +1001,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -992,16 +1019,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1010,16 +1037,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1028,16 +1055,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1046,16 +1073,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1064,16 +1091,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1082,16 +1109,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1100,16 +1127,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1118,21 +1145,330 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32"/>
+      <c r="B42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF34342-9939-40A3-9DCF-A4C829EAE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="44">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,117 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136300606</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 26.01.2026</t>
+  </si>
+  <si>
+    <t>136300754</t>
+  </si>
+  <si>
+    <t>136374813</t>
+  </si>
+  <si>
+    <t>131397161</t>
+  </si>
+  <si>
+    <t>136243540</t>
+  </si>
+  <si>
+    <t>136324789</t>
+  </si>
+  <si>
+    <t>136300819</t>
+  </si>
+  <si>
+    <t>136333574</t>
+  </si>
+  <si>
+    <t>131402374</t>
+  </si>
+  <si>
+    <t>136342863</t>
+  </si>
+  <si>
+    <t>136345433</t>
+  </si>
+  <si>
+    <t>136404781</t>
+  </si>
+  <si>
+    <t>136092712</t>
+  </si>
+  <si>
+    <t>136297992</t>
+  </si>
+  <si>
+    <t>131224520</t>
+  </si>
+  <si>
+    <t>136168401</t>
+  </si>
+  <si>
+    <t>136345720</t>
+  </si>
+  <si>
+    <t>136333120</t>
+  </si>
+  <si>
+    <t>136164324</t>
+  </si>
+  <si>
+    <t>136266045</t>
+  </si>
+  <si>
+    <t>136319079</t>
+  </si>
+  <si>
+    <t>131198820</t>
+  </si>
+  <si>
+    <t>131030625</t>
+  </si>
+  <si>
+    <t>136251460</t>
+  </si>
+  <si>
+    <t>131030724</t>
+  </si>
+  <si>
+    <t>136300478</t>
+  </si>
+  <si>
+    <t>136107316</t>
+  </si>
+  <si>
+    <t>131260463</t>
+  </si>
+  <si>
+    <t>131365658</t>
+  </si>
+  <si>
+    <t>134916861</t>
+  </si>
+  <si>
+    <t>134685449</t>
+  </si>
+  <si>
+    <t>135700209</t>
+  </si>
+  <si>
+    <t>132859862</t>
+  </si>
+  <si>
+    <t>136092593</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -475,132 +586,615 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
   </sheetData>
@@ -617,31 +1211,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915354FB-B092-40E7-92BF-14F966B7521D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,138 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136213062</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.01.2026</t>
+  </si>
+  <si>
+    <t>136211362</t>
+  </si>
+  <si>
+    <t>136045142</t>
+  </si>
+  <si>
+    <t>136300631</t>
+  </si>
+  <si>
+    <t>131166222</t>
+  </si>
+  <si>
+    <t>136321248</t>
+  </si>
+  <si>
+    <t>136321085</t>
+  </si>
+  <si>
+    <t>136106870</t>
+  </si>
+  <si>
+    <t>136032261</t>
+  </si>
+  <si>
+    <t>131365677</t>
+  </si>
+  <si>
+    <t>136321360</t>
+  </si>
+  <si>
+    <t>131200519</t>
+  </si>
+  <si>
+    <t>136300767</t>
+  </si>
+  <si>
+    <t>131473549</t>
+  </si>
+  <si>
+    <t>136366453</t>
+  </si>
+  <si>
+    <t>136328753</t>
+  </si>
+  <si>
+    <t>136053080</t>
+  </si>
+  <si>
+    <t>131365394</t>
+  </si>
+  <si>
+    <t>136363334</t>
+  </si>
+  <si>
+    <t>136321520</t>
+  </si>
+  <si>
+    <t>136378345</t>
+  </si>
+  <si>
+    <t>131362377</t>
+  </si>
+  <si>
+    <t>136321187</t>
+  </si>
+  <si>
+    <t>131030724</t>
+  </si>
+  <si>
+    <t>136300478</t>
+  </si>
+  <si>
+    <t>136107316</t>
+  </si>
+  <si>
+    <t>131260463</t>
+  </si>
+  <si>
+    <t>131365658</t>
+  </si>
+  <si>
+    <t>136368326</t>
+  </si>
+  <si>
+    <t>136243303</t>
+  </si>
+  <si>
+    <t>136319087</t>
+  </si>
+  <si>
+    <t>136131732</t>
+  </si>
+  <si>
+    <t>135701947</t>
+  </si>
+  <si>
+    <t>133082221</t>
+  </si>
+  <si>
+    <t>136077950</t>
+  </si>
+  <si>
+    <t>136400413</t>
+  </si>
+  <si>
+    <t>131625853</t>
+  </si>
+  <si>
+    <t>136342863</t>
+  </si>
+  <si>
+    <t>136304518</t>
+  </si>
+  <si>
+    <t>136341203</t>
+  </si>
+  <si>
+    <t>136340116</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +607,769 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1385,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915354FB-B092-40E7-92BF-14F966B7521D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB139AD-D415-4C77-AA99-0825B5C4CEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,136 +51,136 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136213062</t>
+    <t>136300667</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 27.01.2026</t>
-  </si>
-  <si>
-    <t>136211362</t>
-  </si>
-  <si>
-    <t>136045142</t>
-  </si>
-  <si>
-    <t>136300631</t>
-  </si>
-  <si>
-    <t>131166222</t>
-  </si>
-  <si>
-    <t>136321248</t>
-  </si>
-  <si>
-    <t>136321085</t>
-  </si>
-  <si>
-    <t>136106870</t>
-  </si>
-  <si>
-    <t>136032261</t>
-  </si>
-  <si>
-    <t>131365677</t>
-  </si>
-  <si>
-    <t>136321360</t>
-  </si>
-  <si>
-    <t>131200519</t>
-  </si>
-  <si>
-    <t>136300767</t>
-  </si>
-  <si>
-    <t>131473549</t>
-  </si>
-  <si>
-    <t>136366453</t>
-  </si>
-  <si>
-    <t>136328753</t>
-  </si>
-  <si>
-    <t>136053080</t>
-  </si>
-  <si>
-    <t>131365394</t>
-  </si>
-  <si>
-    <t>136363334</t>
-  </si>
-  <si>
-    <t>136321520</t>
-  </si>
-  <si>
-    <t>136378345</t>
-  </si>
-  <si>
-    <t>131362377</t>
-  </si>
-  <si>
-    <t>136321187</t>
-  </si>
-  <si>
-    <t>131030724</t>
-  </si>
-  <si>
-    <t>136300478</t>
-  </si>
-  <si>
-    <t>136107316</t>
-  </si>
-  <si>
-    <t>131260463</t>
-  </si>
-  <si>
-    <t>131365658</t>
-  </si>
-  <si>
-    <t>136368326</t>
-  </si>
-  <si>
-    <t>136243303</t>
-  </si>
-  <si>
-    <t>136319087</t>
-  </si>
-  <si>
-    <t>136131732</t>
-  </si>
-  <si>
-    <t>135701947</t>
-  </si>
-  <si>
-    <t>133082221</t>
-  </si>
-  <si>
-    <t>136077950</t>
-  </si>
-  <si>
-    <t>136400413</t>
-  </si>
-  <si>
-    <t>131625853</t>
-  </si>
-  <si>
-    <t>136342863</t>
-  </si>
-  <si>
-    <t>136304518</t>
-  </si>
-  <si>
-    <t>136341203</t>
-  </si>
-  <si>
-    <t>136340116</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.01.2026</t>
+    <t>Nup- Cancelamento 28.01.2026</t>
+  </si>
+  <si>
+    <t>131044691</t>
+  </si>
+  <si>
+    <t>135984154</t>
+  </si>
+  <si>
+    <t>131144065</t>
+  </si>
+  <si>
+    <t>136367913</t>
+  </si>
+  <si>
+    <t>136202504</t>
+  </si>
+  <si>
+    <t>136438093</t>
+  </si>
+  <si>
+    <t>136163809</t>
+  </si>
+  <si>
+    <t>135624685</t>
+  </si>
+  <si>
+    <t>136351841</t>
+  </si>
+  <si>
+    <t>131362261</t>
+  </si>
+  <si>
+    <t>136377911</t>
+  </si>
+  <si>
+    <t>131438818</t>
+  </si>
+  <si>
+    <t>131474690</t>
+  </si>
+  <si>
+    <t>131074640</t>
+  </si>
+  <si>
+    <t>136319293</t>
+  </si>
+  <si>
+    <t>131310598</t>
+  </si>
+  <si>
+    <t>131023891</t>
+  </si>
+  <si>
+    <t>136126025</t>
+  </si>
+  <si>
+    <t>136225156</t>
+  </si>
+  <si>
+    <t>136379484</t>
+  </si>
+  <si>
+    <t>131274224</t>
+  </si>
+  <si>
+    <t>136169311</t>
+  </si>
+  <si>
+    <t>131063090</t>
+  </si>
+  <si>
+    <t>136168906</t>
+  </si>
+  <si>
+    <t>134763770</t>
+  </si>
+  <si>
+    <t>136275734</t>
+  </si>
+  <si>
+    <t>136348957</t>
+  </si>
+  <si>
+    <t>136300446</t>
+  </si>
+  <si>
+    <t>131091418</t>
+  </si>
+  <si>
+    <t>136283737</t>
+  </si>
+  <si>
+    <t>136046580</t>
+  </si>
+  <si>
+    <t>130978837</t>
+  </si>
+  <si>
+    <t>136359463</t>
+  </si>
+  <si>
+    <t>136165647</t>
+  </si>
+  <si>
+    <t>133278620</t>
+  </si>
+  <si>
+    <t>136384770</t>
+  </si>
+  <si>
+    <t>136072412</t>
+  </si>
+  <si>
+    <t>136377603</t>
+  </si>
+  <si>
+    <t>134703914</t>
+  </si>
+  <si>
+    <t>134512182</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -576,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>8</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>8</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>8</v>
@@ -1351,23 +1351,6 @@
         <v>50</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956743BE-5AFE-407D-A7F9-5B7DD6B98083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,135 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>131408813</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 29.01.2026</t>
+  </si>
+  <si>
+    <t>136400382</t>
+  </si>
+  <si>
+    <t>131515869</t>
+  </si>
+  <si>
+    <t>131411335</t>
+  </si>
+  <si>
+    <t>136357181</t>
+  </si>
+  <si>
+    <t>136408372</t>
+  </si>
+  <si>
+    <t>136286922</t>
+  </si>
+  <si>
+    <t>136300574</t>
+  </si>
+  <si>
+    <t>136374451</t>
+  </si>
+  <si>
+    <t>131292555</t>
+  </si>
+  <si>
+    <t>131447427</t>
+  </si>
+  <si>
+    <t>131163083</t>
+  </si>
+  <si>
+    <t>131545142</t>
+  </si>
+  <si>
+    <t>136275653</t>
+  </si>
+  <si>
+    <t>136438201</t>
+  </si>
+  <si>
+    <t>131382998</t>
+  </si>
+  <si>
+    <t>136328396</t>
+  </si>
+  <si>
+    <t>136283264</t>
+  </si>
+  <si>
+    <t>136194607</t>
+  </si>
+  <si>
+    <t>131519313</t>
+  </si>
+  <si>
+    <t>136223338</t>
+  </si>
+  <si>
+    <t>131215808</t>
+  </si>
+  <si>
+    <t>136321361</t>
+  </si>
+  <si>
+    <t>136194517</t>
+  </si>
+  <si>
+    <t>136201439</t>
+  </si>
+  <si>
+    <t>136375081</t>
+  </si>
+  <si>
+    <t>136407270</t>
+  </si>
+  <si>
+    <t>135210507</t>
+  </si>
+  <si>
+    <t>136212482</t>
+  </si>
+  <si>
+    <t>134043826</t>
+  </si>
+  <si>
+    <t>131261439</t>
+  </si>
+  <si>
+    <t>130842526</t>
+  </si>
+  <si>
+    <t>135947775</t>
+  </si>
+  <si>
+    <t>136338292</t>
+  </si>
+  <si>
+    <t>136252912</t>
+  </si>
+  <si>
+    <t>136300895</t>
+  </si>
+  <si>
+    <t>133572278</t>
+  </si>
+  <si>
+    <t>136406355</t>
+  </si>
+  <si>
+    <t>136352946</t>
+  </si>
+  <si>
+    <t>132075476</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 29.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +604,718 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1331,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956743BE-5AFE-407D-A7F9-5B7DD6B98083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E81CDA-B10E-4BF5-A218-DC0A4BC4D1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,133 +51,175 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>131408813</t>
+    <t>136178966</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 29.01.2026</t>
-  </si>
-  <si>
-    <t>136400382</t>
-  </si>
-  <si>
-    <t>131515869</t>
-  </si>
-  <si>
-    <t>131411335</t>
-  </si>
-  <si>
-    <t>136357181</t>
-  </si>
-  <si>
-    <t>136408372</t>
-  </si>
-  <si>
-    <t>136286922</t>
-  </si>
-  <si>
-    <t>136300574</t>
-  </si>
-  <si>
-    <t>136374451</t>
-  </si>
-  <si>
-    <t>131292555</t>
-  </si>
-  <si>
-    <t>131447427</t>
-  </si>
-  <si>
-    <t>131163083</t>
-  </si>
-  <si>
-    <t>131545142</t>
-  </si>
-  <si>
-    <t>136275653</t>
-  </si>
-  <si>
-    <t>136438201</t>
-  </si>
-  <si>
-    <t>131382998</t>
-  </si>
-  <si>
-    <t>136328396</t>
-  </si>
-  <si>
-    <t>136283264</t>
-  </si>
-  <si>
-    <t>136194607</t>
-  </si>
-  <si>
-    <t>131519313</t>
-  </si>
-  <si>
-    <t>136223338</t>
-  </si>
-  <si>
-    <t>131215808</t>
-  </si>
-  <si>
-    <t>136321361</t>
-  </si>
-  <si>
-    <t>136194517</t>
-  </si>
-  <si>
-    <t>136201439</t>
-  </si>
-  <si>
-    <t>136375081</t>
-  </si>
-  <si>
-    <t>136407270</t>
-  </si>
-  <si>
-    <t>135210507</t>
-  </si>
-  <si>
-    <t>136212482</t>
-  </si>
-  <si>
-    <t>134043826</t>
-  </si>
-  <si>
-    <t>131261439</t>
-  </si>
-  <si>
-    <t>130842526</t>
-  </si>
-  <si>
-    <t>135947775</t>
-  </si>
-  <si>
-    <t>136338292</t>
-  </si>
-  <si>
-    <t>136252912</t>
-  </si>
-  <si>
-    <t>136300895</t>
-  </si>
-  <si>
-    <t>133572278</t>
-  </si>
-  <si>
-    <t>136406355</t>
-  </si>
-  <si>
-    <t>136352946</t>
-  </si>
-  <si>
-    <t>132075476</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 29.01.2026</t>
+    <t>Nup- Cancelamento 30.01.2026</t>
+  </si>
+  <si>
+    <t>136359462</t>
+  </si>
+  <si>
+    <t>136212756</t>
+  </si>
+  <si>
+    <t>136371166</t>
+  </si>
+  <si>
+    <t>136343176</t>
+  </si>
+  <si>
+    <t>136376486</t>
+  </si>
+  <si>
+    <t>136425791</t>
+  </si>
+  <si>
+    <t>136300824</t>
+  </si>
+  <si>
+    <t>136409941</t>
+  </si>
+  <si>
+    <t>131164476</t>
+  </si>
+  <si>
+    <t>136077962</t>
+  </si>
+  <si>
+    <t>136339945</t>
+  </si>
+  <si>
+    <t>136138777</t>
+  </si>
+  <si>
+    <t>136136478</t>
+  </si>
+  <si>
+    <t>136300783</t>
+  </si>
+  <si>
+    <t>131447172</t>
+  </si>
+  <si>
+    <t>136400286</t>
+  </si>
+  <si>
+    <t>135506008</t>
+  </si>
+  <si>
+    <t>136346831</t>
+  </si>
+  <si>
+    <t>136476355</t>
+  </si>
+  <si>
+    <t>136476258</t>
+  </si>
+  <si>
+    <t>136300785</t>
+  </si>
+  <si>
+    <t>131152838</t>
+  </si>
+  <si>
+    <t>136378527</t>
+  </si>
+  <si>
+    <t>135136265</t>
+  </si>
+  <si>
+    <t>131363017</t>
+  </si>
+  <si>
+    <t>135978788</t>
+  </si>
+  <si>
+    <t>133956623</t>
+  </si>
+  <si>
+    <t>136400270</t>
+  </si>
+  <si>
+    <t>136475688</t>
+  </si>
+  <si>
+    <t>136063300</t>
+  </si>
+  <si>
+    <t>136212895</t>
+  </si>
+  <si>
+    <t>136421044</t>
+  </si>
+  <si>
+    <t>136224371</t>
+  </si>
+  <si>
+    <t>136374266</t>
+  </si>
+  <si>
+    <t>136300817</t>
+  </si>
+  <si>
+    <t>136300955</t>
+  </si>
+  <si>
+    <t>136057340</t>
+  </si>
+  <si>
+    <t>136252722</t>
+  </si>
+  <si>
+    <t>134816090</t>
+  </si>
+  <si>
+    <t>136319680</t>
+  </si>
+  <si>
+    <t>131443185</t>
+  </si>
+  <si>
+    <t>136451740</t>
+  </si>
+  <si>
+    <t>136461060</t>
+  </si>
+  <si>
+    <t>136435149</t>
+  </si>
+  <si>
+    <t>136055153</t>
+  </si>
+  <si>
+    <t>134852742</t>
+  </si>
+  <si>
+    <t>136397576</t>
+  </si>
+  <si>
+    <t>136127718</t>
+  </si>
+  <si>
+    <t>132259733</t>
+  </si>
+  <si>
+    <t>133623546</t>
+  </si>
+  <si>
+    <t>136377379</t>
+  </si>
+  <si>
+    <t>136109322</t>
+  </si>
+  <si>
+    <t>136242405</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 30.01.2026</t>
   </si>
 </sst>
 </file>
@@ -573,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -632,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -650,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -668,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -686,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -704,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -722,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -740,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -758,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -776,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -794,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -812,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -830,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -848,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -866,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -884,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -902,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -920,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -938,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -956,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -974,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -992,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1010,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1028,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1046,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1082,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1100,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1118,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1136,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1154,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1172,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1190,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1208,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1226,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1243,7 +1285,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1260,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1277,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1294,7 +1336,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1311,9 +1353,247 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E81CDA-B10E-4BF5-A218-DC0A4BC4D1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05F1168-7D06-4976-AE6B-EE71BFA761BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,175 +51,136 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136178966</t>
+    <t>135624507</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 30.01.2026</t>
-  </si>
-  <si>
-    <t>136359462</t>
-  </si>
-  <si>
-    <t>136212756</t>
-  </si>
-  <si>
-    <t>136371166</t>
-  </si>
-  <si>
-    <t>136343176</t>
-  </si>
-  <si>
-    <t>136376486</t>
-  </si>
-  <si>
-    <t>136425791</t>
-  </si>
-  <si>
-    <t>136300824</t>
-  </si>
-  <si>
-    <t>136409941</t>
-  </si>
-  <si>
-    <t>131164476</t>
-  </si>
-  <si>
-    <t>136077962</t>
-  </si>
-  <si>
-    <t>136339945</t>
-  </si>
-  <si>
-    <t>136138777</t>
-  </si>
-  <si>
-    <t>136136478</t>
-  </si>
-  <si>
-    <t>136300783</t>
-  </si>
-  <si>
-    <t>131447172</t>
-  </si>
-  <si>
-    <t>136400286</t>
-  </si>
-  <si>
-    <t>135506008</t>
-  </si>
-  <si>
-    <t>136346831</t>
-  </si>
-  <si>
-    <t>136476355</t>
-  </si>
-  <si>
-    <t>136476258</t>
-  </si>
-  <si>
-    <t>136300785</t>
-  </si>
-  <si>
-    <t>131152838</t>
-  </si>
-  <si>
-    <t>136378527</t>
-  </si>
-  <si>
-    <t>135136265</t>
-  </si>
-  <si>
-    <t>131363017</t>
-  </si>
-  <si>
-    <t>135978788</t>
-  </si>
-  <si>
-    <t>133956623</t>
-  </si>
-  <si>
-    <t>136400270</t>
-  </si>
-  <si>
-    <t>136475688</t>
-  </si>
-  <si>
-    <t>136063300</t>
-  </si>
-  <si>
-    <t>136212895</t>
-  </si>
-  <si>
-    <t>136421044</t>
-  </si>
-  <si>
-    <t>136224371</t>
-  </si>
-  <si>
-    <t>136374266</t>
-  </si>
-  <si>
-    <t>136300817</t>
-  </si>
-  <si>
-    <t>136300955</t>
-  </si>
-  <si>
-    <t>136057340</t>
-  </si>
-  <si>
-    <t>136252722</t>
-  </si>
-  <si>
-    <t>134816090</t>
-  </si>
-  <si>
-    <t>136319680</t>
-  </si>
-  <si>
-    <t>131443185</t>
-  </si>
-  <si>
-    <t>136451740</t>
-  </si>
-  <si>
-    <t>136461060</t>
-  </si>
-  <si>
-    <t>136435149</t>
-  </si>
-  <si>
-    <t>136055153</t>
-  </si>
-  <si>
-    <t>134852742</t>
-  </si>
-  <si>
-    <t>136397576</t>
-  </si>
-  <si>
-    <t>136127718</t>
-  </si>
-  <si>
-    <t>132259733</t>
-  </si>
-  <si>
-    <t>133623546</t>
-  </si>
-  <si>
-    <t>136377379</t>
-  </si>
-  <si>
-    <t>136109322</t>
-  </si>
-  <si>
-    <t>136242405</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 30.01.2026</t>
+    <t>Nup- Cancelamento 02.02.2026</t>
+  </si>
+  <si>
+    <t>136378101</t>
+  </si>
+  <si>
+    <t>136448762</t>
+  </si>
+  <si>
+    <t>131017782</t>
+  </si>
+  <si>
+    <t>131130636</t>
+  </si>
+  <si>
+    <t>136374261</t>
+  </si>
+  <si>
+    <t>136283660</t>
+  </si>
+  <si>
+    <t>131545551</t>
+  </si>
+  <si>
+    <t>136449250</t>
+  </si>
+  <si>
+    <t>136300634</t>
+  </si>
+  <si>
+    <t>136445393</t>
+  </si>
+  <si>
+    <t>136388552</t>
+  </si>
+  <si>
+    <t>136275761</t>
+  </si>
+  <si>
+    <t>131517961</t>
+  </si>
+  <si>
+    <t>136275770</t>
+  </si>
+  <si>
+    <t>131563421</t>
+  </si>
+  <si>
+    <t>136465056</t>
+  </si>
+  <si>
+    <t>132193780</t>
+  </si>
+  <si>
+    <t>136440124</t>
+  </si>
+  <si>
+    <t>131446888</t>
+  </si>
+  <si>
+    <t>136471630</t>
+  </si>
+  <si>
+    <t>136448221</t>
+  </si>
+  <si>
+    <t>131535060</t>
+  </si>
+  <si>
+    <t>136402133</t>
+  </si>
+  <si>
+    <t>131128135</t>
+  </si>
+  <si>
+    <t>136251718</t>
+  </si>
+  <si>
+    <t>131224198</t>
+  </si>
+  <si>
+    <t>136419417</t>
+  </si>
+  <si>
+    <t>136361578</t>
+  </si>
+  <si>
+    <t>131557276</t>
+  </si>
+  <si>
+    <t>131340159</t>
+  </si>
+  <si>
+    <t>136339098</t>
+  </si>
+  <si>
+    <t>136376669</t>
+  </si>
+  <si>
+    <t>131373202</t>
+  </si>
+  <si>
+    <t>136446569</t>
+  </si>
+  <si>
+    <t>131224962</t>
+  </si>
+  <si>
+    <t>136247806</t>
+  </si>
+  <si>
+    <t>136466617</t>
+  </si>
+  <si>
+    <t>136439543</t>
+  </si>
+  <si>
+    <t>135671848</t>
+  </si>
+  <si>
+    <t>136154222</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 02.02.2026</t>
   </si>
 </sst>
 </file>
@@ -615,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -656,7 +617,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -674,7 +635,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -692,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -710,7 +671,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -728,7 +689,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -746,7 +707,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -764,7 +725,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -782,7 +743,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -800,7 +761,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -818,7 +779,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -836,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -854,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -872,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -890,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -899,7 +860,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -908,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -917,7 +878,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -926,7 +887,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -935,7 +896,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -944,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -953,7 +914,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
@@ -962,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -971,7 +932,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
@@ -980,7 +941,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -989,7 +950,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -998,7 +959,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1007,7 +968,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
@@ -1016,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1025,7 +986,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
@@ -1034,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1004,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
@@ -1052,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1022,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -1070,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1079,7 +1040,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -1088,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1058,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
@@ -1106,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1076,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
@@ -1124,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1094,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -1142,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1112,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
@@ -1160,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1130,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
@@ -1178,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1148,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>8</v>
@@ -1196,7 +1157,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1205,7 +1166,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -1214,7 +1175,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1223,7 +1184,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
@@ -1232,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1241,7 +1202,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
@@ -1250,7 +1211,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1259,7 +1220,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
@@ -1268,7 +1229,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1276,7 +1237,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -1285,7 +1246,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1293,7 +1254,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
@@ -1302,7 +1263,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1310,7 +1271,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
@@ -1319,7 +1280,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1327,7 +1288,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
@@ -1336,7 +1297,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1344,7 +1305,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -1353,7 +1314,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1361,7 +1322,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>8</v>
@@ -1370,7 +1331,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1378,7 +1339,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>8</v>
@@ -1387,7 +1348,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1395,7 +1356,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>8</v>
@@ -1404,196 +1365,9 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05F1168-7D06-4976-AE6B-EE71BFA761BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB224416-B173-49FD-B539-10B0365D7E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="58">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,136 +51,157 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>135624507</t>
+    <t>136409291</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 02.02.2026</t>
-  </si>
-  <si>
-    <t>136378101</t>
-  </si>
-  <si>
-    <t>136448762</t>
-  </si>
-  <si>
-    <t>131017782</t>
-  </si>
-  <si>
-    <t>131130636</t>
-  </si>
-  <si>
-    <t>136374261</t>
-  </si>
-  <si>
-    <t>136283660</t>
-  </si>
-  <si>
-    <t>131545551</t>
-  </si>
-  <si>
-    <t>136449250</t>
-  </si>
-  <si>
-    <t>136300634</t>
-  </si>
-  <si>
-    <t>136445393</t>
-  </si>
-  <si>
-    <t>136388552</t>
-  </si>
-  <si>
-    <t>136275761</t>
-  </si>
-  <si>
-    <t>131517961</t>
-  </si>
-  <si>
-    <t>136275770</t>
-  </si>
-  <si>
-    <t>131563421</t>
-  </si>
-  <si>
-    <t>136465056</t>
-  </si>
-  <si>
-    <t>132193780</t>
-  </si>
-  <si>
-    <t>136440124</t>
-  </si>
-  <si>
-    <t>131446888</t>
-  </si>
-  <si>
-    <t>136471630</t>
-  </si>
-  <si>
-    <t>136448221</t>
-  </si>
-  <si>
-    <t>131535060</t>
-  </si>
-  <si>
-    <t>136402133</t>
-  </si>
-  <si>
-    <t>131128135</t>
-  </si>
-  <si>
-    <t>136251718</t>
-  </si>
-  <si>
-    <t>131224198</t>
-  </si>
-  <si>
-    <t>136419417</t>
-  </si>
-  <si>
-    <t>136361578</t>
-  </si>
-  <si>
-    <t>131557276</t>
-  </si>
-  <si>
-    <t>131340159</t>
-  </si>
-  <si>
-    <t>136339098</t>
-  </si>
-  <si>
-    <t>136376669</t>
-  </si>
-  <si>
-    <t>131373202</t>
-  </si>
-  <si>
-    <t>136446569</t>
-  </si>
-  <si>
-    <t>131224962</t>
-  </si>
-  <si>
-    <t>136247806</t>
-  </si>
-  <si>
-    <t>136466617</t>
-  </si>
-  <si>
-    <t>136439543</t>
-  </si>
-  <si>
-    <t>135671848</t>
-  </si>
-  <si>
-    <t>136154222</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 02.02.2026</t>
+    <t>Nup- Cancelamento 03.02.2026</t>
+  </si>
+  <si>
+    <t>136092542</t>
+  </si>
+  <si>
+    <t>136243852</t>
+  </si>
+  <si>
+    <t>136400498</t>
+  </si>
+  <si>
+    <t>134782586</t>
+  </si>
+  <si>
+    <t>136321417</t>
+  </si>
+  <si>
+    <t>131486043</t>
+  </si>
+  <si>
+    <t>131999960</t>
+  </si>
+  <si>
+    <t>136519485</t>
+  </si>
+  <si>
+    <t>136490037</t>
+  </si>
+  <si>
+    <t>136483688</t>
+  </si>
+  <si>
+    <t>136476259</t>
+  </si>
+  <si>
+    <t>136480128</t>
+  </si>
+  <si>
+    <t>136378407</t>
+  </si>
+  <si>
+    <t>131338741</t>
+  </si>
+  <si>
+    <t>131360065</t>
+  </si>
+  <si>
+    <t>136489880</t>
+  </si>
+  <si>
+    <t>136474752</t>
+  </si>
+  <si>
+    <t>136458647</t>
+  </si>
+  <si>
+    <t>131575898</t>
+  </si>
+  <si>
+    <t>136500351</t>
+  </si>
+  <si>
+    <t>136327465</t>
+  </si>
+  <si>
+    <t>136077848</t>
+  </si>
+  <si>
+    <t>136465246</t>
+  </si>
+  <si>
+    <t>136483894</t>
+  </si>
+  <si>
+    <t>131535485</t>
+  </si>
+  <si>
+    <t>136369780</t>
+  </si>
+  <si>
+    <t>136493445</t>
+  </si>
+  <si>
+    <t>131246112</t>
+  </si>
+  <si>
+    <t>131319995</t>
+  </si>
+  <si>
+    <t>136400321</t>
+  </si>
+  <si>
+    <t>136519821</t>
+  </si>
+  <si>
+    <t>131450060</t>
+  </si>
+  <si>
+    <t>135513888</t>
+  </si>
+  <si>
+    <t>131262198</t>
+  </si>
+  <si>
+    <t>136212984</t>
+  </si>
+  <si>
+    <t>136514818</t>
+  </si>
+  <si>
+    <t>136411283</t>
+  </si>
+  <si>
+    <t>136375661</t>
+  </si>
+  <si>
+    <t>136376579</t>
+  </si>
+  <si>
+    <t>136300500</t>
+  </si>
+  <si>
+    <t>136479422</t>
+  </si>
+  <si>
+    <t>136462493</t>
+  </si>
+  <si>
+    <t>136405514</t>
+  </si>
+  <si>
+    <t>133845768</t>
+  </si>
+  <si>
+    <t>136479102</t>
+  </si>
+  <si>
+    <t>136471752</t>
+  </si>
+  <si>
+    <t>136496332</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 03.02.2026</t>
   </si>
 </sst>
 </file>
@@ -576,7 +597,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -617,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -635,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -653,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -671,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -689,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -707,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -725,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -743,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -761,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -779,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -797,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -815,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -833,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -851,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -860,7 +881,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -869,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -878,7 +899,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -887,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -896,7 +917,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -905,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -914,7 +935,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
@@ -923,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -932,7 +953,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
@@ -941,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -950,7 +971,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -959,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -968,7 +989,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
@@ -977,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -986,7 +1007,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
@@ -995,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1004,7 +1025,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
@@ -1013,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1022,7 +1043,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -1031,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1040,7 +1061,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -1049,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1058,7 +1079,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
@@ -1067,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1076,7 +1097,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
@@ -1085,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1115,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -1103,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1133,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
@@ -1121,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1130,7 +1151,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
@@ -1139,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1148,7 +1169,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>8</v>
@@ -1157,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1166,7 +1187,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -1175,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1184,7 +1205,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
@@ -1193,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1202,7 +1223,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
@@ -1211,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1220,7 +1241,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
@@ -1229,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1237,7 +1258,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -1246,7 +1267,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1254,7 +1275,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
@@ -1263,7 +1284,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1271,7 +1292,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
@@ -1280,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1288,7 +1309,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
@@ -1297,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1305,7 +1326,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -1314,7 +1335,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1322,7 +1343,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>8</v>
@@ -1331,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1339,7 +1360,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>8</v>
@@ -1348,7 +1369,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1356,7 +1377,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>8</v>
@@ -1365,9 +1386,94 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB224416-B173-49FD-B539-10B0365D7E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5B6921-514C-46EA-8C2F-3A437176FAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="60">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -202,13 +202,19 @@
   </si>
   <si>
     <t>Allianz - Cancelamento 03.02.2026</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Allianz - Cancelamento 03.02.2026.xlsx.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +232,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -263,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -278,6 +292,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -597,7 +614,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -641,9 +658,11 @@
         <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -659,9 +678,11 @@
         <v>57</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
+        <v>58</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -677,9 +698,11 @@
         <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4"/>
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -695,9 +718,11 @@
         <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -713,9 +738,11 @@
         <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6"/>
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -731,9 +758,11 @@
         <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7"/>
+        <v>58</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -749,9 +778,11 @@
         <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8"/>
+        <v>58</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -767,9 +798,11 @@
         <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9"/>
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -785,9 +818,11 @@
         <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10"/>
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -803,9 +838,11 @@
         <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11"/>
+        <v>58</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -821,9 +858,11 @@
         <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -839,9 +878,11 @@
         <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -857,9 +898,11 @@
         <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14"/>
+        <v>58</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -875,9 +918,11 @@
         <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15"/>
+        <v>58</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -893,9 +938,11 @@
         <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
+        <v>58</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -911,9 +958,11 @@
         <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
+        <v>58</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -929,9 +978,11 @@
         <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
+        <v>58</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -947,9 +998,11 @@
         <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
+        <v>58</v>
+      </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -965,9 +1018,11 @@
         <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -983,9 +1038,11 @@
         <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
+        <v>58</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1001,9 +1058,11 @@
         <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
+        <v>58</v>
+      </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -1019,9 +1078,11 @@
         <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+        <v>58</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -1037,9 +1098,11 @@
         <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
+        <v>58</v>
+      </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -1055,9 +1118,11 @@
         <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
+        <v>58</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1073,9 +1138,11 @@
         <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
+        <v>58</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1091,9 +1158,11 @@
         <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
+        <v>58</v>
+      </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -1109,9 +1178,11 @@
         <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
+        <v>58</v>
+      </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1127,9 +1198,11 @@
         <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29"/>
+        <v>58</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1145,9 +1218,11 @@
         <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30"/>
+        <v>58</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1163,9 +1238,11 @@
         <v>57</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31"/>
+        <v>58</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -1181,9 +1258,11 @@
         <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32"/>
+        <v>58</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -1199,9 +1278,11 @@
         <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
+        <v>58</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -1217,9 +1298,11 @@
         <v>57</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
+        <v>58</v>
+      </c>
+      <c r="F34" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -1235,9 +1318,11 @@
         <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35"/>
+        <v>58</v>
+      </c>
+      <c r="F35" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -1253,7 +1338,10 @@
         <v>57</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F36" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1270,7 +1358,10 @@
         <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F37" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1287,7 +1378,10 @@
         <v>57</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F38" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1304,7 +1398,10 @@
         <v>57</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F39" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1321,7 +1418,10 @@
         <v>57</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1338,7 +1438,10 @@
         <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F41" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1355,7 +1458,10 @@
         <v>57</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F42" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1372,7 +1478,10 @@
         <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F43" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1391,6 +1500,7 @@
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
@@ -1406,7 +1516,10 @@
         <v>57</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F45" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1423,7 +1536,10 @@
         <v>57</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F46" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1440,7 +1556,10 @@
         <v>57</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="F47" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1457,10 +1576,13 @@
         <v>57</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="F48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
@@ -1474,8 +1596,14 @@
         <v>57</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F49" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F52" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1491,31 +1619,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5B6921-514C-46EA-8C2F-3A437176FAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE42B8A5-AF2B-448C-ACDE-A79D747E6123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="62">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,170 +51,176 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136409291</t>
+    <t>136519782</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 03.02.2026</t>
-  </si>
-  <si>
-    <t>136092542</t>
-  </si>
-  <si>
-    <t>136243852</t>
-  </si>
-  <si>
-    <t>136400498</t>
-  </si>
-  <si>
-    <t>134782586</t>
-  </si>
-  <si>
-    <t>136321417</t>
-  </si>
-  <si>
-    <t>131486043</t>
-  </si>
-  <si>
-    <t>131999960</t>
-  </si>
-  <si>
-    <t>136519485</t>
-  </si>
-  <si>
-    <t>136490037</t>
-  </si>
-  <si>
-    <t>136483688</t>
-  </si>
-  <si>
-    <t>136476259</t>
-  </si>
-  <si>
-    <t>136480128</t>
-  </si>
-  <si>
-    <t>136378407</t>
-  </si>
-  <si>
-    <t>131338741</t>
+    <t>Nup- Cancelamento 04.02.2026</t>
+  </si>
+  <si>
+    <t>136212984</t>
+  </si>
+  <si>
+    <t>136115403</t>
   </si>
   <si>
     <t>131360065</t>
   </si>
   <si>
-    <t>136489880</t>
-  </si>
-  <si>
-    <t>136474752</t>
-  </si>
-  <si>
-    <t>136458647</t>
-  </si>
-  <si>
-    <t>131575898</t>
-  </si>
-  <si>
-    <t>136500351</t>
-  </si>
-  <si>
-    <t>136327465</t>
-  </si>
-  <si>
-    <t>136077848</t>
-  </si>
-  <si>
-    <t>136465246</t>
+    <t>131376287</t>
+  </si>
+  <si>
+    <t>136320601</t>
+  </si>
+  <si>
+    <t>131533382</t>
+  </si>
+  <si>
+    <t>136300534</t>
+  </si>
+  <si>
+    <t>134830896</t>
+  </si>
+  <si>
+    <t>136339624</t>
+  </si>
+  <si>
+    <t>136211598</t>
+  </si>
+  <si>
+    <t>136465631</t>
+  </si>
+  <si>
+    <t>136377891</t>
+  </si>
+  <si>
+    <t>136432105</t>
+  </si>
+  <si>
+    <t>136340018</t>
+  </si>
+  <si>
+    <t>131178625</t>
+  </si>
+  <si>
+    <t>136340269</t>
+  </si>
+  <si>
+    <t>136300758</t>
+  </si>
+  <si>
+    <t>136241574</t>
+  </si>
+  <si>
+    <t>133463704</t>
+  </si>
+  <si>
+    <t>131521945</t>
+  </si>
+  <si>
+    <t>131239130</t>
+  </si>
+  <si>
+    <t>136464855</t>
+  </si>
+  <si>
+    <t>136378250</t>
+  </si>
+  <si>
+    <t>131205304</t>
+  </si>
+  <si>
+    <t>131346874</t>
+  </si>
+  <si>
+    <t>131342919</t>
+  </si>
+  <si>
+    <t>136465433</t>
+  </si>
+  <si>
+    <t>136248986</t>
+  </si>
+  <si>
+    <t>131260652</t>
+  </si>
+  <si>
+    <t>131391305</t>
+  </si>
+  <si>
+    <t>136441458</t>
+  </si>
+  <si>
+    <t>136505741</t>
+  </si>
+  <si>
+    <t>131612847</t>
+  </si>
+  <si>
+    <t>136065112</t>
+  </si>
+  <si>
+    <t>132462400</t>
+  </si>
+  <si>
+    <t>136508214</t>
   </si>
   <si>
     <t>136483894</t>
   </si>
   <si>
-    <t>131535485</t>
-  </si>
-  <si>
-    <t>136369780</t>
-  </si>
-  <si>
-    <t>136493445</t>
-  </si>
-  <si>
-    <t>131246112</t>
-  </si>
-  <si>
-    <t>131319995</t>
-  </si>
-  <si>
-    <t>136400321</t>
-  </si>
-  <si>
-    <t>136519821</t>
-  </si>
-  <si>
-    <t>131450060</t>
-  </si>
-  <si>
-    <t>135513888</t>
-  </si>
-  <si>
-    <t>131262198</t>
-  </si>
-  <si>
-    <t>136212984</t>
-  </si>
-  <si>
-    <t>136514818</t>
-  </si>
-  <si>
-    <t>136411283</t>
-  </si>
-  <si>
-    <t>136375661</t>
-  </si>
-  <si>
-    <t>136376579</t>
-  </si>
-  <si>
-    <t>136300500</t>
-  </si>
-  <si>
-    <t>136479422</t>
-  </si>
-  <si>
-    <t>136462493</t>
-  </si>
-  <si>
-    <t>136405514</t>
-  </si>
-  <si>
-    <t>133845768</t>
-  </si>
-  <si>
-    <t>136479102</t>
-  </si>
-  <si>
-    <t>136471752</t>
-  </si>
-  <si>
-    <t>136496332</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 03.02.2026</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Allianz - Cancelamento 03.02.2026.xlsx.</t>
+    <t>136183846</t>
+  </si>
+  <si>
+    <t>136545742</t>
+  </si>
+  <si>
+    <t>136339880</t>
+  </si>
+  <si>
+    <t>136118395</t>
+  </si>
+  <si>
+    <t>136284460</t>
+  </si>
+  <si>
+    <t>135578401</t>
+  </si>
+  <si>
+    <t>131441935</t>
+  </si>
+  <si>
+    <t>136519919</t>
+  </si>
+  <si>
+    <t>136500664</t>
+  </si>
+  <si>
+    <t>135894986</t>
+  </si>
+  <si>
+    <t>136445471</t>
+  </si>
+  <si>
+    <t>136476386</t>
+  </si>
+  <si>
+    <t>136446236</t>
+  </si>
+  <si>
+    <t>133602867</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 04.02.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,14 +238,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -277,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -292,9 +290,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -614,7 +609,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -655,14 +650,12 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -675,14 +668,12 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -695,14 +686,12 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -715,14 +704,12 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -735,14 +722,12 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -755,14 +740,12 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -775,14 +758,12 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -795,14 +776,12 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -815,14 +794,12 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -835,14 +812,12 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -855,14 +830,12 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -875,14 +848,12 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -895,14 +866,12 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -915,14 +884,12 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -935,14 +902,12 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -955,14 +920,12 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -975,14 +938,12 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -995,14 +956,12 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -1015,14 +974,12 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -1035,14 +992,12 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1055,14 +1010,12 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -1075,14 +1028,12 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -1095,14 +1046,12 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -1115,14 +1064,12 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1135,14 +1082,12 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1155,14 +1100,12 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -1175,14 +1118,12 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1195,14 +1136,12 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1215,14 +1154,12 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1235,14 +1172,12 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -1255,14 +1190,12 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F32"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -1275,14 +1208,12 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F33"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -1295,14 +1226,12 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -1315,14 +1244,12 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F35"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -1335,13 +1262,10 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1355,13 +1279,10 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1375,13 +1296,10 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1395,13 +1313,10 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,13 +1330,10 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1435,13 +1347,10 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F41" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1455,13 +1364,10 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1475,13 +1381,10 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1495,12 +1398,11 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
@@ -1513,13 +1415,10 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1533,13 +1432,10 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F46" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1553,13 +1449,10 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1573,16 +1466,13 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
@@ -1593,17 +1483,79 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F49" t="s">
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F52" s="6"/>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1619,31 +1571,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE42B8A5-AF2B-448C-ACDE-A79D747E6123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0782B8D-1636-428E-8802-7FDB8ED83BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,7 +213,7 @@
     <t>133602867</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 04.02.2026</t>
+    <t>Allianz-Cancelamento 04.02.2026</t>
   </si>
 </sst>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB83D6E4-8C55-4119-95BD-DD92B88F3849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="52">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,141 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136568550</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.02.2026</t>
+  </si>
+  <si>
+    <t>136400372</t>
+  </si>
+  <si>
+    <t>136459586</t>
+  </si>
+  <si>
+    <t>136500475</t>
+  </si>
+  <si>
+    <t>136495708</t>
+  </si>
+  <si>
+    <t>136378473</t>
+  </si>
+  <si>
+    <t>136500545</t>
+  </si>
+  <si>
+    <t>136432659</t>
+  </si>
+  <si>
+    <t>131239593</t>
+  </si>
+  <si>
+    <t>136321158</t>
+  </si>
+  <si>
+    <t>136338264</t>
+  </si>
+  <si>
+    <t>136500464</t>
+  </si>
+  <si>
+    <t>136400259</t>
+  </si>
+  <si>
+    <t>136473015</t>
+  </si>
+  <si>
+    <t>131557490</t>
+  </si>
+  <si>
+    <t>136473010</t>
+  </si>
+  <si>
+    <t>136321331</t>
+  </si>
+  <si>
+    <t>136378465</t>
+  </si>
+  <si>
+    <t>131196891</t>
+  </si>
+  <si>
+    <t>136319603</t>
+  </si>
+  <si>
+    <t>136466447</t>
+  </si>
+  <si>
+    <t>136347414</t>
+  </si>
+  <si>
+    <t>136402194</t>
+  </si>
+  <si>
+    <t>136580358</t>
+  </si>
+  <si>
+    <t>136283396</t>
+  </si>
+  <si>
+    <t>131478174</t>
+  </si>
+  <si>
+    <t>136275775</t>
+  </si>
+  <si>
+    <t>136463511</t>
+  </si>
+  <si>
+    <t>136446236</t>
+  </si>
+  <si>
+    <t>136376579</t>
+  </si>
+  <si>
+    <t>136440279</t>
+  </si>
+  <si>
+    <t>136378181</t>
+  </si>
+  <si>
+    <t>136420152</t>
+  </si>
+  <si>
+    <t>136569208</t>
+  </si>
+  <si>
+    <t>131472708</t>
+  </si>
+  <si>
+    <t>131133890</t>
+  </si>
+  <si>
+    <t>131373540</t>
+  </si>
+  <si>
+    <t>136424014</t>
+  </si>
+  <si>
+    <t>136540567</t>
+  </si>
+  <si>
+    <t>136400386</t>
+  </si>
+  <si>
+    <t>136109430</t>
+  </si>
+  <si>
+    <t>136578771</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 05.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +610,752 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1371,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A158803-4A67-42DE-995D-2781F28FE7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="60">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,165 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136507517</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 09.02.2026</t>
+  </si>
+  <si>
+    <t>136460557</t>
+  </si>
+  <si>
+    <t>136577526</t>
+  </si>
+  <si>
+    <t>136493802</t>
+  </si>
+  <si>
+    <t>136459099</t>
+  </si>
+  <si>
+    <t>136476120</t>
+  </si>
+  <si>
+    <t>131371830</t>
+  </si>
+  <si>
+    <t>136376021</t>
+  </si>
+  <si>
+    <t>131575100</t>
+  </si>
+  <si>
+    <t>131373671</t>
+  </si>
+  <si>
+    <t>136356894</t>
+  </si>
+  <si>
+    <t>131277925</t>
+  </si>
+  <si>
+    <t>131724869</t>
+  </si>
+  <si>
+    <t>131399180</t>
+  </si>
+  <si>
+    <t>136460130</t>
+  </si>
+  <si>
+    <t>136436280</t>
+  </si>
+  <si>
+    <t>136101445</t>
+  </si>
+  <si>
+    <t>136592170</t>
+  </si>
+  <si>
+    <t>136475950</t>
+  </si>
+  <si>
+    <t>131265718</t>
+  </si>
+  <si>
+    <t>136550912</t>
+  </si>
+  <si>
+    <t>136444870</t>
+  </si>
+  <si>
+    <t>136580070</t>
+  </si>
+  <si>
+    <t>131402845</t>
+  </si>
+  <si>
+    <t>131565175</t>
+  </si>
+  <si>
+    <t>136353048</t>
+  </si>
+  <si>
+    <t>136495125</t>
+  </si>
+  <si>
+    <t>136378474</t>
+  </si>
+  <si>
+    <t>133626249</t>
+  </si>
+  <si>
+    <t>136546617</t>
+  </si>
+  <si>
+    <t>131351243</t>
+  </si>
+  <si>
+    <t>135208860</t>
+  </si>
+  <si>
+    <t>131665701</t>
+  </si>
+  <si>
+    <t>131502014</t>
+  </si>
+  <si>
+    <t>136419956</t>
+  </si>
+  <si>
+    <t>131467764</t>
+  </si>
+  <si>
+    <t>131579583</t>
+  </si>
+  <si>
+    <t>136554112</t>
+  </si>
+  <si>
+    <t>131430843</t>
+  </si>
+  <si>
+    <t>136167667</t>
+  </si>
+  <si>
+    <t>136500753</t>
+  </si>
+  <si>
+    <t>133002966</t>
+  </si>
+  <si>
+    <t>136512866</t>
+  </si>
+  <si>
+    <t>136590604</t>
+  </si>
+  <si>
+    <t>136300627</t>
+  </si>
+  <si>
+    <t>136241693</t>
+  </si>
+  <si>
+    <t>136438074</t>
+  </si>
+  <si>
+    <t>135559563</t>
+  </si>
+  <si>
+    <t>136549187</t>
+  </si>
+  <si>
+    <t>136352831</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 09.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +603,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +634,905 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1548,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A158803-4A67-42DE-995D-2781F28FE7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5358842C-7EDD-45B2-9ED3-9301FEE87E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="65">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,163 +51,178 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136507517</t>
+    <t>131558244</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 09.02.2026</t>
-  </si>
-  <si>
-    <t>136460557</t>
-  </si>
-  <si>
-    <t>136577526</t>
-  </si>
-  <si>
-    <t>136493802</t>
-  </si>
-  <si>
-    <t>136459099</t>
-  </si>
-  <si>
-    <t>136476120</t>
-  </si>
-  <si>
-    <t>131371830</t>
-  </si>
-  <si>
-    <t>136376021</t>
-  </si>
-  <si>
-    <t>131575100</t>
-  </si>
-  <si>
-    <t>131373671</t>
-  </si>
-  <si>
-    <t>136356894</t>
-  </si>
-  <si>
-    <t>131277925</t>
-  </si>
-  <si>
-    <t>131724869</t>
-  </si>
-  <si>
-    <t>131399180</t>
-  </si>
-  <si>
-    <t>136460130</t>
-  </si>
-  <si>
-    <t>136436280</t>
-  </si>
-  <si>
-    <t>136101445</t>
-  </si>
-  <si>
-    <t>136592170</t>
-  </si>
-  <si>
-    <t>136475950</t>
-  </si>
-  <si>
-    <t>131265718</t>
-  </si>
-  <si>
-    <t>136550912</t>
-  </si>
-  <si>
-    <t>136444870</t>
+    <t>Nup- Cancelamento 10.02.2026</t>
+  </si>
+  <si>
+    <t>136378329</t>
+  </si>
+  <si>
+    <t>136359460</t>
+  </si>
+  <si>
+    <t>136571253</t>
+  </si>
+  <si>
+    <t>136547738</t>
+  </si>
+  <si>
+    <t>136512866</t>
+  </si>
+  <si>
+    <t>136596025</t>
+  </si>
+  <si>
+    <t>136605098</t>
+  </si>
+  <si>
+    <t>136433528</t>
+  </si>
+  <si>
+    <t>136438059</t>
+  </si>
+  <si>
+    <t>136378413</t>
+  </si>
+  <si>
+    <t>136583288</t>
+  </si>
+  <si>
+    <t>131470752</t>
+  </si>
+  <si>
+    <t>136548886</t>
+  </si>
+  <si>
+    <t>136543671</t>
+  </si>
+  <si>
+    <t>136566046</t>
+  </si>
+  <si>
+    <t>136340255</t>
+  </si>
+  <si>
+    <t>136577450</t>
+  </si>
+  <si>
+    <t>131678239</t>
+  </si>
+  <si>
+    <t>136473844</t>
+  </si>
+  <si>
+    <t>131221201</t>
+  </si>
+  <si>
+    <t>136466294</t>
+  </si>
+  <si>
+    <t>131460359</t>
+  </si>
+  <si>
+    <t>131565068</t>
+  </si>
+  <si>
+    <t>131315922</t>
+  </si>
+  <si>
+    <t>136633229</t>
+  </si>
+  <si>
+    <t>131704309</t>
+  </si>
+  <si>
+    <t>131287730</t>
+  </si>
+  <si>
+    <t>136077847</t>
+  </si>
+  <si>
+    <t>132180593</t>
+  </si>
+  <si>
+    <t>136499606</t>
+  </si>
+  <si>
+    <t>134441960</t>
+  </si>
+  <si>
+    <t>136378360</t>
+  </si>
+  <si>
+    <t>131501824</t>
+  </si>
+  <si>
+    <t>131333985</t>
+  </si>
+  <si>
+    <t>136570021</t>
   </si>
   <si>
     <t>136580070</t>
   </si>
   <si>
-    <t>131402845</t>
-  </si>
-  <si>
-    <t>131565175</t>
-  </si>
-  <si>
-    <t>136353048</t>
-  </si>
-  <si>
-    <t>136495125</t>
-  </si>
-  <si>
-    <t>136378474</t>
-  </si>
-  <si>
-    <t>133626249</t>
-  </si>
-  <si>
-    <t>136546617</t>
-  </si>
-  <si>
-    <t>131351243</t>
-  </si>
-  <si>
-    <t>135208860</t>
-  </si>
-  <si>
-    <t>131665701</t>
-  </si>
-  <si>
-    <t>131502014</t>
-  </si>
-  <si>
-    <t>136419956</t>
-  </si>
-  <si>
-    <t>131467764</t>
-  </si>
-  <si>
-    <t>131579583</t>
+    <t>136400446</t>
+  </si>
+  <si>
+    <t>131331315</t>
+  </si>
+  <si>
+    <t>136519224</t>
   </si>
   <si>
     <t>136554112</t>
   </si>
   <si>
-    <t>131430843</t>
-  </si>
-  <si>
-    <t>136167667</t>
-  </si>
-  <si>
-    <t>136500753</t>
-  </si>
-  <si>
-    <t>133002966</t>
-  </si>
-  <si>
-    <t>136512866</t>
-  </si>
-  <si>
-    <t>136590604</t>
-  </si>
-  <si>
-    <t>136300627</t>
-  </si>
-  <si>
-    <t>136241693</t>
-  </si>
-  <si>
-    <t>136438074</t>
-  </si>
-  <si>
-    <t>135559563</t>
-  </si>
-  <si>
-    <t>136549187</t>
-  </si>
-  <si>
-    <t>136352831</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 09.02.2026</t>
+    <t>136400329</t>
+  </si>
+  <si>
+    <t>136633617</t>
+  </si>
+  <si>
+    <t>136542840</t>
+  </si>
+  <si>
+    <t>136644047</t>
+  </si>
+  <si>
+    <t>136419611</t>
+  </si>
+  <si>
+    <t>136636095</t>
+  </si>
+  <si>
+    <t>136639628</t>
+  </si>
+  <si>
+    <t>136551234</t>
+  </si>
+  <si>
+    <t>136595018</t>
+  </si>
+  <si>
+    <t>136301068</t>
+  </si>
+  <si>
+    <t>132930937</t>
+  </si>
+  <si>
+    <t>136500555</t>
+  </si>
+  <si>
+    <t>136340236</t>
+  </si>
+  <si>
+    <t>131455926</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamentoo 10.02.2026</t>
   </si>
 </sst>
 </file>
@@ -603,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -644,7 +659,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -662,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -680,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -698,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -716,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -734,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -752,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -770,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -788,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -806,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -824,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -833,7 +848,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
@@ -842,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -851,7 +866,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
@@ -860,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -869,7 +884,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
@@ -878,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -887,7 +902,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -896,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -905,7 +920,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -914,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -923,7 +938,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -932,7 +947,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -941,7 +956,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
@@ -950,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -959,7 +974,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
@@ -968,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -977,7 +992,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -986,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -995,7 +1010,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
@@ -1004,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,7 +1028,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
@@ -1022,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1031,7 +1046,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
@@ -1040,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1049,7 +1064,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -1058,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1067,7 +1082,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -1076,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1085,7 +1100,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
@@ -1094,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1103,7 +1118,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
@@ -1112,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1121,7 +1136,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -1130,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1139,7 +1154,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
@@ -1148,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1157,7 +1172,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
@@ -1166,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1175,7 +1190,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>8</v>
@@ -1184,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1193,7 +1208,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -1202,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1211,7 +1226,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
@@ -1220,7 +1235,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1229,7 +1244,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
@@ -1238,7 +1253,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1247,7 +1262,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
@@ -1256,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1264,7 +1279,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -1273,7 +1288,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1281,7 +1296,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
@@ -1290,7 +1305,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1298,7 +1313,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
@@ -1307,7 +1322,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1315,7 +1330,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
@@ -1324,7 +1339,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1332,7 +1347,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -1341,7 +1356,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1349,7 +1364,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>8</v>
@@ -1358,7 +1373,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1366,7 +1381,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>8</v>
@@ -1375,7 +1390,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1383,7 +1398,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>8</v>
@@ -1392,7 +1407,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1400,7 +1415,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>8</v>
@@ -1409,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1417,7 +1432,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>8</v>
@@ -1426,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1434,7 +1449,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>8</v>
@@ -1443,7 +1458,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1451,7 +1466,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>8</v>
@@ -1460,7 +1475,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1468,7 +1483,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>8</v>
@@ -1477,7 +1492,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1485,7 +1500,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>8</v>
@@ -1494,7 +1509,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1502,7 +1517,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>8</v>
@@ -1511,7 +1526,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1519,7 +1534,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>8</v>
@@ -1528,9 +1543,94 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5358842C-7EDD-45B2-9ED3-9301FEE87E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43ACBB37-E5E7-459F-86AD-3D2708FB9FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="58">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,7 +51,7 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>131558244</t>
+    <t>131570425</t>
   </si>
   <si>
     <t>1070</t>
@@ -60,169 +60,148 @@
     <t>Nup- Cancelamento 10.02.2026</t>
   </si>
   <si>
-    <t>136378329</t>
-  </si>
-  <si>
-    <t>136359460</t>
-  </si>
-  <si>
-    <t>136571253</t>
-  </si>
-  <si>
-    <t>136547738</t>
-  </si>
-  <si>
-    <t>136512866</t>
-  </si>
-  <si>
-    <t>136596025</t>
-  </si>
-  <si>
-    <t>136605098</t>
-  </si>
-  <si>
-    <t>136433528</t>
-  </si>
-  <si>
-    <t>136438059</t>
-  </si>
-  <si>
-    <t>136378413</t>
-  </si>
-  <si>
-    <t>136583288</t>
-  </si>
-  <si>
-    <t>131470752</t>
-  </si>
-  <si>
-    <t>136548886</t>
-  </si>
-  <si>
-    <t>136543671</t>
-  </si>
-  <si>
-    <t>136566046</t>
-  </si>
-  <si>
-    <t>136340255</t>
-  </si>
-  <si>
-    <t>136577450</t>
-  </si>
-  <si>
-    <t>131678239</t>
-  </si>
-  <si>
-    <t>136473844</t>
-  </si>
-  <si>
-    <t>131221201</t>
-  </si>
-  <si>
-    <t>136466294</t>
-  </si>
-  <si>
-    <t>131460359</t>
-  </si>
-  <si>
-    <t>131565068</t>
-  </si>
-  <si>
-    <t>131315922</t>
-  </si>
-  <si>
-    <t>136633229</t>
-  </si>
-  <si>
-    <t>131704309</t>
-  </si>
-  <si>
-    <t>131287730</t>
-  </si>
-  <si>
-    <t>136077847</t>
-  </si>
-  <si>
-    <t>132180593</t>
-  </si>
-  <si>
-    <t>136499606</t>
-  </si>
-  <si>
-    <t>134441960</t>
-  </si>
-  <si>
-    <t>136378360</t>
-  </si>
-  <si>
-    <t>131501824</t>
-  </si>
-  <si>
-    <t>131333985</t>
-  </si>
-  <si>
-    <t>136570021</t>
-  </si>
-  <si>
-    <t>136580070</t>
-  </si>
-  <si>
-    <t>136400446</t>
-  </si>
-  <si>
-    <t>131331315</t>
-  </si>
-  <si>
-    <t>136519224</t>
-  </si>
-  <si>
-    <t>136554112</t>
-  </si>
-  <si>
-    <t>136400329</t>
-  </si>
-  <si>
-    <t>136633617</t>
-  </si>
-  <si>
-    <t>136542840</t>
-  </si>
-  <si>
-    <t>136644047</t>
-  </si>
-  <si>
-    <t>136419611</t>
-  </si>
-  <si>
-    <t>136636095</t>
-  </si>
-  <si>
-    <t>136639628</t>
-  </si>
-  <si>
-    <t>136551234</t>
-  </si>
-  <si>
-    <t>136595018</t>
-  </si>
-  <si>
-    <t>136301068</t>
-  </si>
-  <si>
-    <t>132930937</t>
-  </si>
-  <si>
-    <t>136500555</t>
-  </si>
-  <si>
-    <t>136340236</t>
-  </si>
-  <si>
-    <t>131455926</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamentoo 10.02.2026</t>
+    <t>136649704</t>
+  </si>
+  <si>
+    <t>131148886</t>
+  </si>
+  <si>
+    <t>136528200</t>
+  </si>
+  <si>
+    <t>136628653</t>
+  </si>
+  <si>
+    <t>131650955</t>
+  </si>
+  <si>
+    <t>131625558</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 11.02.2026</t>
+  </si>
+  <si>
+    <t>131559988</t>
+  </si>
+  <si>
+    <t>136357576</t>
+  </si>
+  <si>
+    <t>136404324</t>
+  </si>
+  <si>
+    <t>136300462</t>
+  </si>
+  <si>
+    <t>136400454</t>
+  </si>
+  <si>
+    <t>136458022</t>
+  </si>
+  <si>
+    <t>131327595</t>
+  </si>
+  <si>
+    <t>136566494</t>
+  </si>
+  <si>
+    <t>136653408</t>
+  </si>
+  <si>
+    <t>136500575</t>
+  </si>
+  <si>
+    <t>136300477</t>
+  </si>
+  <si>
+    <t>131666717</t>
+  </si>
+  <si>
+    <t>131612290</t>
+  </si>
+  <si>
+    <t>131348233</t>
+  </si>
+  <si>
+    <t>136659192</t>
+  </si>
+  <si>
+    <t>136553134</t>
+  </si>
+  <si>
+    <t>131382990</t>
+  </si>
+  <si>
+    <t>136541423</t>
+  </si>
+  <si>
+    <t>136448712</t>
+  </si>
+  <si>
+    <t>131448309</t>
+  </si>
+  <si>
+    <t>131693225</t>
+  </si>
+  <si>
+    <t>136576555</t>
+  </si>
+  <si>
+    <t>136568412</t>
+  </si>
+  <si>
+    <t>136358522</t>
+  </si>
+  <si>
+    <t>136459311</t>
+  </si>
+  <si>
+    <t>136569472</t>
+  </si>
+  <si>
+    <t>131632355</t>
+  </si>
+  <si>
+    <t>136547735</t>
+  </si>
+  <si>
+    <t>131740897</t>
+  </si>
+  <si>
+    <t>136377974</t>
+  </si>
+  <si>
+    <t>136539671</t>
+  </si>
+  <si>
+    <t>131481105</t>
+  </si>
+  <si>
+    <t>136449985</t>
+  </si>
+  <si>
+    <t>136400878</t>
+  </si>
+  <si>
+    <t>131493387</t>
+  </si>
+  <si>
+    <t>136651167</t>
+  </si>
+  <si>
+    <t>136506288</t>
+  </si>
+  <si>
+    <t>136648173</t>
+  </si>
+  <si>
+    <t>136357540</t>
+  </si>
+  <si>
+    <t>136694836</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 11.02.2026</t>
   </si>
 </sst>
 </file>
@@ -618,7 +597,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -659,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -677,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -695,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -713,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -731,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -749,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -764,10 +743,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -776,16 +755,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -794,16 +773,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -812,16 +791,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -830,16 +809,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -848,16 +827,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -866,16 +845,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -884,16 +863,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -902,16 +881,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -920,16 +899,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -938,16 +917,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -956,16 +935,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -974,16 +953,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -992,16 +971,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1016,10 +995,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1034,10 +1013,10 @@
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1052,10 +1031,10 @@
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1070,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1088,10 +1067,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1106,10 +1085,10 @@
         <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1124,10 +1103,10 @@
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1142,10 +1121,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1160,10 +1139,10 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1178,10 +1157,10 @@
         <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1196,10 +1175,10 @@
         <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1214,10 +1193,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1232,10 +1211,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1250,10 +1229,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1268,10 +1247,10 @@
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1285,10 +1264,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1302,10 +1281,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1319,10 +1298,10 @@
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1336,10 +1315,10 @@
         <v>8</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1353,10 +1332,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1370,10 +1349,10 @@
         <v>8</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1387,10 +1366,10 @@
         <v>8</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1404,10 +1383,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1421,10 +1400,10 @@
         <v>8</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1438,10 +1417,10 @@
         <v>8</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1455,10 +1434,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1472,10 +1451,10 @@
         <v>8</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1489,148 +1468,12 @@
         <v>8</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43ACBB37-E5E7-459F-86AD-3D2708FB9FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA38CF2C-0E43-4977-B288-4AC25F71A044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="65">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,157 +51,178 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>131570425</t>
+    <t>136693630</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 10.02.2026</t>
-  </si>
-  <si>
-    <t>136649704</t>
-  </si>
-  <si>
-    <t>131148886</t>
-  </si>
-  <si>
-    <t>136528200</t>
-  </si>
-  <si>
-    <t>136628653</t>
-  </si>
-  <si>
-    <t>131650955</t>
-  </si>
-  <si>
-    <t>131625558</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 11.02.2026</t>
-  </si>
-  <si>
-    <t>131559988</t>
-  </si>
-  <si>
-    <t>136357576</t>
-  </si>
-  <si>
-    <t>136404324</t>
-  </si>
-  <si>
-    <t>136300462</t>
-  </si>
-  <si>
-    <t>136400454</t>
-  </si>
-  <si>
-    <t>136458022</t>
-  </si>
-  <si>
-    <t>131327595</t>
-  </si>
-  <si>
-    <t>136566494</t>
-  </si>
-  <si>
-    <t>136653408</t>
-  </si>
-  <si>
-    <t>136500575</t>
-  </si>
-  <si>
-    <t>136300477</t>
-  </si>
-  <si>
-    <t>131666717</t>
-  </si>
-  <si>
-    <t>131612290</t>
-  </si>
-  <si>
-    <t>131348233</t>
-  </si>
-  <si>
-    <t>136659192</t>
-  </si>
-  <si>
-    <t>136553134</t>
-  </si>
-  <si>
-    <t>131382990</t>
-  </si>
-  <si>
-    <t>136541423</t>
-  </si>
-  <si>
-    <t>136448712</t>
-  </si>
-  <si>
-    <t>131448309</t>
-  </si>
-  <si>
-    <t>131693225</t>
-  </si>
-  <si>
-    <t>136576555</t>
-  </si>
-  <si>
-    <t>136568412</t>
-  </si>
-  <si>
-    <t>136358522</t>
-  </si>
-  <si>
-    <t>136459311</t>
-  </si>
-  <si>
-    <t>136569472</t>
-  </si>
-  <si>
-    <t>131632355</t>
-  </si>
-  <si>
-    <t>136547735</t>
-  </si>
-  <si>
-    <t>131740897</t>
-  </si>
-  <si>
-    <t>136377974</t>
-  </si>
-  <si>
-    <t>136539671</t>
-  </si>
-  <si>
-    <t>131481105</t>
-  </si>
-  <si>
-    <t>136449985</t>
-  </si>
-  <si>
-    <t>136400878</t>
-  </si>
-  <si>
-    <t>131493387</t>
-  </si>
-  <si>
-    <t>136651167</t>
-  </si>
-  <si>
-    <t>136506288</t>
-  </si>
-  <si>
-    <t>136648173</t>
-  </si>
-  <si>
-    <t>136357540</t>
-  </si>
-  <si>
-    <t>136694836</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 11.02.2026</t>
+    <t>Nup- Cancelamento 12.02.2026</t>
+  </si>
+  <si>
+    <t>136629898</t>
+  </si>
+  <si>
+    <t>136438158</t>
+  </si>
+  <si>
+    <t>136400899</t>
+  </si>
+  <si>
+    <t>136508937</t>
+  </si>
+  <si>
+    <t>136300899</t>
+  </si>
+  <si>
+    <t>136564443 </t>
+  </si>
+  <si>
+    <t>136674851</t>
+  </si>
+  <si>
+    <t>136702073</t>
+  </si>
+  <si>
+    <t>136709550</t>
+  </si>
+  <si>
+    <t>131440216</t>
+  </si>
+  <si>
+    <t>131571031</t>
+  </si>
+  <si>
+    <t>136539631</t>
+  </si>
+  <si>
+    <t>136555458</t>
+  </si>
+  <si>
+    <t>136377096</t>
+  </si>
+  <si>
+    <t>136690908</t>
+  </si>
+  <si>
+    <t>136437496</t>
+  </si>
+  <si>
+    <t>136628738</t>
+  </si>
+  <si>
+    <t>136572298</t>
+  </si>
+  <si>
+    <t>136694847</t>
+  </si>
+  <si>
+    <t>131557885</t>
+  </si>
+  <si>
+    <t>135988974</t>
+  </si>
+  <si>
+    <t>136377465</t>
+  </si>
+  <si>
+    <t>136519828</t>
+  </si>
+  <si>
+    <t>135668756</t>
+  </si>
+  <si>
+    <t>135850332</t>
+  </si>
+  <si>
+    <t>136628548</t>
+  </si>
+  <si>
+    <t>136719088 </t>
+  </si>
+  <si>
+    <t>133557458</t>
+  </si>
+  <si>
+    <t>131491375</t>
+  </si>
+  <si>
+    <t>131475792</t>
+  </si>
+  <si>
+    <t>136628305</t>
+  </si>
+  <si>
+    <t>132888485</t>
+  </si>
+  <si>
+    <t>131438717</t>
+  </si>
+  <si>
+    <t>131470593</t>
+  </si>
+  <si>
+    <t>136693728</t>
+  </si>
+  <si>
+    <t>136459349</t>
+  </si>
+  <si>
+    <t>136540476</t>
+  </si>
+  <si>
+    <t>136438267</t>
+  </si>
+  <si>
+    <t>136711239</t>
+  </si>
+  <si>
+    <t>136446209</t>
+  </si>
+  <si>
+    <t>136550848</t>
+  </si>
+  <si>
+    <t>131574180</t>
+  </si>
+  <si>
+    <t>131668194</t>
+  </si>
+  <si>
+    <t>136378484</t>
+  </si>
+  <si>
+    <t>136409998</t>
+  </si>
+  <si>
+    <t>136460099</t>
+  </si>
+  <si>
+    <t>136580198</t>
+  </si>
+  <si>
+    <t>135588762</t>
+  </si>
+  <si>
+    <t>136400361</t>
+  </si>
+  <si>
+    <t>136652517</t>
+  </si>
+  <si>
+    <t>136558522</t>
+  </si>
+  <si>
+    <t>136677717</t>
+  </si>
+  <si>
+    <t>136460019</t>
+  </si>
+  <si>
+    <t>136595596 </t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 12.02.2026</t>
   </si>
 </sst>
 </file>
@@ -597,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -638,7 +659,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -656,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -674,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -692,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -710,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -728,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -743,10 +764,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -755,16 +776,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -773,16 +794,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -791,16 +812,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -809,16 +830,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -827,16 +848,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -845,16 +866,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -863,16 +884,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -881,16 +902,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -899,16 +920,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -917,16 +938,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -935,16 +956,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -953,16 +974,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -971,16 +992,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -995,10 +1016,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,10 +1034,10 @@
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1031,10 +1052,10 @@
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1049,10 +1070,10 @@
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1067,10 +1088,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1085,10 +1106,10 @@
         <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1103,10 +1124,10 @@
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1121,10 +1142,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1139,10 +1160,10 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1157,10 +1178,10 @@
         <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1175,10 +1196,10 @@
         <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1193,10 +1214,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1211,10 +1232,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1229,10 +1250,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1247,10 +1268,10 @@
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1264,10 +1285,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1281,10 +1302,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1298,10 +1319,10 @@
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1315,10 +1336,10 @@
         <v>8</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1332,10 +1353,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1349,10 +1370,10 @@
         <v>8</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1366,10 +1387,10 @@
         <v>8</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1383,10 +1404,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1400,10 +1421,10 @@
         <v>8</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1417,10 +1438,10 @@
         <v>8</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1434,10 +1455,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1451,10 +1472,10 @@
         <v>8</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1468,12 +1489,142 @@
         <v>8</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C674ED02-C257-49CF-AE9F-BE73EC74C19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="57">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,156 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>131581275</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 18.02.2026</t>
+  </si>
+  <si>
+    <t>131537058</t>
+  </si>
+  <si>
+    <t>131493533</t>
+  </si>
+  <si>
+    <t>131606285</t>
+  </si>
+  <si>
+    <t>136765795</t>
+  </si>
+  <si>
+    <t>136693712</t>
+  </si>
+  <si>
+    <t>136446389</t>
+  </si>
+  <si>
+    <t>136738923</t>
+  </si>
+  <si>
+    <t>136627284</t>
+  </si>
+  <si>
+    <t>136765632</t>
+  </si>
+  <si>
+    <t>131654462</t>
+  </si>
+  <si>
+    <t>131571078</t>
+  </si>
+  <si>
+    <t>136767669</t>
+  </si>
+  <si>
+    <t>136548505</t>
+  </si>
+  <si>
+    <t>136738929</t>
+  </si>
+  <si>
+    <t>136465023</t>
+  </si>
+  <si>
+    <t>133740888</t>
+  </si>
+  <si>
+    <t>131570445</t>
+  </si>
+  <si>
+    <t>136427291</t>
+  </si>
+  <si>
+    <t>131588063</t>
+  </si>
+  <si>
+    <t>136500473</t>
+  </si>
+  <si>
+    <t>131375288</t>
+  </si>
+  <si>
+    <t>136628672</t>
+  </si>
+  <si>
+    <t>136721957</t>
+  </si>
+  <si>
+    <t>136169305</t>
+  </si>
+  <si>
+    <t>131709436</t>
+  </si>
+  <si>
+    <t>136400287</t>
+  </si>
+  <si>
+    <t>136543219</t>
+  </si>
+  <si>
+    <t>131281816</t>
+  </si>
+  <si>
+    <t>136662728</t>
+  </si>
+  <si>
+    <t>136701821</t>
+  </si>
+  <si>
+    <t>131641658</t>
+  </si>
+  <si>
+    <t>136569217</t>
+  </si>
+  <si>
+    <t>131701698</t>
+  </si>
+  <si>
+    <t>131316777</t>
+  </si>
+  <si>
+    <t>136542052</t>
+  </si>
+  <si>
+    <t>136194454</t>
+  </si>
+  <si>
+    <t>136765597</t>
+  </si>
+  <si>
+    <t>136694026</t>
+  </si>
+  <si>
+    <t>136723690</t>
+  </si>
+  <si>
+    <t>131670310</t>
+  </si>
+  <si>
+    <t>136692709</t>
+  </si>
+  <si>
+    <t>136710199</t>
+  </si>
+  <si>
+    <t>136765182</t>
+  </si>
+  <si>
+    <t>136628856</t>
+  </si>
+  <si>
+    <t>132795605</t>
+  </si>
+  <si>
+    <t>136231870</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 18.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +625,854 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1488,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAC6390-5CA2-432B-A127-E9A54B71E945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,111 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136770190</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 19.02.2026</t>
+  </si>
+  <si>
+    <t>136725985</t>
+  </si>
+  <si>
+    <t>136738752</t>
+  </si>
+  <si>
+    <t>136767869</t>
+  </si>
+  <si>
+    <t>131406512</t>
+  </si>
+  <si>
+    <t>131687319</t>
+  </si>
+  <si>
+    <t>136561663</t>
+  </si>
+  <si>
+    <t>136764686</t>
+  </si>
+  <si>
+    <t>131691808</t>
+  </si>
+  <si>
+    <t>136790843</t>
+  </si>
+  <si>
+    <t>131571682</t>
+  </si>
+  <si>
+    <t>136734602</t>
+  </si>
+  <si>
+    <t>136787692</t>
+  </si>
+  <si>
+    <t>136762250</t>
+  </si>
+  <si>
+    <t>136738882</t>
+  </si>
+  <si>
+    <t>131470127</t>
+  </si>
+  <si>
+    <t>136765766</t>
+  </si>
+  <si>
+    <t>136378023</t>
+  </si>
+  <si>
+    <t>136707527</t>
+  </si>
+  <si>
+    <t>136764365</t>
+  </si>
+  <si>
+    <t>131757154</t>
+  </si>
+  <si>
+    <t>131631229</t>
+  </si>
+  <si>
+    <t>136765302</t>
+  </si>
+  <si>
+    <t>136693700</t>
+  </si>
+  <si>
+    <t>136658089</t>
+  </si>
+  <si>
+    <t>136445117</t>
+  </si>
+  <si>
+    <t>136745200</t>
+  </si>
+  <si>
+    <t>136751279</t>
+  </si>
+  <si>
+    <t>136746818</t>
+  </si>
+  <si>
+    <t>136194446</t>
+  </si>
+  <si>
+    <t>136300799</t>
+  </si>
+  <si>
+    <t>132566665</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 19.02.2026</t>
   </si>
 </sst>
 </file>
@@ -475,132 +580,585 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F35"/>
     </row>
   </sheetData>
@@ -617,31 +1175,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0BEA4D-834B-48D6-8BEC-8AF95F683370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="61">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,168 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>131666387</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 23.02.2026</t>
+  </si>
+  <si>
+    <t>131666435</t>
+  </si>
+  <si>
+    <t>131500738</t>
+  </si>
+  <si>
+    <t>131567885</t>
+  </si>
+  <si>
+    <t>131752942</t>
+  </si>
+  <si>
+    <t>136806803</t>
+  </si>
+  <si>
+    <t>136803337</t>
+  </si>
+  <si>
+    <t>136762726</t>
+  </si>
+  <si>
+    <t>136701112</t>
+  </si>
+  <si>
+    <t>131729280</t>
+  </si>
+  <si>
+    <t>136703652</t>
+  </si>
+  <si>
+    <t>131874092</t>
+  </si>
+  <si>
+    <t>136796114</t>
+  </si>
+  <si>
+    <t>131514231</t>
+  </si>
+  <si>
+    <t>131771180</t>
+  </si>
+  <si>
+    <t>136765521</t>
+  </si>
+  <si>
+    <t>136747220</t>
+  </si>
+  <si>
+    <t>136751442</t>
+  </si>
+  <si>
+    <t>136740470</t>
+  </si>
+  <si>
+    <t>131609761</t>
+  </si>
+  <si>
+    <t>136799189</t>
+  </si>
+  <si>
+    <t>136823048</t>
+  </si>
+  <si>
+    <t>136440410 </t>
+  </si>
+  <si>
+    <t>136574314</t>
+  </si>
+  <si>
+    <t>136765560</t>
+  </si>
+  <si>
+    <t>136716997</t>
+  </si>
+  <si>
+    <t>136765800</t>
+  </si>
+  <si>
+    <t>136816299</t>
+  </si>
+  <si>
+    <t>136473801</t>
+  </si>
+  <si>
+    <t>136767930</t>
+  </si>
+  <si>
+    <t>136627454</t>
+  </si>
+  <si>
+    <t>131612826</t>
+  </si>
+  <si>
+    <t>131569454</t>
+  </si>
+  <si>
+    <t>136400263</t>
+  </si>
+  <si>
+    <t>131609168</t>
+  </si>
+  <si>
+    <t>131352550</t>
+  </si>
+  <si>
+    <t>131605864</t>
+  </si>
+  <si>
+    <t>136385834</t>
+  </si>
+  <si>
+    <t>136656683</t>
+  </si>
+  <si>
+    <t>136765652</t>
+  </si>
+  <si>
+    <t>131630875</t>
+  </si>
+  <si>
+    <t>133232736</t>
+  </si>
+  <si>
+    <t>136371062</t>
+  </si>
+  <si>
+    <t>136765609</t>
+  </si>
+  <si>
+    <t>136302693</t>
+  </si>
+  <si>
+    <t>136756170</t>
+  </si>
+  <si>
+    <t>135113828</t>
+  </si>
+  <si>
+    <t>135506617</t>
+  </si>
+  <si>
+    <t>132917468</t>
+  </si>
+  <si>
+    <t>136825656</t>
+  </si>
+  <si>
+    <t>136633427</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 23.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +606,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +637,905 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1551,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99A5609-DC38-4527-8E41-566C7D9DD41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="52">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,141 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>131344402</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 13.02.2026</t>
+  </si>
+  <si>
+    <t>131653039</t>
+  </si>
+  <si>
+    <t>136549558</t>
+  </si>
+  <si>
+    <t>136064785</t>
+  </si>
+  <si>
+    <t>131377992</t>
+  </si>
+  <si>
+    <t>136400478</t>
+  </si>
+  <si>
+    <t>136633427</t>
+  </si>
+  <si>
+    <t>131646452</t>
+  </si>
+  <si>
+    <t>136513782</t>
+  </si>
+  <si>
+    <t>136711054</t>
+  </si>
+  <si>
+    <t>136500603</t>
+  </si>
+  <si>
+    <t>136738691</t>
+  </si>
+  <si>
+    <t>131326941</t>
+  </si>
+  <si>
+    <t>136540581</t>
+  </si>
+  <si>
+    <t>136746818</t>
+  </si>
+  <si>
+    <t>131724981</t>
+  </si>
+  <si>
+    <t>136713286</t>
+  </si>
+  <si>
+    <t>136767849</t>
+  </si>
+  <si>
+    <t>136738858</t>
+  </si>
+  <si>
+    <t>136540733</t>
+  </si>
+  <si>
+    <t>136628850</t>
+  </si>
+  <si>
+    <t>136438212</t>
+  </si>
+  <si>
+    <t>136549891</t>
+  </si>
+  <si>
+    <t>136665762</t>
+  </si>
+  <si>
+    <t>136872564</t>
+  </si>
+  <si>
+    <t>136525346</t>
+  </si>
+  <si>
+    <t>136738458</t>
+  </si>
+  <si>
+    <t>136849845</t>
+  </si>
+  <si>
+    <t>136129442</t>
+  </si>
+  <si>
+    <t>136627445</t>
+  </si>
+  <si>
+    <t>131343603</t>
+  </si>
+  <si>
+    <t>136857923</t>
+  </si>
+  <si>
+    <t>136628472</t>
+  </si>
+  <si>
+    <t>136362138</t>
+  </si>
+  <si>
+    <t>136539084</t>
+  </si>
+  <si>
+    <t>131365294</t>
+  </si>
+  <si>
+    <t>136686882</t>
+  </si>
+  <si>
+    <t>132319481</t>
+  </si>
+  <si>
+    <t>131779693</t>
+  </si>
+  <si>
+    <t>136403327</t>
+  </si>
+  <si>
+    <t>136028589</t>
+  </si>
+  <si>
+    <t>136516381</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 13.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +610,752 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1371,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99A5609-DC38-4527-8E41-566C7D9DD41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD4BDCF-15F2-4947-99A1-EC08AFBF734E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="57">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,139 +51,154 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>131344402</t>
+    <t>131808830</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 13.02.2026</t>
-  </si>
-  <si>
-    <t>131653039</t>
-  </si>
-  <si>
-    <t>136549558</t>
-  </si>
-  <si>
-    <t>136064785</t>
-  </si>
-  <si>
-    <t>131377992</t>
-  </si>
-  <si>
-    <t>136400478</t>
-  </si>
-  <si>
-    <t>136633427</t>
-  </si>
-  <si>
-    <t>131646452</t>
-  </si>
-  <si>
-    <t>136513782</t>
-  </si>
-  <si>
-    <t>136711054</t>
-  </si>
-  <si>
-    <t>136500603</t>
-  </si>
-  <si>
-    <t>136738691</t>
-  </si>
-  <si>
-    <t>131326941</t>
-  </si>
-  <si>
-    <t>136540581</t>
-  </si>
-  <si>
-    <t>136746818</t>
-  </si>
-  <si>
-    <t>131724981</t>
-  </si>
-  <si>
-    <t>136713286</t>
-  </si>
-  <si>
-    <t>136767849</t>
-  </si>
-  <si>
-    <t>136738858</t>
-  </si>
-  <si>
-    <t>136540733</t>
-  </si>
-  <si>
-    <t>136628850</t>
-  </si>
-  <si>
-    <t>136438212</t>
-  </si>
-  <si>
-    <t>136549891</t>
-  </si>
-  <si>
-    <t>136665762</t>
-  </si>
-  <si>
-    <t>136872564</t>
-  </si>
-  <si>
-    <t>136525346</t>
-  </si>
-  <si>
-    <t>136738458</t>
-  </si>
-  <si>
-    <t>136849845</t>
-  </si>
-  <si>
-    <t>136129442</t>
-  </si>
-  <si>
-    <t>136627445</t>
-  </si>
-  <si>
-    <t>131343603</t>
-  </si>
-  <si>
-    <t>136857923</t>
-  </si>
-  <si>
-    <t>136628472</t>
-  </si>
-  <si>
-    <t>136362138</t>
-  </si>
-  <si>
-    <t>136539084</t>
-  </si>
-  <si>
-    <t>131365294</t>
-  </si>
-  <si>
-    <t>136686882</t>
-  </si>
-  <si>
-    <t>132319481</t>
-  </si>
-  <si>
-    <t>131779693</t>
-  </si>
-  <si>
-    <t>136403327</t>
-  </si>
-  <si>
-    <t>136028589</t>
-  </si>
-  <si>
-    <t>136516381</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 13.02.2026</t>
+    <t>Nup- Cancelamento 25.02.2026</t>
+  </si>
+  <si>
+    <t>131665921</t>
+  </si>
+  <si>
+    <t>136467207</t>
+  </si>
+  <si>
+    <t>136795715</t>
+  </si>
+  <si>
+    <t>131911044</t>
+  </si>
+  <si>
+    <t>136500443</t>
+  </si>
+  <si>
+    <t>135513890</t>
+  </si>
+  <si>
+    <t>136765819</t>
+  </si>
+  <si>
+    <t>131675264</t>
+  </si>
+  <si>
+    <t>136737886</t>
+  </si>
+  <si>
+    <t>131668682</t>
+  </si>
+  <si>
+    <t>136764528</t>
+  </si>
+  <si>
+    <t>136557549</t>
+  </si>
+  <si>
+    <t>136812642</t>
+  </si>
+  <si>
+    <t>131619943</t>
+  </si>
+  <si>
+    <t>131571468</t>
+  </si>
+  <si>
+    <t>131664325</t>
+  </si>
+  <si>
+    <t>136841996</t>
+  </si>
+  <si>
+    <t>131428669</t>
+  </si>
+  <si>
+    <t>136706091</t>
+  </si>
+  <si>
+    <t>135982023</t>
+  </si>
+  <si>
+    <t>131924956</t>
+  </si>
+  <si>
+    <t>136878995</t>
+  </si>
+  <si>
+    <t>131845080</t>
+  </si>
+  <si>
+    <t>131568280</t>
+  </si>
+  <si>
+    <t>136693561</t>
+  </si>
+  <si>
+    <t>131809835</t>
+  </si>
+  <si>
+    <t>131727325</t>
+  </si>
+  <si>
+    <t>136767697</t>
+  </si>
+  <si>
+    <t>136765772</t>
+  </si>
+  <si>
+    <t>136704127</t>
+  </si>
+  <si>
+    <t>134195465</t>
+  </si>
+  <si>
+    <t>136439944</t>
+  </si>
+  <si>
+    <t>136765636</t>
+  </si>
+  <si>
+    <t>136763374</t>
+  </si>
+  <si>
+    <t>136798936</t>
+  </si>
+  <si>
+    <t>136878558</t>
+  </si>
+  <si>
+    <t>136712106</t>
+  </si>
+  <si>
+    <t>135522763</t>
+  </si>
+  <si>
+    <t>136798274</t>
+  </si>
+  <si>
+    <t>136564566</t>
+  </si>
+  <si>
+    <t>136811690</t>
+  </si>
+  <si>
+    <t>135508887</t>
+  </si>
+  <si>
+    <t>132188941</t>
+  </si>
+  <si>
+    <t>136831744</t>
+  </si>
+  <si>
+    <t>136765545</t>
+  </si>
+  <si>
+    <t>136763435</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25.02.2026</t>
   </si>
 </sst>
 </file>
@@ -579,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,7 +635,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -638,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -656,7 +671,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -674,7 +689,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -692,7 +707,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -710,7 +725,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,7 +743,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -746,7 +761,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -764,7 +779,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -782,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -800,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -818,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -836,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -854,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -872,7 +887,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -890,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -908,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -926,7 +941,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -944,7 +959,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -962,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -980,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -998,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1142,7 +1157,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1160,7 +1175,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1178,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1196,7 +1211,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1214,7 +1229,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1232,7 +1247,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1249,7 +1264,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1266,7 +1281,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1283,7 +1298,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1300,7 +1315,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1317,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1334,7 +1349,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1351,9 +1366,94 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD4BDCF-15F2-4947-99A1-EC08AFBF734E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CD0057-44E3-4042-8455-B44A9B1BE03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,154 +51,175 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>131808830</t>
+    <t>136765334</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Nup- Cancelamento 25.02.2026</t>
-  </si>
-  <si>
-    <t>131665921</t>
-  </si>
-  <si>
-    <t>136467207</t>
-  </si>
-  <si>
-    <t>136795715</t>
-  </si>
-  <si>
-    <t>131911044</t>
-  </si>
-  <si>
-    <t>136500443</t>
-  </si>
-  <si>
-    <t>135513890</t>
-  </si>
-  <si>
-    <t>136765819</t>
-  </si>
-  <si>
-    <t>131675264</t>
-  </si>
-  <si>
-    <t>136737886</t>
-  </si>
-  <si>
-    <t>131668682</t>
-  </si>
-  <si>
-    <t>136764528</t>
-  </si>
-  <si>
-    <t>136557549</t>
-  </si>
-  <si>
-    <t>136812642</t>
-  </si>
-  <si>
-    <t>131619943</t>
-  </si>
-  <si>
-    <t>131571468</t>
-  </si>
-  <si>
-    <t>131664325</t>
-  </si>
-  <si>
-    <t>136841996</t>
-  </si>
-  <si>
-    <t>131428669</t>
-  </si>
-  <si>
-    <t>136706091</t>
-  </si>
-  <si>
-    <t>135982023</t>
-  </si>
-  <si>
-    <t>131924956</t>
-  </si>
-  <si>
-    <t>136878995</t>
-  </si>
-  <si>
-    <t>131845080</t>
-  </si>
-  <si>
-    <t>131568280</t>
-  </si>
-  <si>
-    <t>136693561</t>
-  </si>
-  <si>
-    <t>131809835</t>
-  </si>
-  <si>
-    <t>131727325</t>
-  </si>
-  <si>
-    <t>136767697</t>
-  </si>
-  <si>
-    <t>136765772</t>
-  </si>
-  <si>
-    <t>136704127</t>
-  </si>
-  <si>
-    <t>134195465</t>
-  </si>
-  <si>
-    <t>136439944</t>
+    <t>Nup- Cancelamento 26.02.2026</t>
+  </si>
+  <si>
+    <t>131455751</t>
+  </si>
+  <si>
+    <t>131531655</t>
+  </si>
+  <si>
+    <t>131585879</t>
+  </si>
+  <si>
+    <t>136765665</t>
+  </si>
+  <si>
+    <t>136892582</t>
+  </si>
+  <si>
+    <t>131631802</t>
+  </si>
+  <si>
+    <t>131570202</t>
+  </si>
+  <si>
+    <t>136805982</t>
+  </si>
+  <si>
+    <t>136763435</t>
+  </si>
+  <si>
+    <t>136378147</t>
+  </si>
+  <si>
+    <t>136798892</t>
+  </si>
+  <si>
+    <t>131832369</t>
+  </si>
+  <si>
+    <t>136765272</t>
+  </si>
+  <si>
+    <t>131505858</t>
+  </si>
+  <si>
+    <t>136850040</t>
+  </si>
+  <si>
+    <t>131718434</t>
+  </si>
+  <si>
+    <t>136816181</t>
+  </si>
+  <si>
+    <t>136765565</t>
+  </si>
+  <si>
+    <t>131781767</t>
+  </si>
+  <si>
+    <t>136782919</t>
+  </si>
+  <si>
+    <t>136708157</t>
+  </si>
+  <si>
+    <t>136760684</t>
+  </si>
+  <si>
+    <t>136837223</t>
+  </si>
+  <si>
+    <t>131810606</t>
+  </si>
+  <si>
+    <t>131616316</t>
+  </si>
+  <si>
+    <t>136804101</t>
+  </si>
+  <si>
+    <t>131493236</t>
+  </si>
+  <si>
+    <t>136543719</t>
+  </si>
+  <si>
+    <t>136761626</t>
+  </si>
+  <si>
+    <t>131558496</t>
+  </si>
+  <si>
+    <t>136564467</t>
+  </si>
+  <si>
+    <t>131895672</t>
+  </si>
+  <si>
+    <t>136767624</t>
+  </si>
+  <si>
+    <t>136703142</t>
+  </si>
+  <si>
+    <t>136764774</t>
+  </si>
+  <si>
+    <t>136738540</t>
+  </si>
+  <si>
+    <t>131544509</t>
+  </si>
+  <si>
+    <t>131876379</t>
+  </si>
+  <si>
+    <t>131621626</t>
   </si>
   <si>
     <t>136765636</t>
   </si>
   <si>
-    <t>136763374</t>
-  </si>
-  <si>
-    <t>136798936</t>
-  </si>
-  <si>
-    <t>136878558</t>
-  </si>
-  <si>
-    <t>136712106</t>
-  </si>
-  <si>
-    <t>135522763</t>
-  </si>
-  <si>
-    <t>136798274</t>
-  </si>
-  <si>
-    <t>136564566</t>
-  </si>
-  <si>
-    <t>136811690</t>
-  </si>
-  <si>
-    <t>135508887</t>
-  </si>
-  <si>
-    <t>132188941</t>
-  </si>
-  <si>
-    <t>136831744</t>
-  </si>
-  <si>
-    <t>136765545</t>
-  </si>
-  <si>
-    <t>136763435</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25.02.2026</t>
+    <t>131570372</t>
+  </si>
+  <si>
+    <t>131453376</t>
+  </si>
+  <si>
+    <t>132638198</t>
+  </si>
+  <si>
+    <t>136770962</t>
+  </si>
+  <si>
+    <t>136885073</t>
+  </si>
+  <si>
+    <t>133243780</t>
+  </si>
+  <si>
+    <t>131771482</t>
+  </si>
+  <si>
+    <t>136889113</t>
+  </si>
+  <si>
+    <t>136519800</t>
+  </si>
+  <si>
+    <t>131706746</t>
+  </si>
+  <si>
+    <t>136899823</t>
+  </si>
+  <si>
+    <t>136792949</t>
+  </si>
+  <si>
+    <t>136078017</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 26.02.2026</t>
   </si>
 </sst>
 </file>
@@ -594,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -635,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -653,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -671,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -689,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -707,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -725,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -743,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -761,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -779,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -797,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -815,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -833,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -851,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -869,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -887,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -905,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -923,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -941,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -959,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -977,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -995,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1031,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1049,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1067,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1085,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1103,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1121,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1139,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1157,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1175,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1193,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1211,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1229,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1247,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1264,7 +1285,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1281,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1298,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1315,7 +1336,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1332,7 +1353,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1349,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1366,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1383,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1400,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1417,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1434,7 +1455,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1451,9 +1472,128 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{89A07BAE-07E6-4167-A9AE-357A140BA60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD5FF77-CE17-44DA-8D7D-6D6B8E60BFC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6760B1D1-0DFD-4763-90C5-82D0341162CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="67">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,186 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136843639</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.02.2026</t>
+  </si>
+  <si>
+    <t>136876564</t>
+  </si>
+  <si>
+    <t>136765643</t>
+  </si>
+  <si>
+    <t>136838957</t>
+  </si>
+  <si>
+    <t>136910483</t>
+  </si>
+  <si>
+    <t>136844460</t>
+  </si>
+  <si>
+    <t>136879337</t>
+  </si>
+  <si>
+    <t>131956803</t>
+  </si>
+  <si>
+    <t>136381729</t>
+  </si>
+  <si>
+    <t>131581197</t>
+  </si>
+  <si>
+    <t>136872528</t>
+  </si>
+  <si>
+    <t>136659379</t>
+  </si>
+  <si>
+    <t>136877220</t>
+  </si>
+  <si>
+    <t>131721951</t>
+  </si>
+  <si>
+    <t>131834184</t>
+  </si>
+  <si>
+    <t>136515803</t>
+  </si>
+  <si>
+    <t>136910456</t>
+  </si>
+  <si>
+    <t>135284700</t>
+  </si>
+  <si>
+    <t>136849564</t>
+  </si>
+  <si>
+    <t>136898840</t>
+  </si>
+  <si>
+    <t>131746430</t>
+  </si>
+  <si>
+    <t>136764540</t>
+  </si>
+  <si>
+    <t>136862682</t>
+  </si>
+  <si>
+    <t>136738712</t>
+  </si>
+  <si>
+    <t>131805706</t>
+  </si>
+  <si>
+    <t>131563379</t>
+  </si>
+  <si>
+    <t>131845352</t>
+  </si>
+  <si>
+    <t>136658818</t>
+  </si>
+  <si>
+    <t>135983652</t>
+  </si>
+  <si>
+    <t>131623908</t>
+  </si>
+  <si>
+    <t>136872679</t>
+  </si>
+  <si>
+    <t>136794121</t>
+  </si>
+  <si>
+    <t>136881037</t>
+  </si>
+  <si>
+    <t>136693814</t>
+  </si>
+  <si>
+    <t>131958178</t>
+  </si>
+  <si>
+    <t>136812143</t>
+  </si>
+  <si>
+    <t>133898249</t>
+  </si>
+  <si>
+    <t>136577660</t>
+  </si>
+  <si>
+    <t>131622175</t>
+  </si>
+  <si>
+    <t>131517841</t>
+  </si>
+  <si>
+    <t>136799319</t>
+  </si>
+  <si>
+    <t>131686768</t>
+  </si>
+  <si>
+    <t>131516554</t>
+  </si>
+  <si>
+    <t>131615401</t>
+  </si>
+  <si>
+    <t>131858264</t>
+  </si>
+  <si>
+    <t>136828583</t>
+  </si>
+  <si>
+    <t>136787970</t>
+  </si>
+  <si>
+    <t>134854699</t>
+  </si>
+  <si>
+    <t>136182687</t>
+  </si>
+  <si>
+    <t>136889286</t>
+  </si>
+  <si>
+    <t>136783975</t>
+  </si>
+  <si>
+    <t>136911576</t>
+  </si>
+  <si>
+    <t>136791424</t>
+  </si>
+  <si>
+    <t>136800082</t>
+  </si>
+  <si>
+    <t>136656486</t>
+  </si>
+  <si>
+    <t>136764707</t>
+  </si>
+  <si>
+    <t>132256943</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +624,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,133 +655,1007 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -617,31 +1671,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>